--- a/KAFD00330_Delivery_Master.xlsx
+++ b/KAFD00330_Delivery_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbcmsa-my.sharepoint.com/personal/mohammed_b_sbcm-sa_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_8BA9DB37BA53F7FBFE4CBC98CE6C187D79F3B5EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8605C6B1-B5B9-414D-A51A-BF1F35C017D0}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="11_8BA9DB37BA53F7FBFE4CBC98CE6C187D79F3B5EA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2DDC95CD-C869-4C05-BC2E-A85D73E03700}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,6 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">Delivery!$A$1:$Z$160</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -41,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2081" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2253" uniqueCount="488">
   <si>
     <t>KAFD00330 — RO Plant: Material Delivery Master (edit here; sync to the report)</t>
   </si>
@@ -1286,9 +1285,6 @@
     <t>Hollow Metal Doors and Frames</t>
   </si>
   <si>
-    <t>Al Kuhami</t>
-  </si>
-  <si>
     <t>ROLLING SHUTTER DOOR,</t>
   </si>
   <si>
@@ -1521,6 +1517,29 @@
   </si>
   <si>
     <t>Shipped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Partially Delivered
+</t>
+  </si>
+  <si>
+    <t>Partially Delivered</t>
+  </si>
+  <si>
+    <t>Crawford</t>
+  </si>
+  <si>
+    <t>Rollec</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MIR-00050</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-CIV-MIR-00008
+KAFD-636-SBC-CIV-MIR-00011
+KAFD-636-SBC-CIV-MIR-00012
+KAFD-636-SBC-CIV-MIR-00048
+KAFD-636-SBC-MEC-MIR-00008</t>
   </si>
 </sst>
 </file>
@@ -1665,6 +1684,12 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1683,12 +1708,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1715,7 +1734,7 @@
       <sheetName val="MECH"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0">
+      <sheetData sheetId="0" refreshError="1">
         <row r="3">
           <cell r="I3" t="str">
             <v>SCADA System</v>
@@ -3126,7 +3145,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z160"/>
+  <dimension ref="A1:Z161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" style="14" bestFit="1" customWidth="1"/>
@@ -3153,39 +3172,39 @@
     <col min="23" max="23" width="22.77734375" style="12" customWidth="1"/>
     <col min="24" max="24" width="11.88671875" customWidth="1"/>
     <col min="25" max="25" width="11.5546875" customWidth="1"/>
-    <col min="26" max="26" width="25.88671875" style="30" customWidth="1"/>
+    <col min="26" max="26" width="25.88671875" style="23" customWidth="1"/>
     <col min="27" max="28" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="25"/>
-      <c r="R1" s="25"/>
-      <c r="S1" s="25"/>
-      <c r="T1" s="25"/>
-      <c r="U1" s="27"/>
-      <c r="V1" s="28"/>
-      <c r="W1" s="24"/>
-      <c r="X1" s="26"/>
-      <c r="Y1" s="26"/>
-      <c r="Z1" s="26"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="25"/>
+      <c r="O1" s="25"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="27"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="26"/>
+      <c r="X1" s="28"/>
+      <c r="Y1" s="28"/>
+      <c r="Z1" s="28"/>
     </row>
     <row r="2" spans="1:26" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
@@ -3263,7 +3282,7 @@
       <c r="Y2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Z2" s="29" t="s">
+      <c r="Z2" s="22" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3393,12 +3412,14 @@
         <v>46321</v>
       </c>
       <c r="W4" s="9" t="s">
-        <v>39</v>
+        <v>368</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="Y4" s="3"/>
+        <v>481</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="Z4" s="3" t="s">
         <v>48</v>
       </c>
@@ -3942,7 +3963,9 @@
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
-      <c r="T13" s="5"/>
+      <c r="T13" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U13" s="11">
         <v>46319</v>
       </c>
@@ -4001,7 +4024,9 @@
       <c r="Q14" s="13"/>
       <c r="R14" s="13"/>
       <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
+      <c r="T14" s="13" t="s">
+        <v>112</v>
+      </c>
       <c r="U14" s="20">
         <v>46344</v>
       </c>
@@ -4060,7 +4085,9 @@
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
-      <c r="T15" s="5"/>
+      <c r="T15" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U15" s="11">
         <v>46344</v>
       </c>
@@ -4119,7 +4146,9 @@
       <c r="Q16" s="13"/>
       <c r="R16" s="13"/>
       <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
+      <c r="T16" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U16" s="20">
         <v>46344</v>
       </c>
@@ -4178,7 +4207,9 @@
       <c r="Q17" s="5"/>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
-      <c r="T17" s="5"/>
+      <c r="T17" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U17" s="11">
         <v>46330</v>
       </c>
@@ -4300,7 +4331,9 @@
       <c r="S19" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T19" s="5"/>
+      <c r="T19" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U19" s="11">
         <v>46362</v>
       </c>
@@ -4358,7 +4391,9 @@
       <c r="Q20" s="13"/>
       <c r="R20" s="13"/>
       <c r="S20" s="13"/>
-      <c r="T20" s="13"/>
+      <c r="T20" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U20" s="20">
         <v>46353</v>
       </c>
@@ -4416,7 +4451,9 @@
       <c r="Q21" s="5"/>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
-      <c r="T21" s="5"/>
+      <c r="T21" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U21" s="11">
         <v>46285</v>
       </c>
@@ -4475,7 +4512,9 @@
       <c r="Q22" s="13"/>
       <c r="R22" s="13"/>
       <c r="S22" s="13"/>
-      <c r="T22" s="13"/>
+      <c r="T22" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U22" s="20">
         <v>46285</v>
       </c>
@@ -4486,9 +4525,11 @@
       <c r="W22" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="X22" s="3"/>
+      <c r="X22" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y22" s="2" t="s">
-        <v>118</v>
+        <v>482</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>119</v>
@@ -4540,7 +4581,9 @@
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
-      <c r="T23" s="5"/>
+      <c r="T23" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U23" s="11">
         <v>46285</v>
       </c>
@@ -4551,7 +4594,9 @@
       <c r="W23" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="X23" s="2"/>
+      <c r="X23" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y23" s="2" t="s">
         <v>118</v>
       </c>
@@ -4605,7 +4650,9 @@
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
       <c r="S24" s="13"/>
-      <c r="T24" s="13"/>
+      <c r="T24" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U24" s="20">
         <v>46285</v>
       </c>
@@ -4615,7 +4662,9 @@
       <c r="W24" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="X24" s="3"/>
+      <c r="X24" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y24" s="2" t="s">
         <v>118</v>
       </c>
@@ -4669,7 +4718,9 @@
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
+      <c r="T25" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U25" s="11">
         <v>46285</v>
       </c>
@@ -4680,9 +4731,11 @@
       <c r="W25" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="X25" s="2"/>
+      <c r="X25" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y25" s="2" t="s">
-        <v>118</v>
+        <v>482</v>
       </c>
       <c r="Z25" s="2" t="s">
         <v>135</v>
@@ -4734,7 +4787,9 @@
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
       <c r="S26" s="13"/>
-      <c r="T26" s="13"/>
+      <c r="T26" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U26" s="20">
         <v>46306</v>
       </c>
@@ -4743,8 +4798,12 @@
         <v>46280</v>
       </c>
       <c r="W26" s="9"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
+      <c r="X26" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>482</v>
+      </c>
       <c r="Z26" s="3" t="s">
         <v>140</v>
       </c>
@@ -4795,7 +4854,9 @@
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
-      <c r="T27" s="5"/>
+      <c r="T27" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U27" s="11">
         <v>46306</v>
       </c>
@@ -4853,7 +4914,9 @@
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
       <c r="S28" s="13"/>
-      <c r="T28" s="13"/>
+      <c r="T28" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U28" s="20">
         <v>46326</v>
       </c>
@@ -4864,7 +4927,9 @@
       <c r="W28" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="X28" s="3"/>
+      <c r="X28" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y28" s="2" t="s">
         <v>118</v>
       </c>
@@ -4914,7 +4979,9 @@
       <c r="Q29" s="5"/>
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
+      <c r="T29" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U29" s="11">
         <v>46353</v>
       </c>
@@ -4969,7 +5036,9 @@
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
       <c r="S30" s="13"/>
-      <c r="T30" s="13"/>
+      <c r="T30" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U30" s="20">
         <v>46285</v>
       </c>
@@ -4982,7 +5051,7 @@
       </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="2" t="s">
-        <v>118</v>
+        <v>483</v>
       </c>
       <c r="Z30" s="3"/>
     </row>
@@ -5032,7 +5101,9 @@
       <c r="Q31" s="5"/>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
-      <c r="T31" s="5"/>
+      <c r="T31" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U31" s="11">
         <v>46285</v>
       </c>
@@ -5047,7 +5118,9 @@
       <c r="Y31" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="Z31" s="2"/>
+      <c r="Z31" s="2" t="s">
+        <v>487</v>
+      </c>
     </row>
     <row r="32" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19">
@@ -5089,7 +5162,9 @@
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
       <c r="S32" s="13"/>
-      <c r="T32" s="13"/>
+      <c r="T32" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U32" s="20">
         <v>46367</v>
       </c>
@@ -5147,7 +5222,9 @@
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
-      <c r="T33" s="5"/>
+      <c r="T33" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U33" s="11">
         <v>46353</v>
       </c>
@@ -5205,7 +5282,9 @@
       <c r="Q34" s="13"/>
       <c r="R34" s="13"/>
       <c r="S34" s="13"/>
-      <c r="T34" s="13"/>
+      <c r="T34" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U34" s="20">
         <v>46172</v>
       </c>
@@ -5214,9 +5293,11 @@
         <v>#N/A</v>
       </c>
       <c r="W34" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X34" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X34" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y34" s="3" t="s">
         <v>118</v>
       </c>
@@ -5274,7 +5355,9 @@
       <c r="S35" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T35" s="5"/>
+      <c r="T35" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U35" s="11">
         <v>46172</v>
       </c>
@@ -5284,7 +5367,9 @@
       <c r="W35" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="X35" s="2"/>
+      <c r="X35" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y35" s="2" t="s">
         <v>118</v>
       </c>
@@ -5342,7 +5427,9 @@
       <c r="S36" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T36" s="13"/>
+      <c r="T36" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U36" s="20">
         <v>46172</v>
       </c>
@@ -5352,7 +5439,9 @@
       <c r="W36" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="X36" s="3"/>
+      <c r="X36" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y36" s="2" t="s">
         <v>118</v>
       </c>
@@ -5406,7 +5495,9 @@
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
       <c r="S37" s="5"/>
-      <c r="T37" s="5"/>
+      <c r="T37" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U37" s="11">
         <v>46290</v>
       </c>
@@ -5416,7 +5507,9 @@
       <c r="W37" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="X37" s="2"/>
+      <c r="X37" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y37" s="2" t="s">
         <v>118</v>
       </c>
@@ -5485,9 +5578,11 @@
         <v>#N/A</v>
       </c>
       <c r="W38" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X38" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X38" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
@@ -5537,7 +5632,9 @@
       <c r="Q39" s="5"/>
       <c r="R39" s="5"/>
       <c r="S39" s="5"/>
-      <c r="T39" s="5"/>
+      <c r="T39" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U39" s="11">
         <v>46275</v>
       </c>
@@ -5551,7 +5648,9 @@
       <c r="Y39" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="Z39" s="2"/>
+      <c r="Z39" s="2" t="s">
+        <v>486</v>
+      </c>
     </row>
     <row r="40" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19">
@@ -5611,7 +5710,9 @@
       <c r="W40" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="X40" s="2"/>
+      <c r="X40" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y40" s="2" t="s">
         <v>118</v>
       </c>
@@ -5667,7 +5768,9 @@
       </c>
       <c r="R41" s="13"/>
       <c r="S41" s="13"/>
-      <c r="T41" s="13"/>
+      <c r="T41" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U41" s="20">
         <v>46302</v>
       </c>
@@ -5722,7 +5825,9 @@
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
-      <c r="T42" s="5"/>
+      <c r="T42" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U42" s="11">
         <v>46411</v>
       </c>
@@ -5774,7 +5879,9 @@
       <c r="Q43" s="13"/>
       <c r="R43" s="13"/>
       <c r="S43" s="13"/>
-      <c r="T43" s="13"/>
+      <c r="T43" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U43" s="20">
         <v>46411</v>
       </c>
@@ -5832,7 +5939,9 @@
       <c r="S44" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="T44" s="5"/>
+      <c r="T44" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U44" s="11">
         <v>46312</v>
       </c>
@@ -5888,7 +5997,9 @@
       <c r="Q45" s="13"/>
       <c r="R45" s="13"/>
       <c r="S45" s="13"/>
-      <c r="T45" s="13"/>
+      <c r="T45" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U45" s="20">
         <v>46411</v>
       </c>
@@ -6022,9 +6133,11 @@
         <v>46285</v>
       </c>
       <c r="W47" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X47" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
@@ -6074,7 +6187,9 @@
       <c r="Q48" s="5"/>
       <c r="R48" s="5"/>
       <c r="S48" s="5"/>
-      <c r="T48" s="5"/>
+      <c r="T48" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U48" s="11">
         <v>46299</v>
       </c>
@@ -6082,9 +6197,11 @@
         <v>46259</v>
       </c>
       <c r="W48" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X48" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X48" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
@@ -6134,7 +6251,9 @@
       <c r="Q49" s="13"/>
       <c r="R49" s="13"/>
       <c r="S49" s="13"/>
-      <c r="T49" s="13"/>
+      <c r="T49" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U49" s="20">
         <v>46299</v>
       </c>
@@ -6142,9 +6261,11 @@
         <v>46285</v>
       </c>
       <c r="W49" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X49" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X49" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
@@ -6206,9 +6327,11 @@
         <v>46285</v>
       </c>
       <c r="W50" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X50" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X50" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
@@ -6260,7 +6383,9 @@
       <c r="S51" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="T51" s="13"/>
+      <c r="T51" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U51" s="20">
         <v>46312</v>
       </c>
@@ -6268,9 +6393,11 @@
         <v>46280</v>
       </c>
       <c r="W51" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X51" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X51" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
@@ -6322,7 +6449,9 @@
       <c r="S52" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="T52" s="5"/>
+      <c r="T52" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U52" s="11">
         <v>46344</v>
       </c>
@@ -6330,9 +6459,11 @@
         <v>46280</v>
       </c>
       <c r="W52" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X52" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X52" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
@@ -6394,9 +6525,11 @@
         <v>46291</v>
       </c>
       <c r="W53" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X53" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X53" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
@@ -6448,7 +6581,9 @@
       <c r="S54" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="T54" s="5"/>
+      <c r="T54" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U54" s="11">
         <v>46312</v>
       </c>
@@ -6456,9 +6591,11 @@
         <v>46280</v>
       </c>
       <c r="W54" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X54" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X54" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
@@ -6574,7 +6711,9 @@
       <c r="Q56" s="5"/>
       <c r="R56" s="5"/>
       <c r="S56" s="5"/>
-      <c r="T56" s="5"/>
+      <c r="T56" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U56" s="11">
         <v>46271</v>
       </c>
@@ -6634,7 +6773,9 @@
       <c r="Q57" s="13"/>
       <c r="R57" s="13"/>
       <c r="S57" s="13"/>
-      <c r="T57" s="13"/>
+      <c r="T57" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U57" s="20">
         <v>46271</v>
       </c>
@@ -6692,7 +6833,9 @@
       <c r="Q58" s="5"/>
       <c r="R58" s="5"/>
       <c r="S58" s="5"/>
-      <c r="T58" s="5"/>
+      <c r="T58" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U58" s="11">
         <v>46271</v>
       </c>
@@ -6752,7 +6895,9 @@
       <c r="Q59" s="13"/>
       <c r="R59" s="13"/>
       <c r="S59" s="13"/>
-      <c r="T59" s="13"/>
+      <c r="T59" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U59" s="20">
         <v>46271</v>
       </c>
@@ -7010,16 +7155,22 @@
       <c r="Q63" s="13"/>
       <c r="R63" s="13"/>
       <c r="S63" s="13"/>
-      <c r="T63" s="13"/>
+      <c r="T63" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U63" s="20">
         <v>46266</v>
       </c>
       <c r="V63" s="16"/>
       <c r="W63" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X63" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y63" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="Z63" s="3" t="s">
         <v>287</v>
       </c>
@@ -7068,7 +7219,9 @@
       <c r="S64" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T64" s="5"/>
+      <c r="T64" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U64" s="11">
         <v>46299</v>
       </c>
@@ -7124,7 +7277,9 @@
       <c r="Q65" s="13"/>
       <c r="R65" s="13"/>
       <c r="S65" s="13"/>
-      <c r="T65" s="13"/>
+      <c r="T65" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U65" s="20">
         <v>46294</v>
       </c>
@@ -7174,7 +7329,9 @@
       <c r="Q66" s="5"/>
       <c r="R66" s="5"/>
       <c r="S66" s="5"/>
-      <c r="T66" s="5"/>
+      <c r="T66" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U66" s="11">
         <v>46266</v>
       </c>
@@ -7234,7 +7391,9 @@
       <c r="S67" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T67" s="13"/>
+      <c r="T67" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U67" s="20">
         <v>46313</v>
       </c>
@@ -7290,7 +7449,9 @@
       <c r="Q68" s="5"/>
       <c r="R68" s="5"/>
       <c r="S68" s="5"/>
-      <c r="T68" s="5"/>
+      <c r="T68" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U68" s="11">
         <v>46271</v>
       </c>
@@ -7416,7 +7577,9 @@
       <c r="S70" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T70" s="5"/>
+      <c r="T70" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U70" s="11">
         <v>46313</v>
       </c>
@@ -7480,7 +7643,9 @@
       <c r="S71" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T71" s="13"/>
+      <c r="T71" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U71" s="20">
         <v>46313</v>
       </c>
@@ -7540,7 +7705,9 @@
       <c r="Q72" s="5"/>
       <c r="R72" s="5"/>
       <c r="S72" s="5"/>
-      <c r="T72" s="5"/>
+      <c r="T72" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U72" s="11">
         <v>46315</v>
       </c>
@@ -7600,7 +7767,9 @@
       <c r="S73" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T73" s="13"/>
+      <c r="T73" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U73" s="20">
         <v>46328</v>
       </c>
@@ -7662,7 +7831,9 @@
       </c>
       <c r="R74" s="5"/>
       <c r="S74" s="5"/>
-      <c r="T74" s="5"/>
+      <c r="T74" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U74" s="11">
         <v>46313</v>
       </c>
@@ -7788,7 +7959,9 @@
       <c r="Q76" s="5"/>
       <c r="R76" s="5"/>
       <c r="S76" s="5"/>
-      <c r="T76" s="5"/>
+      <c r="T76" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U76" s="11">
         <v>46296</v>
       </c>
@@ -7848,7 +8021,9 @@
       <c r="Q77" s="13"/>
       <c r="R77" s="13"/>
       <c r="S77" s="13"/>
-      <c r="T77" s="13"/>
+      <c r="T77" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U77" s="20">
         <v>46296</v>
       </c>
@@ -7856,10 +8031,14 @@
         <v>46247</v>
       </c>
       <c r="W77" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X77" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y77" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="Z77" s="3" t="s">
         <v>171</v>
       </c>
@@ -7910,7 +8089,9 @@
       <c r="Q78" s="5"/>
       <c r="R78" s="5"/>
       <c r="S78" s="5"/>
-      <c r="T78" s="5"/>
+      <c r="T78" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U78" s="11">
         <v>46296</v>
       </c>
@@ -7970,7 +8151,9 @@
       <c r="Q79" s="13"/>
       <c r="R79" s="13"/>
       <c r="S79" s="13"/>
-      <c r="T79" s="13"/>
+      <c r="T79" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U79" s="20">
         <v>46315</v>
       </c>
@@ -8030,7 +8213,9 @@
       <c r="Q80" s="5"/>
       <c r="R80" s="5"/>
       <c r="S80" s="5"/>
-      <c r="T80" s="5"/>
+      <c r="T80" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U80" s="11">
         <v>46296</v>
       </c>
@@ -8038,9 +8223,11 @@
         <v>46247</v>
       </c>
       <c r="W80" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X80" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X80" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
@@ -8090,7 +8277,9 @@
       <c r="Q81" s="13"/>
       <c r="R81" s="13"/>
       <c r="S81" s="13"/>
-      <c r="T81" s="13"/>
+      <c r="T81" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U81" s="20">
         <v>46290</v>
       </c>
@@ -8098,9 +8287,11 @@
         <v>46341</v>
       </c>
       <c r="W81" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X81" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X81" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
@@ -8150,7 +8341,9 @@
       <c r="Q82" s="5"/>
       <c r="R82" s="5"/>
       <c r="S82" s="5"/>
-      <c r="T82" s="5"/>
+      <c r="T82" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U82" s="11">
         <v>46290</v>
       </c>
@@ -8158,9 +8351,11 @@
         <v>46341</v>
       </c>
       <c r="W82" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X82" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X82" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
@@ -8210,7 +8405,9 @@
       <c r="Q83" s="13"/>
       <c r="R83" s="13"/>
       <c r="S83" s="13"/>
-      <c r="T83" s="13"/>
+      <c r="T83" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U83" s="20">
         <v>46290</v>
       </c>
@@ -8218,9 +8415,11 @@
         <v>46341</v>
       </c>
       <c r="W83" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X83" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X83" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
@@ -8270,7 +8469,9 @@
       <c r="Q84" s="5"/>
       <c r="R84" s="5"/>
       <c r="S84" s="5"/>
-      <c r="T84" s="5"/>
+      <c r="T84" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U84" s="11">
         <v>46290</v>
       </c>
@@ -8278,9 +8479,11 @@
         <v>46341</v>
       </c>
       <c r="W84" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X84" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X84" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
@@ -8330,7 +8533,9 @@
       <c r="Q85" s="13"/>
       <c r="R85" s="13"/>
       <c r="S85" s="13"/>
-      <c r="T85" s="13"/>
+      <c r="T85" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U85" s="20">
         <v>46315</v>
       </c>
@@ -8338,9 +8543,11 @@
         <v>46341</v>
       </c>
       <c r="W85" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X85" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X85" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
@@ -8390,7 +8597,9 @@
       <c r="Q86" s="5"/>
       <c r="R86" s="5"/>
       <c r="S86" s="5"/>
-      <c r="T86" s="5"/>
+      <c r="T86" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U86" s="11">
         <v>46315</v>
       </c>
@@ -8398,9 +8607,11 @@
         <v>46341</v>
       </c>
       <c r="W86" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X86" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X86" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
@@ -8586,7 +8797,9 @@
       <c r="S89" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T89" s="13"/>
+      <c r="T89" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U89" s="20">
         <v>46344</v>
       </c>
@@ -8594,9 +8807,11 @@
         <v>46296</v>
       </c>
       <c r="W89" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X89" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X89" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
@@ -8650,7 +8865,9 @@
       <c r="S90" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T90" s="5"/>
+      <c r="T90" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U90" s="11">
         <v>46318</v>
       </c>
@@ -8658,9 +8875,11 @@
         <v>46296</v>
       </c>
       <c r="W90" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X90" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X90" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
@@ -8714,7 +8933,9 @@
       <c r="S91" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T91" s="13"/>
+      <c r="T91" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U91" s="20">
         <v>46318</v>
       </c>
@@ -8722,9 +8943,11 @@
         <v>46296</v>
       </c>
       <c r="W91" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X91" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X91" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
@@ -8788,9 +9011,11 @@
         <v>46296</v>
       </c>
       <c r="W92" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X92" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X92" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
@@ -8844,7 +9069,9 @@
       <c r="S93" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="T93" s="13"/>
+      <c r="T93" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U93" s="20">
         <v>46348</v>
       </c>
@@ -8908,7 +9135,9 @@
       <c r="S94" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="T94" s="5"/>
+      <c r="T94" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U94" s="11">
         <v>46348</v>
       </c>
@@ -9038,7 +9267,9 @@
       <c r="S96" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T96" s="5"/>
+      <c r="T96" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U96" s="11">
         <v>46348</v>
       </c>
@@ -9168,7 +9399,9 @@
       <c r="S98" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T98" s="5"/>
+      <c r="T98" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U98" s="11"/>
       <c r="V98" s="16"/>
       <c r="W98" s="9" t="s">
@@ -9228,7 +9461,9 @@
       <c r="S99" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T99" s="13"/>
+      <c r="T99" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U99" s="20"/>
       <c r="V99" s="16">
         <v>46284</v>
@@ -9288,7 +9523,9 @@
       <c r="Q100" s="5"/>
       <c r="R100" s="5"/>
       <c r="S100" s="5"/>
-      <c r="T100" s="5"/>
+      <c r="T100" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U100" s="11">
         <v>46328</v>
       </c>
@@ -9344,7 +9581,9 @@
       <c r="Q101" s="13"/>
       <c r="R101" s="13"/>
       <c r="S101" s="13"/>
-      <c r="T101" s="13"/>
+      <c r="T101" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U101" s="20">
         <v>46271</v>
       </c>
@@ -9398,7 +9637,9 @@
       <c r="Q102" s="5"/>
       <c r="R102" s="5"/>
       <c r="S102" s="5"/>
-      <c r="T102" s="5"/>
+      <c r="T102" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U102" s="11">
         <v>46271</v>
       </c>
@@ -9452,7 +9693,9 @@
       <c r="Q103" s="13"/>
       <c r="R103" s="13"/>
       <c r="S103" s="13"/>
-      <c r="T103" s="13"/>
+      <c r="T103" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U103" s="20">
         <v>46313</v>
       </c>
@@ -9514,7 +9757,9 @@
       <c r="S104" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T104" s="5"/>
+      <c r="T104" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U104" s="11">
         <v>46257</v>
       </c>
@@ -9522,9 +9767,11 @@
         <v>46284</v>
       </c>
       <c r="W104" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X104" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X104" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
@@ -9576,7 +9823,9 @@
       <c r="S105" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T105" s="13"/>
+      <c r="T105" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U105" s="20">
         <v>46257</v>
       </c>
@@ -9584,9 +9833,11 @@
         <v>46284</v>
       </c>
       <c r="W105" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X105" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X105" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
@@ -9638,7 +9889,9 @@
       <c r="S106" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T106" s="5"/>
+      <c r="T106" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U106" s="11">
         <v>46257</v>
       </c>
@@ -9700,7 +9953,9 @@
       <c r="S107" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T107" s="13"/>
+      <c r="T107" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U107" s="20">
         <v>46257</v>
       </c>
@@ -9708,9 +9963,11 @@
         <v>46284</v>
       </c>
       <c r="W107" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X107" s="3"/>
+        <v>368</v>
+      </c>
+      <c r="X107" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
@@ -9762,7 +10019,9 @@
       <c r="S108" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T108" s="5"/>
+      <c r="T108" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U108" s="11">
         <v>46257</v>
       </c>
@@ -9824,7 +10083,9 @@
       <c r="S109" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T109" s="13"/>
+      <c r="T109" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U109" s="20">
         <v>46257</v>
       </c>
@@ -9886,7 +10147,9 @@
       <c r="S110" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T110" s="5"/>
+      <c r="T110" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U110" s="11">
         <v>46257</v>
       </c>
@@ -9894,9 +10157,11 @@
         <v>46284</v>
       </c>
       <c r="W110" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="X110" s="2"/>
+        <v>368</v>
+      </c>
+      <c r="X110" s="3" t="s">
+        <v>481</v>
+      </c>
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
@@ -9948,7 +10213,9 @@
       <c r="S111" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T111" s="13"/>
+      <c r="T111" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U111" s="20">
         <v>46257</v>
       </c>
@@ -10010,7 +10277,9 @@
       <c r="S112" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T112" s="5"/>
+      <c r="T112" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U112" s="11">
         <v>46257</v>
       </c>
@@ -10061,14 +10330,16 @@
         <v>36</v>
       </c>
       <c r="P113" s="7" t="s">
-        <v>404</v>
+        <v>485</v>
       </c>
       <c r="Q113" s="13"/>
       <c r="R113" s="13"/>
       <c r="S113" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T113" s="13"/>
+      <c r="T113" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U113" s="20">
         <v>46279</v>
       </c>
@@ -10104,7 +10375,7 @@
         <v>32</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>373</v>
@@ -10117,14 +10388,16 @@
         <v>36</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>404</v>
+        <v>484</v>
       </c>
       <c r="Q114" s="5"/>
       <c r="R114" s="5"/>
       <c r="S114" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T114" s="5"/>
+      <c r="T114" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U114" s="11">
         <v>46279</v>
       </c>
@@ -10160,10 +10433,10 @@
         <v>32</v>
       </c>
       <c r="I115" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="J115" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="J115" s="3" t="s">
-        <v>407</v>
       </c>
       <c r="K115" s="3"/>
       <c r="L115" s="3"/>
@@ -10173,14 +10446,16 @@
         <v>36</v>
       </c>
       <c r="P115" s="7" t="s">
-        <v>404</v>
+        <v>485</v>
       </c>
       <c r="Q115" s="13"/>
       <c r="R115" s="13"/>
       <c r="S115" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T115" s="13"/>
+      <c r="T115" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U115" s="20">
         <v>46279</v>
       </c>
@@ -10226,15 +10501,17 @@
       <c r="O116" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="P116" s="6" t="s">
-        <v>404</v>
+      <c r="P116" s="7" t="s">
+        <v>485</v>
       </c>
       <c r="Q116" s="5"/>
       <c r="R116" s="5"/>
       <c r="S116" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T116" s="5"/>
+      <c r="T116" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U116" s="11">
         <v>46327</v>
       </c>
@@ -10270,10 +10547,10 @@
         <v>32</v>
       </c>
       <c r="I117" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="J117" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="J117" s="3" t="s">
-        <v>407</v>
       </c>
       <c r="K117" s="3"/>
       <c r="L117" s="3"/>
@@ -10283,14 +10560,16 @@
         <v>36</v>
       </c>
       <c r="P117" s="7" t="s">
-        <v>404</v>
+        <v>485</v>
       </c>
       <c r="Q117" s="13"/>
       <c r="R117" s="13"/>
       <c r="S117" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T117" s="13"/>
+      <c r="T117" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U117" s="20">
         <v>46327</v>
       </c>
@@ -10308,7 +10587,7 @@
         <v>26</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>83</v>
@@ -10326,7 +10605,7 @@
         <v>32</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J118" s="2"/>
       <c r="K118" s="2"/>
@@ -10340,7 +10619,9 @@
       <c r="Q118" s="5"/>
       <c r="R118" s="5"/>
       <c r="S118" s="5"/>
-      <c r="T118" s="5"/>
+      <c r="T118" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U118" s="11">
         <v>46398</v>
       </c>
@@ -10358,10 +10639,10 @@
         <v>26</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>112</v>
@@ -10370,13 +10651,13 @@
         <v>30</v>
       </c>
       <c r="G119" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I119" s="7" t="s">
         <v>411</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I119" s="7" t="s">
-        <v>412</v>
       </c>
       <c r="J119" s="3"/>
       <c r="K119" s="3"/>
@@ -10387,12 +10668,14 @@
         <v>45</v>
       </c>
       <c r="P119" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q119" s="13"/>
       <c r="R119" s="13"/>
       <c r="S119" s="13"/>
-      <c r="T119" s="13"/>
+      <c r="T119" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U119" s="20"/>
       <c r="V119" s="16"/>
       <c r="W119" s="9"/>
@@ -10408,10 +10691,10 @@
         <v>164</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>112</v>
@@ -10420,13 +10703,13 @@
         <v>30</v>
       </c>
       <c r="G120" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I120" s="6" t="s">
         <v>411</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>412</v>
       </c>
       <c r="J120" s="2"/>
       <c r="K120" s="2"/>
@@ -10437,12 +10720,14 @@
         <v>45</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q120" s="5"/>
       <c r="R120" s="5"/>
       <c r="S120" s="5"/>
-      <c r="T120" s="5"/>
+      <c r="T120" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U120" s="11"/>
       <c r="V120" s="16"/>
       <c r="W120" s="9"/>
@@ -10458,10 +10743,10 @@
         <v>26</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>112</v>
@@ -10470,13 +10755,13 @@
         <v>30</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H121" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J121" s="3"/>
       <c r="K121" s="3"/>
@@ -10487,12 +10772,14 @@
         <v>45</v>
       </c>
       <c r="P121" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q121" s="13"/>
       <c r="R121" s="13"/>
       <c r="S121" s="13"/>
-      <c r="T121" s="13"/>
+      <c r="T121" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U121" s="20">
         <v>46398</v>
       </c>
@@ -10510,10 +10797,10 @@
         <v>164</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>112</v>
@@ -10522,13 +10809,13 @@
         <v>30</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
@@ -10539,12 +10826,14 @@
         <v>45</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q122" s="5"/>
       <c r="R122" s="5"/>
       <c r="S122" s="5"/>
-      <c r="T122" s="5"/>
+      <c r="T122" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U122" s="11">
         <v>46364</v>
       </c>
@@ -10562,7 +10851,7 @@
         <v>164</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D123" s="13" t="s">
         <v>83</v>
@@ -10580,7 +10869,7 @@
         <v>32</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J123" s="3"/>
       <c r="K123" s="3"/>
@@ -10591,12 +10880,14 @@
         <v>45</v>
       </c>
       <c r="P123" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q123" s="13"/>
       <c r="R123" s="13"/>
       <c r="S123" s="13"/>
-      <c r="T123" s="13"/>
+      <c r="T123" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U123" s="20">
         <v>46307</v>
       </c>
@@ -10622,13 +10913,13 @@
         <v>84</v>
       </c>
       <c r="G124" s="9" t="s">
+        <v>416</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I124" s="6" t="s">
         <v>417</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I124" s="6" t="s">
-        <v>418</v>
       </c>
       <c r="J124" s="2"/>
       <c r="K124" s="2"/>
@@ -10642,7 +10933,9 @@
       <c r="Q124" s="5"/>
       <c r="R124" s="5"/>
       <c r="S124" s="5"/>
-      <c r="T124" s="5"/>
+      <c r="T124" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U124" s="11"/>
       <c r="V124" s="16"/>
       <c r="W124" s="9"/>
@@ -10658,10 +10951,10 @@
         <v>26</v>
       </c>
       <c r="C125" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="D125" s="13" t="s">
         <v>419</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>420</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>112</v>
@@ -10670,13 +10963,13 @@
         <v>30</v>
       </c>
       <c r="G125" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I125" s="7" t="s">
         <v>421</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I125" s="7" t="s">
-        <v>422</v>
       </c>
       <c r="J125" s="3"/>
       <c r="K125" s="3"/>
@@ -10687,12 +10980,14 @@
         <v>45</v>
       </c>
       <c r="P125" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q125" s="13"/>
       <c r="R125" s="13"/>
       <c r="S125" s="13"/>
-      <c r="T125" s="13"/>
+      <c r="T125" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U125" s="20">
         <v>46305</v>
       </c>
@@ -10710,10 +11005,10 @@
         <v>26</v>
       </c>
       <c r="C126" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D126" s="5" t="s">
         <v>419</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>420</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>112</v>
@@ -10728,7 +11023,7 @@
         <v>32</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
@@ -10739,12 +11034,14 @@
         <v>45</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q126" s="5"/>
       <c r="R126" s="5"/>
       <c r="S126" s="5"/>
-      <c r="T126" s="5"/>
+      <c r="T126" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U126" s="11">
         <v>46305</v>
       </c>
@@ -10762,10 +11059,10 @@
         <v>26</v>
       </c>
       <c r="C127" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="D127" s="13" t="s">
         <v>419</v>
-      </c>
-      <c r="D127" s="13" t="s">
-        <v>420</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>112</v>
@@ -10780,7 +11077,7 @@
         <v>32</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
@@ -10791,12 +11088,14 @@
         <v>45</v>
       </c>
       <c r="P127" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q127" s="13"/>
       <c r="R127" s="13"/>
       <c r="S127" s="13"/>
-      <c r="T127" s="13"/>
+      <c r="T127" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U127" s="20">
         <v>46305</v>
       </c>
@@ -10814,10 +11113,10 @@
         <v>26</v>
       </c>
       <c r="C128" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D128" s="5" t="s">
         <v>419</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>420</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>112</v>
@@ -10832,7 +11131,7 @@
         <v>32</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
@@ -10843,12 +11142,14 @@
         <v>45</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q128" s="5"/>
       <c r="R128" s="5"/>
       <c r="S128" s="5"/>
-      <c r="T128" s="5"/>
+      <c r="T128" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U128" s="11">
         <v>46305</v>
       </c>
@@ -10866,10 +11167,10 @@
         <v>26</v>
       </c>
       <c r="C129" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D129" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>112</v>
@@ -10884,7 +11185,7 @@
         <v>32</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
@@ -10895,12 +11196,14 @@
         <v>45</v>
       </c>
       <c r="P129" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q129" s="13"/>
       <c r="R129" s="13"/>
       <c r="S129" s="13"/>
-      <c r="T129" s="13"/>
+      <c r="T129" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U129" s="20">
         <v>46411</v>
       </c>
@@ -10918,10 +11221,10 @@
         <v>26</v>
       </c>
       <c r="C130" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="D130" s="5" t="s">
         <v>428</v>
-      </c>
-      <c r="D130" s="5" t="s">
-        <v>429</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>112</v>
@@ -10936,7 +11239,7 @@
         <v>32</v>
       </c>
       <c r="I130" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
@@ -10947,7 +11250,7 @@
         <v>36</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q130" s="5"/>
       <c r="R130" s="5"/>
@@ -10972,10 +11275,10 @@
         <v>26</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>112</v>
@@ -10990,7 +11293,7 @@
         <v>32</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J131" s="3"/>
       <c r="K131" s="3"/>
@@ -11001,7 +11304,7 @@
         <v>36</v>
       </c>
       <c r="P131" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q131" s="13"/>
       <c r="R131" s="13"/>
@@ -11009,7 +11312,9 @@
       <c r="T131" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="U131" s="20"/>
+      <c r="U131" s="20" t="s">
+        <v>112</v>
+      </c>
       <c r="V131" s="16"/>
       <c r="W131" s="9"/>
       <c r="X131" s="3"/>
@@ -11024,10 +11329,10 @@
         <v>26</v>
       </c>
       <c r="C132" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D132" s="5" t="s">
         <v>435</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>436</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>112</v>
@@ -11042,7 +11347,7 @@
         <v>32</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
@@ -11053,7 +11358,7 @@
         <v>36</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q132" s="5" t="s">
         <v>38</v>
@@ -11086,10 +11391,10 @@
         <v>26</v>
       </c>
       <c r="C133" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D133" s="13" t="s">
         <v>435</v>
-      </c>
-      <c r="D133" s="13" t="s">
-        <v>436</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>112</v>
@@ -11104,7 +11409,7 @@
         <v>32</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
@@ -11115,14 +11420,14 @@
         <v>36</v>
       </c>
       <c r="P133" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q133" s="13" t="s">
         <v>38</v>
       </c>
       <c r="R133" s="13"/>
       <c r="S133" s="13" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="T133" s="5" t="s">
         <v>38</v>
@@ -11148,10 +11453,10 @@
         <v>26</v>
       </c>
       <c r="C134" s="9" t="s">
+        <v>434</v>
+      </c>
+      <c r="D134" s="5" t="s">
         <v>435</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>436</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>112</v>
@@ -11166,7 +11471,7 @@
         <v>32</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
@@ -11177,14 +11482,14 @@
         <v>36</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q134" s="5" t="s">
         <v>38</v>
       </c>
       <c r="R134" s="5"/>
       <c r="S134" s="5" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="T134" s="5" t="s">
         <v>38</v>
@@ -11210,10 +11515,10 @@
         <v>26</v>
       </c>
       <c r="C135" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="D135" s="13" t="s">
         <v>435</v>
-      </c>
-      <c r="D135" s="13" t="s">
-        <v>436</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>112</v>
@@ -11228,7 +11533,7 @@
         <v>32</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
@@ -11239,14 +11544,14 @@
         <v>36</v>
       </c>
       <c r="P135" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q135" s="13" t="s">
         <v>38</v>
       </c>
       <c r="R135" s="13"/>
       <c r="S135" s="13" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="T135" s="5" t="s">
         <v>38</v>
@@ -11272,13 +11577,13 @@
         <v>26</v>
       </c>
       <c r="C136" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D136" s="5" t="s">
         <v>160</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>30</v>
@@ -11287,7 +11592,7 @@
         <v>32</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I136" s="6"/>
       <c r="J136" s="2" t="s">
@@ -11301,7 +11606,7 @@
         <v>45</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Q136" s="5" t="s">
         <v>176</v>
@@ -11312,14 +11617,22 @@
       <c r="S136" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T136" s="5"/>
+      <c r="T136" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U136" s="11">
         <v>46146</v>
       </c>
       <c r="V136" s="16"/>
-      <c r="W136" s="9"/>
-      <c r="X136" s="2"/>
-      <c r="Y136" s="2"/>
+      <c r="W136" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="X136" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y136" s="2" t="s">
+        <v>483</v>
+      </c>
       <c r="Z136" s="2"/>
     </row>
     <row r="137" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11330,13 +11643,13 @@
         <v>26</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D137" s="13" t="s">
         <v>160</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>30</v>
@@ -11345,7 +11658,7 @@
         <v>32</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I137" s="7"/>
       <c r="J137" s="3" t="s">
@@ -11359,7 +11672,7 @@
         <v>45</v>
       </c>
       <c r="P137" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Q137" s="13" t="s">
         <v>176</v>
@@ -11370,7 +11683,9 @@
       <c r="S137" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T137" s="13"/>
+      <c r="T137" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U137" s="20">
         <v>46249</v>
       </c>
@@ -11388,7 +11703,7 @@
         <v>26</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>83</v>
@@ -11406,7 +11721,7 @@
         <v>32</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
@@ -11420,7 +11735,9 @@
       <c r="Q138" s="5"/>
       <c r="R138" s="5"/>
       <c r="S138" s="5"/>
-      <c r="T138" s="5"/>
+      <c r="T138" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U138" s="11">
         <v>46311</v>
       </c>
@@ -11438,10 +11755,10 @@
         <v>26</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>112</v>
@@ -11456,10 +11773,10 @@
         <v>32</v>
       </c>
       <c r="I139" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="J139" s="3" t="s">
         <v>451</v>
-      </c>
-      <c r="J139" s="3" t="s">
-        <v>452</v>
       </c>
       <c r="K139" s="3"/>
       <c r="L139" s="3"/>
@@ -11469,7 +11786,7 @@
         <v>36</v>
       </c>
       <c r="P139" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q139" s="13" t="s">
         <v>38</v>
@@ -11480,7 +11797,9 @@
       <c r="S139" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="T139" s="13"/>
+      <c r="T139" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U139" s="20">
         <v>46305</v>
       </c>
@@ -11502,10 +11821,10 @@
         <v>26</v>
       </c>
       <c r="C140" s="9" t="s">
+        <v>418</v>
+      </c>
+      <c r="D140" s="5" t="s">
         <v>419</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>420</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>112</v>
@@ -11520,7 +11839,7 @@
         <v>32</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
@@ -11531,12 +11850,14 @@
         <v>45</v>
       </c>
       <c r="P140" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q140" s="5"/>
       <c r="R140" s="5"/>
       <c r="S140" s="5"/>
-      <c r="T140" s="5"/>
+      <c r="T140" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U140" s="11">
         <v>46305</v>
       </c>
@@ -11554,10 +11875,10 @@
         <v>26</v>
       </c>
       <c r="C141" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="D141" s="13" t="s">
         <v>419</v>
-      </c>
-      <c r="D141" s="13" t="s">
-        <v>420</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>112</v>
@@ -11572,7 +11893,7 @@
         <v>32</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
@@ -11583,12 +11904,14 @@
         <v>45</v>
       </c>
       <c r="P141" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q141" s="13"/>
       <c r="R141" s="13"/>
       <c r="S141" s="13"/>
-      <c r="T141" s="13"/>
+      <c r="T141" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U141" s="20">
         <v>46305</v>
       </c>
@@ -11606,7 +11929,7 @@
         <v>26</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>83</v>
@@ -11624,7 +11947,7 @@
         <v>32</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
@@ -11638,7 +11961,9 @@
       <c r="Q142" s="5"/>
       <c r="R142" s="5"/>
       <c r="S142" s="5"/>
-      <c r="T142" s="5"/>
+      <c r="T142" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U142" s="11">
         <v>46411</v>
       </c>
@@ -11656,10 +11981,10 @@
         <v>26</v>
       </c>
       <c r="C143" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D143" s="13" t="s">
         <v>456</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>457</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>112</v>
@@ -11674,7 +11999,7 @@
         <v>32</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
@@ -11685,12 +12010,14 @@
         <v>45</v>
       </c>
       <c r="P143" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q143" s="13"/>
       <c r="R143" s="13"/>
       <c r="S143" s="13"/>
-      <c r="T143" s="13"/>
+      <c r="T143" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U143" s="20">
         <v>46351</v>
       </c>
@@ -11708,10 +12035,10 @@
         <v>26</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>112</v>
@@ -11723,10 +12050,10 @@
         <v>387</v>
       </c>
       <c r="H144" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="I144" s="6" t="s">
         <v>461</v>
-      </c>
-      <c r="I144" s="6" t="s">
-        <v>462</v>
       </c>
       <c r="J144" s="2"/>
       <c r="K144" s="2"/>
@@ -11737,7 +12064,7 @@
         <v>45</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q144" s="5" t="s">
         <v>176</v>
@@ -11748,7 +12075,9 @@
       <c r="S144" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T144" s="5"/>
+      <c r="T144" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U144" s="11">
         <v>46147</v>
       </c>
@@ -11766,10 +12095,10 @@
         <v>26</v>
       </c>
       <c r="C145" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D145" s="13" t="s">
         <v>456</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>457</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>112</v>
@@ -11784,7 +12113,7 @@
         <v>32</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
@@ -11795,12 +12124,14 @@
         <v>45</v>
       </c>
       <c r="P145" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q145" s="13"/>
       <c r="R145" s="13"/>
       <c r="S145" s="13"/>
-      <c r="T145" s="13"/>
+      <c r="T145" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U145" s="20">
         <v>46147</v>
       </c>
@@ -11821,7 +12152,7 @@
         <v>401</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>112</v>
@@ -11836,7 +12167,7 @@
         <v>32</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
@@ -11847,12 +12178,14 @@
         <v>45</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q146" s="5"/>
       <c r="R146" s="5"/>
       <c r="S146" s="5"/>
-      <c r="T146" s="5"/>
+      <c r="T146" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U146" s="11">
         <v>46351</v>
       </c>
@@ -11870,10 +12203,10 @@
         <v>26</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>112</v>
@@ -11888,7 +12221,7 @@
         <v>32</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
@@ -11899,12 +12232,14 @@
         <v>45</v>
       </c>
       <c r="P147" s="7" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q147" s="13"/>
       <c r="R147" s="13"/>
       <c r="S147" s="13"/>
-      <c r="T147" s="13"/>
+      <c r="T147" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U147" s="20">
         <v>46253</v>
       </c>
@@ -11922,10 +12257,10 @@
         <v>26</v>
       </c>
       <c r="C148" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="D148" s="5" t="s">
         <v>468</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>469</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>112</v>
@@ -11934,13 +12269,13 @@
         <v>30</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H148" s="6">
         <v>46095</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>377</v>
@@ -11953,14 +12288,14 @@
         <v>36</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q148" s="5" t="s">
         <v>38</v>
       </c>
       <c r="R148" s="5"/>
       <c r="S148" s="5" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="T148" s="5" t="s">
         <v>38</v>
@@ -11989,7 +12324,7 @@
         <v>363</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>112</v>
@@ -11998,13 +12333,13 @@
         <v>30</v>
       </c>
       <c r="G149" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="H149" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="I149" s="7" t="s">
         <v>476</v>
-      </c>
-      <c r="I149" s="7" t="s">
-        <v>477</v>
       </c>
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
@@ -12015,7 +12350,7 @@
         <v>45</v>
       </c>
       <c r="P149" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Q149" s="13" t="s">
         <v>176</v>
@@ -12026,7 +12361,9 @@
       <c r="S149" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T149" s="13"/>
+      <c r="T149" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U149" s="20">
         <v>46039</v>
       </c>
@@ -12044,7 +12381,7 @@
         <v>26</v>
       </c>
       <c r="C150" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D150" s="13" t="s">
         <v>83</v>
@@ -12062,7 +12399,7 @@
         <v>32</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
@@ -12076,7 +12413,9 @@
       <c r="Q150" s="13"/>
       <c r="R150" s="13"/>
       <c r="S150" s="13"/>
-      <c r="T150" s="13"/>
+      <c r="T150" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U150" s="20">
         <v>46341</v>
       </c>
@@ -12094,13 +12433,13 @@
         <v>164</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>160</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>30</v>
@@ -12109,7 +12448,7 @@
         <v>32</v>
       </c>
       <c r="H151" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I151" s="6"/>
       <c r="J151" s="2" t="s">
@@ -12123,7 +12462,7 @@
         <v>45</v>
       </c>
       <c r="P151" s="6" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Q151" s="5" t="s">
         <v>176</v>
@@ -12134,7 +12473,9 @@
       <c r="S151" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="T151" s="5"/>
+      <c r="T151" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U151" s="11">
         <v>46176</v>
       </c>
@@ -12152,13 +12493,13 @@
         <v>164</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D152" s="13" t="s">
         <v>160</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>30</v>
@@ -12167,7 +12508,7 @@
         <v>32</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="I152" s="7"/>
       <c r="J152" s="3" t="s">
@@ -12181,7 +12522,7 @@
         <v>45</v>
       </c>
       <c r="P152" s="7" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Q152" s="13" t="s">
         <v>176</v>
@@ -12192,7 +12533,9 @@
       <c r="S152" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T152" s="13"/>
+      <c r="T152" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U152" s="20">
         <v>46216</v>
       </c>
@@ -12213,7 +12556,7 @@
         <v>401</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E153" s="6" t="s">
         <v>112</v>
@@ -12228,7 +12571,7 @@
         <v>32</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J153" s="2"/>
       <c r="K153" s="2"/>
@@ -12239,12 +12582,14 @@
         <v>45</v>
       </c>
       <c r="P153" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q153" s="5"/>
       <c r="R153" s="5"/>
       <c r="S153" s="5"/>
-      <c r="T153" s="5"/>
+      <c r="T153" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U153" s="11">
         <v>46264</v>
       </c>
@@ -12265,7 +12610,7 @@
         <v>401</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>112</v>
@@ -12280,7 +12625,7 @@
         <v>32</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
@@ -12291,12 +12636,14 @@
         <v>45</v>
       </c>
       <c r="P154" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q154" s="13"/>
       <c r="R154" s="13"/>
       <c r="S154" s="13"/>
-      <c r="T154" s="13"/>
+      <c r="T154" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U154" s="20"/>
       <c r="V154" s="16"/>
       <c r="W154" s="9"/>
@@ -12312,10 +12659,10 @@
         <v>164</v>
       </c>
       <c r="C155" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="D155" s="5" t="s">
         <v>456</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>457</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>112</v>
@@ -12330,7 +12677,7 @@
         <v>32</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
@@ -12341,12 +12688,14 @@
         <v>45</v>
       </c>
       <c r="P155" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q155" s="5"/>
       <c r="R155" s="5"/>
       <c r="S155" s="5"/>
-      <c r="T155" s="5"/>
+      <c r="T155" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U155" s="11">
         <v>46241</v>
       </c>
@@ -12364,10 +12713,10 @@
         <v>164</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="E156" s="7" t="s">
         <v>112</v>
@@ -12379,10 +12728,10 @@
         <v>387</v>
       </c>
       <c r="H156" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="I156" s="7" t="s">
         <v>461</v>
-      </c>
-      <c r="I156" s="7" t="s">
-        <v>462</v>
       </c>
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
@@ -12393,7 +12742,7 @@
         <v>45</v>
       </c>
       <c r="P156" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="Q156" s="13" t="s">
         <v>176</v>
@@ -12404,7 +12753,9 @@
       <c r="S156" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T156" s="13"/>
+      <c r="T156" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U156" s="20">
         <v>46148</v>
       </c>
@@ -12412,8 +12763,12 @@
       <c r="W156" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="X156" s="3"/>
-      <c r="Y156" s="3"/>
+      <c r="X156" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="Y156" s="3" t="s">
+        <v>483</v>
+      </c>
       <c r="Z156" s="3"/>
     </row>
     <row r="157" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -12424,10 +12779,10 @@
         <v>164</v>
       </c>
       <c r="C157" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="D157" s="5" t="s">
         <v>456</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>457</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>112</v>
@@ -12442,7 +12797,7 @@
         <v>32</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
@@ -12453,12 +12808,14 @@
         <v>45</v>
       </c>
       <c r="P157" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q157" s="5"/>
       <c r="R157" s="5"/>
       <c r="S157" s="5"/>
-      <c r="T157" s="5"/>
+      <c r="T157" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U157" s="11">
         <v>46148</v>
       </c>
@@ -12479,7 +12836,7 @@
         <v>401</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>112</v>
@@ -12494,7 +12851,7 @@
         <v>32</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
@@ -12505,7 +12862,7 @@
         <v>45</v>
       </c>
       <c r="P158" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q158" s="13"/>
       <c r="R158" s="13"/>
@@ -12530,10 +12887,10 @@
         <v>164</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>112</v>
@@ -12548,7 +12905,7 @@
         <v>32</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
@@ -12559,12 +12916,14 @@
         <v>45</v>
       </c>
       <c r="P159" s="6" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q159" s="5"/>
       <c r="R159" s="5"/>
       <c r="S159" s="5"/>
-      <c r="T159" s="5"/>
+      <c r="T159" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U159" s="11">
         <v>46253</v>
       </c>
@@ -12585,7 +12944,7 @@
         <v>363</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>112</v>
@@ -12594,13 +12953,13 @@
         <v>30</v>
       </c>
       <c r="G160" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="H160" s="7" t="s">
         <v>475</v>
       </c>
-      <c r="H160" s="7" t="s">
+      <c r="I160" s="7" t="s">
         <v>476</v>
-      </c>
-      <c r="I160" s="7" t="s">
-        <v>477</v>
       </c>
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
@@ -12611,7 +12970,7 @@
         <v>45</v>
       </c>
       <c r="P160" s="7" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Q160" s="13" t="s">
         <v>176</v>
@@ -12622,7 +12981,9 @@
       <c r="S160" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="T160" s="13"/>
+      <c r="T160" s="5" t="s">
+        <v>112</v>
+      </c>
       <c r="U160" s="20">
         <v>46133</v>
       </c>
@@ -12638,7 +12999,14 @@
       <c r="Y160" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="Z160" s="3"/>
+      <c r="Z160" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="161" spans="24:24" x14ac:dyDescent="0.3">
+      <c r="X161">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:Z160" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/KAFD00330_Delivery_Master.xlsx
+++ b/KAFD00330_Delivery_Master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbcmsa-my.sharepoint.com/personal/mohammed_b_sbcm-sa_com/Documents/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://macest-my.sharepoint.com/personal/aqadoumi_mac-est_com/Documents/Desktop/Files/RO Plant and Collection Ground Water System/7.0 Procurement/github_site/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_B464D923760B716A87BF040CED6C1C7D597CE204" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC4D7080-F0AC-4874-B26A-E8C7FD31F239}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_B464D923760B716A87BF040CED6C1C7D597CE204" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC24A43C-359B-44C4-91BD-1A43C1CE43F7}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Delivery" sheetId="1" r:id="rId1"/>
@@ -1836,6 +1836,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2127,37 +2131,37 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z161"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="7" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.21875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.54296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.90625" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.1796875" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34" style="8" customWidth="1"/>
-    <col min="10" max="10" width="8.44140625" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="11.88671875" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.109375" style="8" customWidth="1"/>
-    <col min="15" max="15" width="13.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="31.33203125" customWidth="1"/>
-    <col min="17" max="17" width="8.21875" style="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.21875" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="18.6640625" style="14" customWidth="1"/>
-    <col min="21" max="21" width="32.109375" style="21" customWidth="1"/>
-    <col min="22" max="22" width="30.21875" style="17" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="22.77734375" style="12" customWidth="1"/>
-    <col min="24" max="24" width="11.88671875" customWidth="1"/>
-    <col min="25" max="25" width="11.5546875" customWidth="1"/>
-    <col min="26" max="26" width="25.88671875" style="23" customWidth="1"/>
-    <col min="27" max="28" width="8.88671875" customWidth="1"/>
+    <col min="10" max="10" width="8.453125" customWidth="1"/>
+    <col min="11" max="11" width="11.90625" customWidth="1"/>
+    <col min="12" max="12" width="10.08984375" customWidth="1"/>
+    <col min="13" max="13" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.08984375" style="8" customWidth="1"/>
+    <col min="15" max="15" width="13.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="31.36328125" customWidth="1"/>
+    <col min="17" max="17" width="8.1796875" style="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.1796875" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="18.6328125" style="14" customWidth="1"/>
+    <col min="21" max="21" width="32.08984375" style="21" customWidth="1"/>
+    <col min="22" max="22" width="30.1796875" style="17" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.81640625" style="12" customWidth="1"/>
+    <col min="24" max="24" width="11.90625" customWidth="1"/>
+    <col min="25" max="25" width="11.54296875" customWidth="1"/>
+    <col min="26" max="26" width="25.90625" style="23" customWidth="1"/>
+    <col min="27" max="28" width="8.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -2187,7 +2191,7 @@
       <c r="Y1" s="34"/>
       <c r="Z1" s="37"/>
     </row>
-    <row r="2" spans="1:26" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:26" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -2267,7 +2271,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="19">
         <v>1</v>
       </c>
@@ -2333,7 +2337,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="19">
         <v>2</v>
       </c>
@@ -2411,7 +2415,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="19">
         <v>3</v>
       </c>
@@ -2475,7 +2479,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="19">
         <v>4</v>
       </c>
@@ -2541,7 +2545,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="19">
         <v>5</v>
       </c>
@@ -2603,7 +2607,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="19">
         <v>6</v>
       </c>
@@ -2669,7 +2673,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="19">
         <v>7</v>
       </c>
@@ -2735,7 +2739,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="19">
         <v>8</v>
       </c>
@@ -2801,7 +2805,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="19">
         <v>9</v>
       </c>
@@ -2867,7 +2871,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="19">
         <v>10</v>
       </c>
@@ -2931,7 +2935,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="19">
         <v>11</v>
       </c>
@@ -2995,7 +2999,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="19">
         <v>12</v>
       </c>
@@ -3059,7 +3063,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="19">
         <v>13</v>
       </c>
@@ -3123,7 +3127,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="19">
         <v>14</v>
       </c>
@@ -3187,7 +3191,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="19">
         <v>15</v>
       </c>
@@ -3251,7 +3255,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="19">
         <v>16</v>
       </c>
@@ -3317,7 +3321,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="19">
         <v>17</v>
       </c>
@@ -3383,7 +3387,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="19">
         <v>18</v>
       </c>
@@ -3447,7 +3451,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="19">
         <v>19</v>
       </c>
@@ -3511,7 +3515,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="19">
         <v>20</v>
       </c>
@@ -3583,7 +3587,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="19">
         <v>21</v>
       </c>
@@ -3655,7 +3659,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="19">
         <v>22</v>
       </c>
@@ -3727,7 +3731,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="19">
         <v>23</v>
       </c>
@@ -3799,7 +3803,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="19">
         <v>24</v>
       </c>
@@ -3869,7 +3873,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="19">
         <v>25</v>
       </c>
@@ -3933,7 +3937,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="19">
         <v>26</v>
       </c>
@@ -4005,7 +4009,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="19">
         <v>27</v>
       </c>
@@ -4065,7 +4069,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="19">
         <v>28</v>
       </c>
@@ -4129,7 +4133,7 @@
       </c>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="19">
         <v>29</v>
       </c>
@@ -4199,7 +4203,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="19">
         <v>30</v>
       </c>
@@ -4259,7 +4263,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="19">
         <v>31</v>
       </c>
@@ -4323,7 +4327,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="19">
         <v>32</v>
       </c>
@@ -4395,7 +4399,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="19">
         <v>33</v>
       </c>
@@ -4469,7 +4473,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="19">
         <v>34</v>
       </c>
@@ -4543,7 +4547,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="19">
         <v>35</v>
       </c>
@@ -4615,7 +4619,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="19">
         <v>36</v>
       </c>
@@ -4685,7 +4689,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="19">
         <v>37</v>
       </c>
@@ -4757,7 +4761,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="19">
         <v>39</v>
       </c>
@@ -4829,7 +4833,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="19">
         <v>40</v>
       </c>
@@ -4901,7 +4905,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="19">
         <v>41</v>
       </c>
@@ -4959,7 +4963,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="19">
         <v>42</v>
       </c>
@@ -5017,7 +5021,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="19">
         <v>43</v>
       </c>
@@ -5085,7 +5089,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="19">
         <v>44</v>
       </c>
@@ -5143,7 +5147,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="19">
         <v>45</v>
       </c>
@@ -5211,7 +5215,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="19">
         <v>46</v>
       </c>
@@ -5281,7 +5285,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="19">
         <v>47</v>
       </c>
@@ -5349,7 +5353,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="19">
         <v>48</v>
       </c>
@@ -5417,7 +5421,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="19">
         <v>49</v>
       </c>
@@ -5487,7 +5491,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="19">
         <v>50</v>
       </c>
@@ -5557,7 +5561,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="19">
         <v>51</v>
       </c>
@@ -5627,7 +5631,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="19">
         <v>52</v>
       </c>
@@ -5697,7 +5701,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="19">
         <v>53</v>
       </c>
@@ -5767,7 +5771,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="19">
         <v>54</v>
       </c>
@@ -5835,7 +5839,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="19">
         <v>55</v>
       </c>
@@ -5901,7 +5905,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="19">
         <v>56</v>
       </c>
@@ -5965,7 +5969,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="19">
         <v>57</v>
       </c>
@@ -6031,7 +6035,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="19">
         <v>58</v>
       </c>
@@ -6097,7 +6101,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="19">
         <v>59</v>
       </c>
@@ -6165,7 +6169,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="19">
         <v>60</v>
       </c>
@@ -6233,7 +6237,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="19">
         <v>61</v>
       </c>
@@ -6301,7 +6305,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="19">
         <v>62</v>
       </c>
@@ -6371,7 +6375,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="64" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="19">
         <v>63</v>
       </c>
@@ -6431,7 +6435,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="19">
         <v>64</v>
       </c>
@@ -6493,7 +6497,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="19">
         <v>65</v>
       </c>
@@ -6549,7 +6553,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="19">
         <v>66</v>
       </c>
@@ -6617,7 +6621,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="19">
         <v>67</v>
       </c>
@@ -6675,7 +6679,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="19">
         <v>68</v>
       </c>
@@ -6743,7 +6747,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="19">
         <v>69</v>
       </c>
@@ -6811,7 +6815,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="19">
         <v>70</v>
       </c>
@@ -6879,7 +6883,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="19">
         <v>71</v>
       </c>
@@ -6941,7 +6945,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="19">
         <v>72</v>
       </c>
@@ -7009,7 +7013,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="19">
         <v>73</v>
       </c>
@@ -7075,7 +7079,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="19">
         <v>74</v>
       </c>
@@ -7143,7 +7147,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="19">
         <v>75</v>
       </c>
@@ -7209,7 +7213,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="19">
         <v>76</v>
       </c>
@@ -7281,7 +7285,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="19">
         <v>77</v>
       </c>
@@ -7347,7 +7351,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="19">
         <v>78</v>
       </c>
@@ -7413,7 +7417,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="19">
         <v>79</v>
       </c>
@@ -7481,7 +7485,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="19">
         <v>80</v>
       </c>
@@ -7549,7 +7553,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="19">
         <v>81</v>
       </c>
@@ -7617,7 +7621,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="19">
         <v>82</v>
       </c>
@@ -7685,7 +7689,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="19">
         <v>83</v>
       </c>
@@ -7753,7 +7757,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="19">
         <v>84</v>
       </c>
@@ -7821,7 +7825,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="19">
         <v>85</v>
       </c>
@@ -7889,7 +7893,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="19">
         <v>86</v>
       </c>
@@ -7957,7 +7961,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="19">
         <v>87</v>
       </c>
@@ -8025,7 +8029,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="19">
         <v>88</v>
       </c>
@@ -8095,7 +8099,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="19">
         <v>89</v>
       </c>
@@ -8165,7 +8169,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="19">
         <v>90</v>
       </c>
@@ -8235,7 +8239,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
-    <row r="92" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="19">
         <v>91</v>
       </c>
@@ -8305,7 +8309,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="19">
         <v>92</v>
       </c>
@@ -8373,7 +8377,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="19">
         <v>93</v>
       </c>
@@ -8441,7 +8445,7 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="19">
         <v>94</v>
       </c>
@@ -8509,7 +8513,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="19">
         <v>95</v>
       </c>
@@ -8577,7 +8581,7 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="19">
         <v>96</v>
       </c>
@@ -8645,7 +8649,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" spans="1:26" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:26" ht="79.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="19">
         <v>97</v>
       </c>
@@ -8711,7 +8715,7 @@
       </c>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="19">
         <v>98</v>
       </c>
@@ -8777,7 +8781,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="19">
         <v>99</v>
       </c>
@@ -8843,7 +8847,7 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="19">
         <v>100</v>
       </c>
@@ -8909,7 +8913,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="19">
         <v>101</v>
       </c>
@@ -8975,7 +8979,7 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="19">
         <v>102</v>
       </c>
@@ -9043,7 +9047,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="19">
         <v>103</v>
       </c>
@@ -9115,7 +9119,7 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
-    <row r="105" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="19">
         <v>104</v>
       </c>
@@ -9187,7 +9191,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="19">
         <v>105</v>
       </c>
@@ -9257,7 +9261,7 @@
       <c r="Y106" s="2"/>
       <c r="Z106" s="2"/>
     </row>
-    <row r="107" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="19">
         <v>106</v>
       </c>
@@ -9329,7 +9333,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="19">
         <v>107</v>
       </c>
@@ -9399,7 +9403,7 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="19">
         <v>108</v>
       </c>
@@ -9469,7 +9473,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="19">
         <v>109</v>
       </c>
@@ -9541,7 +9545,7 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
-    <row r="111" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="19">
         <v>110</v>
       </c>
@@ -9611,7 +9615,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="19">
         <v>111</v>
       </c>
@@ -9681,7 +9685,7 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
     </row>
-    <row r="113" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="19">
         <v>112</v>
       </c>
@@ -9745,7 +9749,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="19">
         <v>113</v>
       </c>
@@ -9811,7 +9815,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="19">
         <v>114</v>
       </c>
@@ -9877,7 +9881,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="19">
         <v>115</v>
       </c>
@@ -9941,7 +9945,7 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="19">
         <v>116</v>
       </c>
@@ -10007,7 +10011,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="19">
         <v>117</v>
       </c>
@@ -10063,7 +10067,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="19">
         <v>118</v>
       </c>
@@ -10123,7 +10127,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="19">
         <v>119</v>
       </c>
@@ -10183,7 +10187,7 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="19">
         <v>120</v>
       </c>
@@ -10241,7 +10245,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="19">
         <v>121</v>
       </c>
@@ -10299,7 +10303,7 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" s="19">
         <v>122</v>
       </c>
@@ -10357,7 +10361,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="19">
         <v>123</v>
       </c>
@@ -10407,7 +10411,7 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="19">
         <v>124</v>
       </c>
@@ -10469,7 +10473,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="19">
         <v>125</v>
       </c>
@@ -10531,7 +10535,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="19">
         <v>126</v>
       </c>
@@ -10593,7 +10597,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="19">
         <v>127</v>
       </c>
@@ -10655,7 +10659,7 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="19">
         <v>128</v>
       </c>
@@ -10713,7 +10717,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="19">
         <v>129</v>
       </c>
@@ -10775,7 +10779,7 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
     </row>
-    <row r="131" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="19">
         <v>130</v>
       </c>
@@ -10837,7 +10841,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="19">
         <v>131</v>
       </c>
@@ -10905,7 +10909,7 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
     </row>
-    <row r="133" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="19">
         <v>132</v>
       </c>
@@ -10969,7 +10973,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="19">
         <v>133</v>
       </c>
@@ -11037,7 +11041,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="19">
         <v>134</v>
       </c>
@@ -11105,7 +11109,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="19">
         <v>135</v>
       </c>
@@ -11177,7 +11181,7 @@
       </c>
       <c r="Z136" s="2"/>
     </row>
-    <row r="137" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="19">
         <v>136</v>
       </c>
@@ -11249,7 +11253,7 @@
       </c>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="19">
         <v>137</v>
       </c>
@@ -11307,7 +11311,7 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
     </row>
-    <row r="139" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="19">
         <v>138</v>
       </c>
@@ -11377,7 +11381,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="19">
         <v>139</v>
       </c>
@@ -11435,7 +11439,7 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
     </row>
-    <row r="141" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="19">
         <v>140</v>
       </c>
@@ -11497,7 +11501,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="19">
         <v>141</v>
       </c>
@@ -11553,7 +11557,7 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
     </row>
-    <row r="143" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="19">
         <v>142</v>
       </c>
@@ -11611,7 +11615,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="19">
         <v>143</v>
       </c>
@@ -11675,7 +11679,7 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
     </row>
-    <row r="145" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="19">
         <v>144</v>
       </c>
@@ -11733,7 +11737,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="19">
         <v>145</v>
       </c>
@@ -11795,7 +11799,7 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="19">
         <v>146</v>
       </c>
@@ -11853,7 +11857,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A148" s="19">
         <v>147</v>
       </c>
@@ -11923,7 +11927,7 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A149" s="19">
         <v>148</v>
       </c>
@@ -11983,7 +11987,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A150" s="19">
         <v>150</v>
       </c>
@@ -12041,7 +12045,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="19">
         <v>151</v>
       </c>
@@ -12109,7 +12113,7 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A152" s="19">
         <v>152</v>
       </c>
@@ -12177,7 +12181,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="19">
         <v>157</v>
       </c>
@@ -12239,7 +12243,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A154" s="19">
         <v>158</v>
       </c>
@@ -12299,7 +12303,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="19">
         <v>159</v>
       </c>
@@ -12361,7 +12365,7 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
     </row>
-    <row r="156" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A156" s="19">
         <v>160</v>
       </c>
@@ -12431,7 +12435,7 @@
       </c>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="19">
         <v>161</v>
       </c>
@@ -12489,7 +12493,7 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A158" s="19">
         <v>162</v>
       </c>
@@ -12551,7 +12555,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="19">
         <v>164</v>
       </c>
@@ -12609,7 +12613,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="19">
         <v>165</v>
       </c>
@@ -12679,7 +12683,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="161" spans="24:24" x14ac:dyDescent="0.3">
+    <row r="161" spans="24:24" x14ac:dyDescent="0.35">
       <c r="X161">
         <v>1</v>
       </c>
@@ -12690,6 +12694,6 @@
     <mergeCell ref="A1:Z1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="8" scale="39" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/KAFD00330_Delivery_Master.xlsx
+++ b/KAFD00330_Delivery_Master.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://macest-my.sharepoint.com/personal/aqadoumi_mac-est_com/Documents/Desktop/Files/RO Plant and Collection Ground Water System/7.0 Procurement/github_site/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbcmsa-my.sharepoint.com/personal/mohammed_b_sbcm-sa_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_B464D923760B716A87BF040CED6C1C7D597CE204" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC24A43C-359B-44C4-91BD-1A43C1CE43F7}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="11_B464D923760B716A87BF040CED6C1C7D597CE204" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D82BE06-BFB7-4709-AF33-A51D86421432}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Delivery" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2621" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2631" uniqueCount="521">
   <si>
     <t>KAFD00330 — RO Plant: Material Delivery Master (edit here; sync to the report)</t>
   </si>
@@ -1430,9 +1430,6 @@
     <t>P01039</t>
   </si>
   <si>
-    <t>RO membranes</t>
-  </si>
-  <si>
     <t>KAFD-636-SBC-MEC-MAR-00012</t>
   </si>
   <si>
@@ -1620,6 +1617,18 @@
   </si>
   <si>
     <t>KAFD-636-SBC-ARC-MAR-00009</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MIR-00053</t>
+  </si>
+  <si>
+    <t>RO Skids</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MIR-00052</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-ARC-MAR-00019</t>
   </si>
 </sst>
 </file>
@@ -2131,37 +2140,37 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z161"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.1796875" style="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="33.54296875" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.90625" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.21875" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" style="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="34" style="8" customWidth="1"/>
-    <col min="10" max="10" width="8.453125" customWidth="1"/>
-    <col min="11" max="11" width="11.90625" customWidth="1"/>
-    <col min="12" max="12" width="10.08984375" customWidth="1"/>
-    <col min="13" max="13" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.08984375" style="8" customWidth="1"/>
-    <col min="15" max="15" width="13.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="31.36328125" customWidth="1"/>
-    <col min="17" max="17" width="8.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="18.6328125" style="14" customWidth="1"/>
-    <col min="21" max="21" width="32.08984375" style="21" customWidth="1"/>
-    <col min="22" max="22" width="30.1796875" style="17" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="22.81640625" style="12" customWidth="1"/>
-    <col min="24" max="24" width="11.90625" customWidth="1"/>
-    <col min="25" max="25" width="11.54296875" customWidth="1"/>
-    <col min="26" max="26" width="25.90625" style="23" customWidth="1"/>
-    <col min="27" max="28" width="8.90625" customWidth="1"/>
+    <col min="10" max="10" width="8.44140625" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="11.88671875" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.109375" style="8" customWidth="1"/>
+    <col min="15" max="15" width="13.109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="31.33203125" customWidth="1"/>
+    <col min="17" max="17" width="8.21875" style="14" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.21875" style="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="18.6640625" style="14" customWidth="1"/>
+    <col min="21" max="21" width="32.109375" style="21" customWidth="1"/>
+    <col min="22" max="22" width="30.21875" style="17" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.77734375" style="12" customWidth="1"/>
+    <col min="24" max="24" width="11.88671875" customWidth="1"/>
+    <col min="25" max="25" width="11.5546875" customWidth="1"/>
+    <col min="26" max="26" width="25.88671875" style="23" customWidth="1"/>
+    <col min="27" max="28" width="8.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -2191,7 +2200,7 @@
       <c r="Y1" s="34"/>
       <c r="Z1" s="37"/>
     </row>
-    <row r="2" spans="1:26" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:26" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -2271,7 +2280,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19">
         <v>1</v>
       </c>
@@ -2337,7 +2346,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19">
         <v>2</v>
       </c>
@@ -2415,7 +2424,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19">
         <v>3</v>
       </c>
@@ -2479,7 +2488,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19">
         <v>4</v>
       </c>
@@ -2545,7 +2554,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
         <v>5</v>
       </c>
@@ -2607,7 +2616,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="19">
         <v>6</v>
       </c>
@@ -2673,7 +2682,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="19">
         <v>7</v>
       </c>
@@ -2739,7 +2748,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19">
         <v>8</v>
       </c>
@@ -2805,7 +2814,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19">
         <v>9</v>
       </c>
@@ -2871,7 +2880,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19">
         <v>10</v>
       </c>
@@ -2935,7 +2944,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19">
         <v>11</v>
       </c>
@@ -2999,7 +3008,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19">
         <v>12</v>
       </c>
@@ -3063,7 +3072,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19">
         <v>13</v>
       </c>
@@ -3127,7 +3136,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19">
         <v>14</v>
       </c>
@@ -3191,7 +3200,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19">
         <v>15</v>
       </c>
@@ -3255,7 +3264,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19">
         <v>16</v>
       </c>
@@ -3321,7 +3330,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19">
         <v>17</v>
       </c>
@@ -3387,7 +3396,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19">
         <v>18</v>
       </c>
@@ -3451,7 +3460,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19">
         <v>19</v>
       </c>
@@ -3515,7 +3524,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19">
         <v>20</v>
       </c>
@@ -3587,7 +3596,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19">
         <v>21</v>
       </c>
@@ -3659,7 +3668,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19">
         <v>22</v>
       </c>
@@ -3731,7 +3740,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19">
         <v>23</v>
       </c>
@@ -3803,7 +3812,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="19">
         <v>24</v>
       </c>
@@ -3873,7 +3882,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="19">
         <v>25</v>
       </c>
@@ -3937,7 +3946,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19">
         <v>26</v>
       </c>
@@ -4009,7 +4018,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19">
         <v>27</v>
       </c>
@@ -4069,7 +4078,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19">
         <v>28</v>
       </c>
@@ -4133,7 +4142,7 @@
       </c>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19">
         <v>29</v>
       </c>
@@ -4203,7 +4212,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="19">
         <v>30</v>
       </c>
@@ -4263,7 +4272,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="19">
         <v>31</v>
       </c>
@@ -4327,7 +4336,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19">
         <v>32</v>
       </c>
@@ -4399,7 +4408,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
         <v>33</v>
       </c>
@@ -4473,7 +4482,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19">
         <v>34</v>
       </c>
@@ -4547,7 +4556,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
         <v>35</v>
       </c>
@@ -4619,7 +4628,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="38" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="19">
         <v>36</v>
       </c>
@@ -4689,7 +4698,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19">
         <v>37</v>
       </c>
@@ -4761,7 +4770,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19">
         <v>39</v>
       </c>
@@ -4833,7 +4842,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19">
         <v>40</v>
       </c>
@@ -4905,7 +4914,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19">
         <v>41</v>
       </c>
@@ -4963,7 +4972,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19">
         <v>42</v>
       </c>
@@ -5021,7 +5030,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19">
         <v>43</v>
       </c>
@@ -5089,7 +5098,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19">
         <v>44</v>
       </c>
@@ -5147,7 +5156,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19">
         <v>45</v>
       </c>
@@ -5215,7 +5224,7 @@
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
-    <row r="47" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="19">
         <v>46</v>
       </c>
@@ -5285,7 +5294,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19">
         <v>47</v>
       </c>
@@ -5353,7 +5362,7 @@
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19">
         <v>48</v>
       </c>
@@ -5421,7 +5430,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="19">
         <v>49</v>
       </c>
@@ -5491,7 +5500,7 @@
       <c r="Y50" s="2"/>
       <c r="Z50" s="2"/>
     </row>
-    <row r="51" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="19">
         <v>50</v>
       </c>
@@ -5561,7 +5570,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="19">
         <v>51</v>
       </c>
@@ -5631,7 +5640,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="19">
         <v>52</v>
       </c>
@@ -5701,7 +5710,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19">
         <v>53</v>
       </c>
@@ -5771,7 +5780,7 @@
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19">
         <v>54</v>
       </c>
@@ -5839,7 +5848,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19">
         <v>55</v>
       </c>
@@ -5905,7 +5914,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="19">
         <v>56</v>
       </c>
@@ -5969,7 +5978,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="19">
         <v>57</v>
       </c>
@@ -6035,7 +6044,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="19">
         <v>58</v>
       </c>
@@ -6101,7 +6110,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="19">
         <v>59</v>
       </c>
@@ -6169,7 +6178,7 @@
       <c r="Y60" s="2"/>
       <c r="Z60" s="2"/>
     </row>
-    <row r="61" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="19">
         <v>60</v>
       </c>
@@ -6237,7 +6246,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="19">
         <v>61</v>
       </c>
@@ -6305,7 +6314,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="19">
         <v>62</v>
       </c>
@@ -6375,7 +6384,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="64" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="19">
         <v>63</v>
       </c>
@@ -6435,7 +6444,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="19">
         <v>64</v>
       </c>
@@ -6497,7 +6506,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="19">
         <v>65</v>
       </c>
@@ -6553,7 +6562,7 @@
       <c r="Y66" s="2"/>
       <c r="Z66" s="2"/>
     </row>
-    <row r="67" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="19">
         <v>66</v>
       </c>
@@ -6621,7 +6630,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="19">
         <v>67</v>
       </c>
@@ -6679,7 +6688,7 @@
       <c r="Y68" s="2"/>
       <c r="Z68" s="2"/>
     </row>
-    <row r="69" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="19">
         <v>68</v>
       </c>
@@ -6747,7 +6756,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="19">
         <v>69</v>
       </c>
@@ -6815,7 +6824,7 @@
       <c r="Y70" s="2"/>
       <c r="Z70" s="2"/>
     </row>
-    <row r="71" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="19">
         <v>70</v>
       </c>
@@ -6883,7 +6892,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="19">
         <v>71</v>
       </c>
@@ -6945,7 +6954,7 @@
       <c r="Y72" s="2"/>
       <c r="Z72" s="2"/>
     </row>
-    <row r="73" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="19">
         <v>72</v>
       </c>
@@ -7013,7 +7022,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="19">
         <v>73</v>
       </c>
@@ -7079,7 +7088,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="19">
         <v>74</v>
       </c>
@@ -7147,7 +7156,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="19">
         <v>75</v>
       </c>
@@ -7213,7 +7222,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="19">
         <v>76</v>
       </c>
@@ -7285,7 +7294,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="78" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="19">
         <v>77</v>
       </c>
@@ -7351,7 +7360,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="19">
         <v>78</v>
       </c>
@@ -7417,7 +7426,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="19">
         <v>79</v>
       </c>
@@ -7485,7 +7494,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="19">
         <v>80</v>
       </c>
@@ -7553,7 +7562,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="19">
         <v>81</v>
       </c>
@@ -7621,7 +7630,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="19">
         <v>82</v>
       </c>
@@ -7689,7 +7698,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="19">
         <v>83</v>
       </c>
@@ -7757,7 +7766,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="19">
         <v>84</v>
       </c>
@@ -7825,7 +7834,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="19">
         <v>85</v>
       </c>
@@ -7893,7 +7902,7 @@
       <c r="Y86" s="2"/>
       <c r="Z86" s="2"/>
     </row>
-    <row r="87" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="19">
         <v>86</v>
       </c>
@@ -7961,7 +7970,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="19">
         <v>87</v>
       </c>
@@ -8029,7 +8038,7 @@
       <c r="Y88" s="2"/>
       <c r="Z88" s="2"/>
     </row>
-    <row r="89" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="19">
         <v>88</v>
       </c>
@@ -8096,10 +8105,14 @@
       <c r="X89" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Y89" s="3"/>
-      <c r="Z89" s="3"/>
-    </row>
-    <row r="90" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="Y89" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z89" s="3" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="19">
         <v>89</v>
       </c>
@@ -8169,7 +8182,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="19">
         <v>90</v>
       </c>
@@ -8239,7 +8252,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
-    <row r="92" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="19">
         <v>91</v>
       </c>
@@ -8309,7 +8322,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="19">
         <v>92</v>
       </c>
@@ -8377,7 +8390,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="19">
         <v>93</v>
       </c>
@@ -8445,7 +8458,7 @@
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
-    <row r="95" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="19">
         <v>94</v>
       </c>
@@ -8513,7 +8526,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="19">
         <v>95</v>
       </c>
@@ -8581,7 +8594,7 @@
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
-    <row r="97" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="19">
         <v>96</v>
       </c>
@@ -8649,7 +8662,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" spans="1:26" ht="79.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:26" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="19">
         <v>97</v>
       </c>
@@ -8715,7 +8728,7 @@
       </c>
       <c r="Z98" s="2"/>
     </row>
-    <row r="99" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="19">
         <v>98</v>
       </c>
@@ -8781,7 +8794,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="19">
         <v>99</v>
       </c>
@@ -8847,7 +8860,7 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="19">
         <v>100</v>
       </c>
@@ -8913,7 +8926,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="19">
         <v>101</v>
       </c>
@@ -8979,7 +8992,7 @@
       <c r="Y102" s="2"/>
       <c r="Z102" s="2"/>
     </row>
-    <row r="103" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="19">
         <v>102</v>
       </c>
@@ -9047,7 +9060,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="19">
         <v>103</v>
       </c>
@@ -9119,7 +9132,7 @@
       <c r="Y104" s="2"/>
       <c r="Z104" s="2"/>
     </row>
-    <row r="105" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="19">
         <v>104</v>
       </c>
@@ -9191,7 +9204,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="19">
         <v>105</v>
       </c>
@@ -9261,7 +9274,7 @@
       <c r="Y106" s="2"/>
       <c r="Z106" s="2"/>
     </row>
-    <row r="107" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="19">
         <v>106</v>
       </c>
@@ -9333,7 +9346,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="19">
         <v>107</v>
       </c>
@@ -9403,7 +9416,7 @@
       <c r="Y108" s="2"/>
       <c r="Z108" s="2"/>
     </row>
-    <row r="109" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="19">
         <v>108</v>
       </c>
@@ -9473,7 +9486,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="19">
         <v>109</v>
       </c>
@@ -9545,7 +9558,7 @@
       <c r="Y110" s="2"/>
       <c r="Z110" s="2"/>
     </row>
-    <row r="111" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="19">
         <v>110</v>
       </c>
@@ -9615,7 +9628,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="19">
         <v>111</v>
       </c>
@@ -9685,7 +9698,7 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
     </row>
-    <row r="113" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="19">
         <v>112</v>
       </c>
@@ -9749,7 +9762,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="19">
         <v>113</v>
       </c>
@@ -9815,7 +9828,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="19">
         <v>114</v>
       </c>
@@ -9881,7 +9894,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="19">
         <v>115</v>
       </c>
@@ -9945,7 +9958,7 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="19">
         <v>116</v>
       </c>
@@ -10011,7 +10024,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="19">
         <v>117</v>
       </c>
@@ -10067,7 +10080,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="19">
         <v>118</v>
       </c>
@@ -10127,7 +10140,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="19">
         <v>119</v>
       </c>
@@ -10187,7 +10200,7 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="19">
         <v>120</v>
       </c>
@@ -10245,7 +10258,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="19">
         <v>121</v>
       </c>
@@ -10303,7 +10316,7 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="19">
         <v>122</v>
       </c>
@@ -10361,7 +10374,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="19">
         <v>123</v>
       </c>
@@ -10411,7 +10424,7 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="19">
         <v>124</v>
       </c>
@@ -10473,7 +10486,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="19">
         <v>125</v>
       </c>
@@ -10535,7 +10548,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="19">
         <v>126</v>
       </c>
@@ -10597,7 +10610,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="19">
         <v>127</v>
       </c>
@@ -10659,7 +10672,7 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="19">
         <v>128</v>
       </c>
@@ -10717,7 +10730,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="19">
         <v>129</v>
       </c>
@@ -10779,7 +10792,7 @@
       <c r="Y130" s="2"/>
       <c r="Z130" s="2"/>
     </row>
-    <row r="131" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="19">
         <v>130</v>
       </c>
@@ -10841,7 +10854,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="19">
         <v>131</v>
       </c>
@@ -10867,13 +10880,13 @@
         <v>32</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>456</v>
+        <v>518</v>
       </c>
       <c r="J132" s="2"/>
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
       <c r="M132" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="N132" s="6" t="s">
         <v>35</v>
@@ -10882,7 +10895,7 @@
         <v>36</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q132" s="5" t="s">
         <v>39</v>
@@ -10903,13 +10916,19 @@
         <v>46286</v>
       </c>
       <c r="W132" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="X132" s="2"/>
-      <c r="Y132" s="2"/>
-      <c r="Z132" s="2"/>
-    </row>
-    <row r="133" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="X132" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y132" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z132" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="133" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="19">
         <v>132</v>
       </c>
@@ -10935,7 +10954,7 @@
         <v>32</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
@@ -10946,7 +10965,7 @@
         <v>36</v>
       </c>
       <c r="P133" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q133" s="13" t="s">
         <v>39</v>
@@ -10955,7 +10974,7 @@
         <v>38</v>
       </c>
       <c r="S133" s="13" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="T133" s="5" t="s">
         <v>39</v>
@@ -10969,11 +10988,17 @@
       <c r="W133" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="X133" s="3"/>
-      <c r="Y133" s="3"/>
-      <c r="Z133" s="3"/>
-    </row>
-    <row r="134" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="X133" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y133" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z133" s="3" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="134" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="19">
         <v>133</v>
       </c>
@@ -10999,13 +11024,13 @@
         <v>32</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
       <c r="M134" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="N134" s="6" t="s">
         <v>35</v>
@@ -11014,7 +11039,7 @@
         <v>36</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q134" s="5" t="s">
         <v>39</v>
@@ -11023,7 +11048,7 @@
         <v>39</v>
       </c>
       <c r="S134" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="T134" s="5" t="s">
         <v>39</v>
@@ -11041,7 +11066,7 @@
       <c r="Y134" s="2"/>
       <c r="Z134" s="2"/>
     </row>
-    <row r="135" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="19">
         <v>134</v>
       </c>
@@ -11067,13 +11092,13 @@
         <v>32</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="3"/>
       <c r="M135" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N135" s="6" t="s">
         <v>35</v>
@@ -11082,7 +11107,7 @@
         <v>36</v>
       </c>
       <c r="P135" s="7" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q135" s="13" t="s">
         <v>39</v>
@@ -11091,7 +11116,7 @@
         <v>39</v>
       </c>
       <c r="S135" s="13" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="T135" s="5" t="s">
         <v>39</v>
@@ -11109,7 +11134,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="19">
         <v>135</v>
       </c>
@@ -11117,10 +11142,10 @@
         <v>26</v>
       </c>
       <c r="C136" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="D136" s="5" t="s">
         <v>467</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>468</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>419</v>
@@ -11132,10 +11157,10 @@
         <v>32</v>
       </c>
       <c r="H136" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="I136" s="6" t="s">
         <v>469</v>
-      </c>
-      <c r="I136" s="6" t="s">
-        <v>470</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>384</v>
@@ -11143,7 +11168,7 @@
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
       <c r="M136" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N136" s="6" t="s">
         <v>35</v>
@@ -11152,7 +11177,7 @@
         <v>46</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q136" s="5" t="s">
         <v>38</v>
@@ -11181,7 +11206,7 @@
       </c>
       <c r="Z136" s="2"/>
     </row>
-    <row r="137" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="19">
         <v>136</v>
       </c>
@@ -11189,10 +11214,10 @@
         <v>26</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>419</v>
@@ -11204,10 +11229,10 @@
         <v>32</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="J137" s="3" t="s">
         <v>384</v>
@@ -11215,7 +11240,7 @@
       <c r="K137" s="3"/>
       <c r="L137" s="3"/>
       <c r="M137" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N137" s="6" t="s">
         <v>35</v>
@@ -11224,7 +11249,7 @@
         <v>46</v>
       </c>
       <c r="P137" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q137" s="13" t="s">
         <v>38</v>
@@ -11253,7 +11278,7 @@
       </c>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="19">
         <v>137</v>
       </c>
@@ -11261,7 +11286,7 @@
         <v>26</v>
       </c>
       <c r="C138" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D138" s="5" t="s">
         <v>87</v>
@@ -11279,7 +11304,7 @@
         <v>32</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J138" s="2"/>
       <c r="K138" s="2"/>
@@ -11290,7 +11315,7 @@
         <v>46</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Q138" s="29" t="s">
         <v>38</v>
@@ -11311,7 +11336,7 @@
       <c r="Y138" s="2"/>
       <c r="Z138" s="2"/>
     </row>
-    <row r="139" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="19">
         <v>138</v>
       </c>
@@ -11322,7 +11347,7 @@
         <v>433</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>93</v>
@@ -11337,15 +11362,15 @@
         <v>32</v>
       </c>
       <c r="I139" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="J139" s="3" t="s">
         <v>480</v>
-      </c>
-      <c r="J139" s="3" t="s">
-        <v>481</v>
       </c>
       <c r="K139" s="3"/>
       <c r="L139" s="3"/>
       <c r="M139" s="24" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N139" s="6" t="s">
         <v>35</v>
@@ -11381,7 +11406,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="19">
         <v>139</v>
       </c>
@@ -11407,7 +11432,7 @@
         <v>32</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
@@ -11439,7 +11464,7 @@
       <c r="Y140" s="2"/>
       <c r="Z140" s="2"/>
     </row>
-    <row r="141" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="19">
         <v>140</v>
       </c>
@@ -11501,7 +11526,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="19">
         <v>141</v>
       </c>
@@ -11509,7 +11534,7 @@
         <v>26</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D142" s="5" t="s">
         <v>87</v>
@@ -11527,7 +11552,7 @@
         <v>32</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
@@ -11557,7 +11582,7 @@
       <c r="Y142" s="2"/>
       <c r="Z142" s="2"/>
     </row>
-    <row r="143" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="19">
         <v>142</v>
       </c>
@@ -11565,10 +11590,10 @@
         <v>26</v>
       </c>
       <c r="C143" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="D143" s="13" t="s">
         <v>486</v>
-      </c>
-      <c r="D143" s="13" t="s">
-        <v>487</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>93</v>
@@ -11583,7 +11608,7 @@
         <v>32</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
@@ -11594,7 +11619,7 @@
         <v>46</v>
       </c>
       <c r="P143" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q143" s="29" t="s">
         <v>38</v>
@@ -11615,7 +11640,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="19">
         <v>143</v>
       </c>
@@ -11623,10 +11648,10 @@
         <v>26</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>93</v>
@@ -11638,16 +11663,16 @@
         <v>395</v>
       </c>
       <c r="H144" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="I144" s="6" t="s">
         <v>491</v>
-      </c>
-      <c r="I144" s="6" t="s">
-        <v>492</v>
       </c>
       <c r="J144" s="2"/>
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
       <c r="M144" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N144" s="6" t="s">
         <v>35</v>
@@ -11656,7 +11681,7 @@
         <v>46</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q144" s="5" t="s">
         <v>38</v>
@@ -11679,7 +11704,7 @@
       <c r="Y144" s="2"/>
       <c r="Z144" s="2"/>
     </row>
-    <row r="145" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="19">
         <v>144</v>
       </c>
@@ -11687,10 +11712,10 @@
         <v>26</v>
       </c>
       <c r="C145" s="10" t="s">
+        <v>485</v>
+      </c>
+      <c r="D145" s="13" t="s">
         <v>486</v>
-      </c>
-      <c r="D145" s="13" t="s">
-        <v>487</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>93</v>
@@ -11705,18 +11730,22 @@
         <v>32</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J145" s="3"/>
       <c r="K145" s="3"/>
       <c r="L145" s="3"/>
-      <c r="M145" s="3"/>
-      <c r="N145" s="6"/>
+      <c r="M145" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="N145" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="O145" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="P145" s="7" t="s">
-        <v>489</v>
+      <c r="P145" s="6" t="s">
+        <v>493</v>
       </c>
       <c r="Q145" s="29" t="s">
         <v>38</v>
@@ -11737,7 +11766,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="19">
         <v>145</v>
       </c>
@@ -11748,7 +11777,7 @@
         <v>409</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>93</v>
@@ -11763,13 +11792,13 @@
         <v>32</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
       <c r="M146" s="25" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N146" s="26" t="s">
         <v>63</v>
@@ -11778,7 +11807,7 @@
         <v>46</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q146" s="29" t="s">
         <v>38</v>
@@ -11799,7 +11828,7 @@
       <c r="Y146" s="2"/>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="19">
         <v>146</v>
       </c>
@@ -11807,7 +11836,7 @@
         <v>26</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D147" s="13" t="s">
         <v>422</v>
@@ -11825,7 +11854,7 @@
         <v>32</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
@@ -11857,7 +11886,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="19">
         <v>147</v>
       </c>
@@ -11865,10 +11894,10 @@
         <v>26</v>
       </c>
       <c r="C148" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="D148" s="5" t="s">
         <v>500</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>501</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>93</v>
@@ -11877,13 +11906,13 @@
         <v>30</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H148" s="28">
         <v>46095</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>384</v>
@@ -11891,7 +11920,7 @@
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
       <c r="M148" s="25" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N148" s="26" t="s">
         <v>35</v>
@@ -11900,16 +11929,16 @@
         <v>36</v>
       </c>
       <c r="P148" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q148" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R148" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S148" s="5" t="s">
         <v>505</v>
-      </c>
-      <c r="Q148" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R148" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S148" s="5" t="s">
-        <v>506</v>
       </c>
       <c r="T148" s="5" t="s">
         <v>39</v>
@@ -11927,7 +11956,7 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="19">
         <v>148</v>
       </c>
@@ -11938,7 +11967,7 @@
         <v>370</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>93</v>
@@ -11947,13 +11976,13 @@
         <v>30</v>
       </c>
       <c r="G149" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="H149" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="I149" s="7" t="s">
         <v>509</v>
-      </c>
-      <c r="I149" s="7" t="s">
-        <v>510</v>
       </c>
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
@@ -11964,7 +11993,7 @@
         <v>46</v>
       </c>
       <c r="P149" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="Q149" s="13" t="s">
         <v>38</v>
@@ -11987,7 +12016,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="19">
         <v>150</v>
       </c>
@@ -12013,7 +12042,7 @@
         <v>32</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J150" s="3"/>
       <c r="K150" s="3"/>
@@ -12024,7 +12053,7 @@
         <v>46</v>
       </c>
       <c r="P150" s="7" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="Q150" s="29" t="s">
         <v>38</v>
@@ -12045,7 +12074,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="19">
         <v>151</v>
       </c>
@@ -12053,10 +12082,10 @@
         <v>170</v>
       </c>
       <c r="C151" s="9" t="s">
+        <v>466</v>
+      </c>
+      <c r="D151" s="5" t="s">
         <v>467</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>468</v>
       </c>
       <c r="E151" s="6" t="s">
         <v>419</v>
@@ -12068,20 +12097,20 @@
         <v>32</v>
       </c>
       <c r="H151" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="I151" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="I151" s="6" t="s">
+      <c r="J151" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="J151" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="K151" s="6" t="s">
         <v>35</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="N151" s="6" t="s">
         <v>35</v>
@@ -12090,7 +12119,7 @@
         <v>46</v>
       </c>
       <c r="P151" s="6" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q151" s="5" t="s">
         <v>38</v>
@@ -12113,7 +12142,7 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="19">
         <v>152</v>
       </c>
@@ -12121,10 +12150,10 @@
         <v>170</v>
       </c>
       <c r="C152" s="10" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="D152" s="13" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>419</v>
@@ -12136,20 +12165,20 @@
         <v>32</v>
       </c>
       <c r="H152" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="I152" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="J152" s="3" t="s">
         <v>474</v>
-      </c>
-      <c r="J152" s="3" t="s">
-        <v>475</v>
       </c>
       <c r="K152" s="6" t="s">
         <v>35</v>
       </c>
       <c r="L152" s="3"/>
       <c r="M152" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="N152" s="6" t="s">
         <v>35</v>
@@ -12158,7 +12187,7 @@
         <v>46</v>
       </c>
       <c r="P152" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q152" s="13" t="s">
         <v>38</v>
@@ -12181,7 +12210,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="19">
         <v>157</v>
       </c>
@@ -12192,7 +12221,7 @@
         <v>409</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E153" s="6" t="s">
         <v>93</v>
@@ -12207,13 +12236,13 @@
         <v>32</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J153" s="2"/>
       <c r="K153" s="2"/>
       <c r="L153" s="2"/>
       <c r="M153" s="25" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N153" s="26" t="s">
         <v>63</v>
@@ -12222,7 +12251,7 @@
         <v>46</v>
       </c>
       <c r="P153" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q153" s="29" t="s">
         <v>38</v>
@@ -12243,7 +12272,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="19">
         <v>158</v>
       </c>
@@ -12254,7 +12283,7 @@
         <v>409</v>
       </c>
       <c r="D154" s="13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>93</v>
@@ -12269,13 +12298,13 @@
         <v>32</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J154" s="3"/>
       <c r="K154" s="3"/>
       <c r="L154" s="3"/>
       <c r="M154" s="25" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="N154" s="26" t="s">
         <v>63</v>
@@ -12284,7 +12313,7 @@
         <v>46</v>
       </c>
       <c r="P154" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q154" s="29" t="s">
         <v>38</v>
@@ -12303,7 +12332,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="19">
         <v>159</v>
       </c>
@@ -12311,10 +12340,10 @@
         <v>170</v>
       </c>
       <c r="C155" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="D155" s="5" t="s">
         <v>486</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>487</v>
       </c>
       <c r="E155" s="6" t="s">
         <v>93</v>
@@ -12329,13 +12358,13 @@
         <v>32</v>
       </c>
       <c r="I155" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
       <c r="L155" s="2"/>
       <c r="M155" s="25" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="N155" s="26" t="s">
         <v>35</v>
@@ -12344,7 +12373,7 @@
         <v>46</v>
       </c>
       <c r="P155" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q155" s="29" t="s">
         <v>38</v>
@@ -12365,7 +12394,7 @@
       <c r="Y155" s="2"/>
       <c r="Z155" s="2"/>
     </row>
-    <row r="156" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="19">
         <v>160</v>
       </c>
@@ -12373,10 +12402,10 @@
         <v>170</v>
       </c>
       <c r="C156" s="10" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="D156" s="13" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E156" s="7" t="s">
         <v>93</v>
@@ -12388,16 +12417,16 @@
         <v>395</v>
       </c>
       <c r="H156" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="I156" s="7" t="s">
         <v>491</v>
-      </c>
-      <c r="I156" s="7" t="s">
-        <v>492</v>
       </c>
       <c r="J156" s="3"/>
       <c r="K156" s="3"/>
       <c r="L156" s="3"/>
       <c r="M156" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N156" s="6" t="s">
         <v>35</v>
@@ -12406,7 +12435,7 @@
         <v>46</v>
       </c>
       <c r="P156" s="7" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q156" s="13" t="s">
         <v>38</v>
@@ -12435,7 +12464,7 @@
       </c>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="19">
         <v>161</v>
       </c>
@@ -12443,10 +12472,10 @@
         <v>170</v>
       </c>
       <c r="C157" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="D157" s="5" t="s">
         <v>486</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>487</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>93</v>
@@ -12461,7 +12490,7 @@
         <v>32</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
@@ -12472,7 +12501,7 @@
         <v>46</v>
       </c>
       <c r="P157" s="6" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q157" s="29" t="s">
         <v>38</v>
@@ -12493,7 +12522,7 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="19">
         <v>162</v>
       </c>
@@ -12504,7 +12533,7 @@
         <v>409</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>93</v>
@@ -12519,13 +12548,13 @@
         <v>32</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="3"/>
       <c r="M158" s="25" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="N158" s="26" t="s">
         <v>63</v>
@@ -12534,7 +12563,7 @@
         <v>46</v>
       </c>
       <c r="P158" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q158" s="29" t="s">
         <v>38</v>
@@ -12555,7 +12584,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="19">
         <v>164</v>
       </c>
@@ -12563,7 +12592,7 @@
         <v>170</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D159" s="5" t="s">
         <v>422</v>
@@ -12581,7 +12610,7 @@
         <v>32</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
@@ -12613,7 +12642,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160" spans="1:26" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="19">
         <v>165</v>
       </c>
@@ -12624,7 +12653,7 @@
         <v>370</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>93</v>
@@ -12633,13 +12662,13 @@
         <v>30</v>
       </c>
       <c r="G160" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="H160" s="7" t="s">
         <v>508</v>
       </c>
-      <c r="H160" s="7" t="s">
+      <c r="I160" s="7" t="s">
         <v>509</v>
-      </c>
-      <c r="I160" s="7" t="s">
-        <v>510</v>
       </c>
       <c r="J160" s="3"/>
       <c r="K160" s="3"/>
@@ -12650,7 +12679,7 @@
         <v>46</v>
       </c>
       <c r="P160" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="Q160" s="13" t="s">
         <v>38</v>
@@ -12683,7 +12712,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="161" spans="24:24" x14ac:dyDescent="0.35">
+    <row r="161" spans="24:24" x14ac:dyDescent="0.3">
       <c r="X161">
         <v>1</v>
       </c>
@@ -12694,6 +12723,6 @@
     <mergeCell ref="A1:Z1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="8" scale="37" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="39" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/KAFD00330_Delivery_Master.xlsx
+++ b/KAFD00330_Delivery_Master.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbcmsa-my.sharepoint.com/personal/mohammed_b_sbcm-sa_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="11_B464D923760B716A87BF040CED6C1C7D597CE204" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2D82BE06-BFB7-4709-AF33-A51D86421432}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="11_B464D923760B716A87BF040CED6C1C7D597CE204" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C2FAD4CD-5A99-4729-8A06-50585F35BDEE}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,15 +16,15 @@
     <sheet name="Delivery" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Delivery!$A$2:$Z$161</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Delivery!$A$1:$Z$160</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Delivery!$A$2:$Z$169</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Delivery!$A$1:$Z$168</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2631" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2771" uniqueCount="537">
   <si>
     <t>KAFD00330 — RO Plant: Material Delivery Master (edit here; sync to the report)</t>
   </si>
@@ -1436,22 +1436,13 @@
     <t>Veolia</t>
   </si>
   <si>
-    <t>Protech</t>
-  </si>
-  <si>
     <t>Spain</t>
   </si>
   <si>
-    <t>Sentrifugal Pumps</t>
-  </si>
-  <si>
     <t>KAFD-636-SBC-MEC-MAR-00007</t>
   </si>
   <si>
     <t>Hungary</t>
-  </si>
-  <si>
-    <t>Dosing Pumps</t>
   </si>
   <si>
     <t>KAFD-636-SBC-MEC-MAR-00009</t>
@@ -1622,13 +1613,70 @@
     <t>KAFD-636-SBC-MEC-MIR-00053</t>
   </si>
   <si>
-    <t>RO Skids</t>
-  </si>
-  <si>
     <t>KAFD-636-SBC-MEC-MIR-00052</t>
   </si>
   <si>
     <t>KAFD-636-SBC-ARC-MAR-00019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R.O skids </t>
+  </si>
+  <si>
+    <t xml:space="preserve">R.O Cartridge filters </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIP Cartridge filters </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosing skids </t>
+  </si>
+  <si>
+    <t>Static Mixers</t>
+  </si>
+  <si>
+    <t>Media for filters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High pressure pumps </t>
+  </si>
+  <si>
+    <t>Backwash pumps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIP pumps </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air blowers </t>
+  </si>
+  <si>
+    <t>CIP Heaters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dosing tanks </t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MAR-00006</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MAR-00025</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MAR-00034</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MAR-00047</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MAR-00074</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MAR-00067</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MIR-00054</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MIR-00055</t>
   </si>
 </sst>
 </file>
@@ -1668,7 +1716,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1683,12 +1731,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F6FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1719,7 +1761,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1798,9 +1840,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2139,7 +2178,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z161"/>
+  <dimension ref="A1:Z169"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7" style="14" bestFit="1" customWidth="1"/>
@@ -2171,34 +2210,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
-      <c r="M1" s="34"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="34"/>
-      <c r="Q1" s="33"/>
-      <c r="R1" s="33"/>
-      <c r="S1" s="33"/>
-      <c r="T1" s="33"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="36"/>
-      <c r="W1" s="32"/>
-      <c r="X1" s="34"/>
-      <c r="Y1" s="34"/>
-      <c r="Z1" s="37"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="33"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="35"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="33"/>
+      <c r="Y1" s="33"/>
+      <c r="Z1" s="36"/>
     </row>
     <row r="2" spans="1:26" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="18" t="s">
@@ -4772,7 +4811,7 @@
     </row>
     <row r="40" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="19">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>170</v>
@@ -4844,7 +4883,7 @@
     </row>
     <row r="41" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>170</v>
@@ -4916,7 +4955,7 @@
     </row>
     <row r="42" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>26</v>
@@ -4974,7 +5013,7 @@
     </row>
     <row r="43" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>26</v>
@@ -5032,7 +5071,7 @@
     </row>
     <row r="44" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="19">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>26</v>
@@ -5100,7 +5139,7 @@
     </row>
     <row r="45" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>26</v>
@@ -5158,7 +5197,7 @@
     </row>
     <row r="46" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="19">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>26</v>
@@ -5226,7 +5265,7 @@
     </row>
     <row r="47" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="19">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>26</v>
@@ -5296,7 +5335,7 @@
     </row>
     <row r="48" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>26</v>
@@ -5364,7 +5403,7 @@
     </row>
     <row r="49" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>26</v>
@@ -5432,7 +5471,7 @@
     </row>
     <row r="50" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="19">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>26</v>
@@ -5502,7 +5541,7 @@
     </row>
     <row r="51" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="19">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>26</v>
@@ -5572,7 +5611,7 @@
     </row>
     <row r="52" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="19">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>26</v>
@@ -5642,7 +5681,7 @@
     </row>
     <row r="53" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="19">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>26</v>
@@ -5712,7 +5751,7 @@
     </row>
     <row r="54" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>26</v>
@@ -5782,7 +5821,7 @@
     </row>
     <row r="55" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>26</v>
@@ -5850,7 +5889,7 @@
     </row>
     <row r="56" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>26</v>
@@ -5916,7 +5955,7 @@
     </row>
     <row r="57" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="19">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>26</v>
@@ -5980,7 +6019,7 @@
     </row>
     <row r="58" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="19">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>26</v>
@@ -6046,7 +6085,7 @@
     </row>
     <row r="59" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="19">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>26</v>
@@ -6112,7 +6151,7 @@
     </row>
     <row r="60" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="19">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>26</v>
@@ -6180,7 +6219,7 @@
     </row>
     <row r="61" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="19">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>26</v>
@@ -6248,7 +6287,7 @@
     </row>
     <row r="62" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="19">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>26</v>
@@ -6316,7 +6355,7 @@
     </row>
     <row r="63" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="19">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>26</v>
@@ -6386,7 +6425,7 @@
     </row>
     <row r="64" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="19">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>26</v>
@@ -6446,7 +6485,7 @@
     </row>
     <row r="65" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="19">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>26</v>
@@ -6508,7 +6547,7 @@
     </row>
     <row r="66" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="19">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>26</v>
@@ -6564,7 +6603,7 @@
     </row>
     <row r="67" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="19">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B67" s="7" t="s">
         <v>26</v>
@@ -6632,7 +6671,7 @@
     </row>
     <row r="68" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="19">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>26</v>
@@ -6690,7 +6729,7 @@
     </row>
     <row r="69" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="19">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B69" s="7" t="s">
         <v>26</v>
@@ -6758,7 +6797,7 @@
     </row>
     <row r="70" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="19">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>26</v>
@@ -6826,7 +6865,7 @@
     </row>
     <row r="71" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="19">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B71" s="7" t="s">
         <v>26</v>
@@ -6894,7 +6933,7 @@
     </row>
     <row r="72" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="19">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>26</v>
@@ -6956,7 +6995,7 @@
     </row>
     <row r="73" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="19">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>26</v>
@@ -7024,7 +7063,7 @@
     </row>
     <row r="74" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="19">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>26</v>
@@ -7090,7 +7129,7 @@
     </row>
     <row r="75" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="19">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B75" s="7" t="s">
         <v>26</v>
@@ -7158,7 +7197,7 @@
     </row>
     <row r="76" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="19">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>26</v>
@@ -7224,7 +7263,7 @@
     </row>
     <row r="77" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="19">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B77" s="7" t="s">
         <v>26</v>
@@ -7296,7 +7335,7 @@
     </row>
     <row r="78" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="19">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>26</v>
@@ -7362,7 +7401,7 @@
     </row>
     <row r="79" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="19">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B79" s="7" t="s">
         <v>26</v>
@@ -7428,7 +7467,7 @@
     </row>
     <row r="80" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="19">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>26</v>
@@ -7496,7 +7535,7 @@
     </row>
     <row r="81" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="19">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B81" s="7" t="s">
         <v>26</v>
@@ -7564,7 +7603,7 @@
     </row>
     <row r="82" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="19">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>26</v>
@@ -7632,7 +7671,7 @@
     </row>
     <row r="83" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="19">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B83" s="7" t="s">
         <v>26</v>
@@ -7700,7 +7739,7 @@
     </row>
     <row r="84" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="19">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>26</v>
@@ -7768,7 +7807,7 @@
     </row>
     <row r="85" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="19">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B85" s="7" t="s">
         <v>26</v>
@@ -7836,7 +7875,7 @@
     </row>
     <row r="86" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="19">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>26</v>
@@ -7904,7 +7943,7 @@
     </row>
     <row r="87" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="19">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B87" s="7" t="s">
         <v>26</v>
@@ -7972,7 +8011,7 @@
     </row>
     <row r="88" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="19">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>26</v>
@@ -8040,7 +8079,7 @@
     </row>
     <row r="89" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="19">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B89" s="7" t="s">
         <v>26</v>
@@ -8109,12 +8148,12 @@
         <v>51</v>
       </c>
       <c r="Z89" s="3" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="90" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="19">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>26</v>
@@ -8184,7 +8223,7 @@
     </row>
     <row r="91" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="19">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" s="7" t="s">
         <v>26</v>
@@ -8254,7 +8293,7 @@
     </row>
     <row r="92" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="19">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>26</v>
@@ -8324,7 +8363,7 @@
     </row>
     <row r="93" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="19">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>26</v>
@@ -8392,7 +8431,7 @@
     </row>
     <row r="94" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="19">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>26</v>
@@ -8460,7 +8499,7 @@
     </row>
     <row r="95" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="19">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B95" s="7" t="s">
         <v>26</v>
@@ -8528,7 +8567,7 @@
     </row>
     <row r="96" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="19">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>26</v>
@@ -8596,7 +8635,7 @@
     </row>
     <row r="97" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="19">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B97" s="7" t="s">
         <v>26</v>
@@ -8664,7 +8703,7 @@
     </row>
     <row r="98" spans="1:26" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="19">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>26</v>
@@ -8730,7 +8769,7 @@
     </row>
     <row r="99" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="19">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="10" t="s">
@@ -8796,7 +8835,7 @@
     </row>
     <row r="100" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="19">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>26</v>
@@ -8839,7 +8878,7 @@
       <c r="P100" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="Q100" s="29" t="s">
+      <c r="Q100" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R100" s="5" t="s">
@@ -8862,7 +8901,7 @@
     </row>
     <row r="101" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="19">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B101" s="7" t="s">
         <v>26</v>
@@ -8905,7 +8944,7 @@
       <c r="P101" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="Q101" s="29" t="s">
+      <c r="Q101" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R101" s="13" t="s">
@@ -8928,7 +8967,7 @@
     </row>
     <row r="102" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="19">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>26</v>
@@ -8971,7 +9010,7 @@
       <c r="P102" s="6" t="s">
         <v>389</v>
       </c>
-      <c r="Q102" s="29" t="s">
+      <c r="Q102" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R102" s="5" t="s">
@@ -8994,7 +9033,7 @@
     </row>
     <row r="103" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="19">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B103" s="7" t="s">
         <v>26</v>
@@ -9037,7 +9076,7 @@
       <c r="P103" s="7" t="s">
         <v>389</v>
       </c>
-      <c r="Q103" s="29" t="s">
+      <c r="Q103" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R103" s="13" t="s">
@@ -9062,7 +9101,7 @@
     </row>
     <row r="104" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="19">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>393</v>
@@ -9134,7 +9173,7 @@
     </row>
     <row r="105" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="19">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B105" s="7" t="s">
         <v>393</v>
@@ -9206,7 +9245,7 @@
     </row>
     <row r="106" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="19">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>393</v>
@@ -9276,7 +9315,7 @@
     </row>
     <row r="107" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="19">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B107" s="7" t="s">
         <v>393</v>
@@ -9348,7 +9387,7 @@
     </row>
     <row r="108" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="19">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>393</v>
@@ -9418,7 +9457,7 @@
     </row>
     <row r="109" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="19">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B109" s="7" t="s">
         <v>393</v>
@@ -9488,7 +9527,7 @@
     </row>
     <row r="110" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="19">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>393</v>
@@ -9560,7 +9599,7 @@
     </row>
     <row r="111" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="19">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>393</v>
@@ -9630,7 +9669,7 @@
     </row>
     <row r="112" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="19">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>393</v>
@@ -9700,7 +9739,7 @@
     </row>
     <row r="113" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="19">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B113" s="7" t="s">
         <v>26</v>
@@ -9741,7 +9780,7 @@
       <c r="P113" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="Q113" s="29" t="s">
+      <c r="Q113" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R113" s="13" t="s">
@@ -9764,7 +9803,7 @@
     </row>
     <row r="114" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="19">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>26</v>
@@ -9807,7 +9846,7 @@
       <c r="P114" s="6" t="s">
         <v>417</v>
       </c>
-      <c r="Q114" s="29" t="s">
+      <c r="Q114" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R114" s="5" t="s">
@@ -9830,7 +9869,7 @@
     </row>
     <row r="115" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="19">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B115" s="7" t="s">
         <v>26</v>
@@ -9873,7 +9912,7 @@
       <c r="P115" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="Q115" s="29" t="s">
+      <c r="Q115" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R115" s="13" t="s">
@@ -9896,7 +9935,7 @@
     </row>
     <row r="116" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="19">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>170</v>
@@ -9937,7 +9976,7 @@
       <c r="P116" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="Q116" s="29" t="s">
+      <c r="Q116" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R116" s="5" t="s">
@@ -9960,7 +9999,7 @@
     </row>
     <row r="117" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="19">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B117" s="7" t="s">
         <v>170</v>
@@ -10003,7 +10042,7 @@
       <c r="P117" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="Q117" s="29" t="s">
+      <c r="Q117" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R117" s="13" t="s">
@@ -10026,7 +10065,7 @@
     </row>
     <row r="118" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="19">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>26</v>
@@ -10061,7 +10100,7 @@
         <v>46</v>
       </c>
       <c r="P118" s="6"/>
-      <c r="Q118" s="29" t="s">
+      <c r="Q118" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R118" s="5" t="s">
@@ -10082,7 +10121,7 @@
     </row>
     <row r="119" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="19">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B119" s="7" t="s">
         <v>26</v>
@@ -10123,7 +10162,7 @@
       <c r="P119" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="Q119" s="29" t="s">
+      <c r="Q119" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R119" s="13" t="s">
@@ -10142,7 +10181,7 @@
     </row>
     <row r="120" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="19">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>170</v>
@@ -10183,7 +10222,7 @@
       <c r="P120" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="Q120" s="29" t="s">
+      <c r="Q120" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R120" s="5" t="s">
@@ -10202,7 +10241,7 @@
     </row>
     <row r="121" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="19">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B121" s="7" t="s">
         <v>26</v>
@@ -10239,7 +10278,7 @@
       <c r="P121" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="Q121" s="29" t="s">
+      <c r="Q121" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R121" s="13" t="s">
@@ -10260,7 +10299,7 @@
     </row>
     <row r="122" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="19">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>170</v>
@@ -10297,7 +10336,7 @@
       <c r="P122" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="Q122" s="29" t="s">
+      <c r="Q122" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R122" s="5" t="s">
@@ -10318,7 +10357,7 @@
     </row>
     <row r="123" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="19">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B123" s="7" t="s">
         <v>170</v>
@@ -10355,7 +10394,7 @@
       <c r="P123" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="Q123" s="29" t="s">
+      <c r="Q123" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R123" s="13" t="s">
@@ -10376,7 +10415,7 @@
     </row>
     <row r="124" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="19">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B124" s="6"/>
       <c r="C124" s="9"/>
@@ -10407,7 +10446,7 @@
         <v>46</v>
       </c>
       <c r="P124" s="6"/>
-      <c r="Q124" s="29" t="s">
+      <c r="Q124" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R124" s="5" t="s">
@@ -10426,7 +10465,7 @@
     </row>
     <row r="125" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="19">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B125" s="7" t="s">
         <v>26</v>
@@ -10467,7 +10506,7 @@
       <c r="P125" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="Q125" s="29" t="s">
+      <c r="Q125" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R125" s="13" t="s">
@@ -10488,7 +10527,7 @@
     </row>
     <row r="126" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="19">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>26</v>
@@ -10529,7 +10568,7 @@
       <c r="P126" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="Q126" s="29" t="s">
+      <c r="Q126" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R126" s="5" t="s">
@@ -10550,7 +10589,7 @@
     </row>
     <row r="127" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="19">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B127" s="7" t="s">
         <v>26</v>
@@ -10591,7 +10630,7 @@
       <c r="P127" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="Q127" s="29" t="s">
+      <c r="Q127" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R127" s="13" t="s">
@@ -10612,7 +10651,7 @@
     </row>
     <row r="128" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="19">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>26</v>
@@ -10653,7 +10692,7 @@
       <c r="P128" s="6" t="s">
         <v>438</v>
       </c>
-      <c r="Q128" s="29" t="s">
+      <c r="Q128" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R128" s="5" t="s">
@@ -10674,7 +10713,7 @@
     </row>
     <row r="129" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="19">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B129" s="7" t="s">
         <v>26</v>
@@ -10711,7 +10750,7 @@
       <c r="P129" s="7" t="s">
         <v>427</v>
       </c>
-      <c r="Q129" s="29" t="s">
+      <c r="Q129" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R129" s="13" t="s">
@@ -10732,7 +10771,7 @@
     </row>
     <row r="130" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="19">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>26</v>
@@ -10773,7 +10812,7 @@
       <c r="P130" s="6" t="s">
         <v>449</v>
       </c>
-      <c r="Q130" s="29" t="s">
+      <c r="Q130" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R130" s="5" t="s">
@@ -10794,7 +10833,7 @@
     </row>
     <row r="131" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="19">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B131" s="7" t="s">
         <v>26</v>
@@ -10835,7 +10874,7 @@
       <c r="P131" s="7" t="s">
         <v>453</v>
       </c>
-      <c r="Q131" s="29" t="s">
+      <c r="Q131" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R131" s="13" t="s">
@@ -10856,60 +10895,60 @@
     </row>
     <row r="132" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="19">
-        <v>131</v>
-      </c>
-      <c r="B132" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B132" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C132" s="9" t="s">
+      <c r="C132" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="D132" s="5" t="s">
+      <c r="D132" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="E132" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F132" s="2" t="s">
+      <c r="E132" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F132" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G132" s="9" t="s">
+      <c r="G132" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="H132" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I132" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="J132" s="2"/>
-      <c r="K132" s="2"/>
-      <c r="L132" s="2"/>
-      <c r="M132" s="2" t="s">
+      <c r="H132" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I132" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="J132" s="3"/>
+      <c r="K132" s="3"/>
+      <c r="L132" s="3"/>
+      <c r="M132" s="3" t="s">
         <v>456</v>
       </c>
       <c r="N132" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O132" s="6" t="s">
+      <c r="O132" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="P132" s="6" t="s">
+      <c r="P132" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="Q132" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R132" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S132" s="5" t="s">
+      <c r="Q132" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="R132" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S132" s="13" t="s">
         <v>347</v>
       </c>
       <c r="T132" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="U132" s="11">
+      <c r="U132" s="20">
         <v>46356</v>
       </c>
       <c r="V132" s="16">
@@ -10918,19 +10957,19 @@
       <c r="W132" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="X132" s="2" t="s">
+      <c r="X132" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Y132" s="2" t="s">
+      <c r="Y132" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="Z132" s="2" t="s">
-        <v>519</v>
+      <c r="Z132" s="3" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="133" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="19">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B133" s="7" t="s">
         <v>26</v>
@@ -10954,27 +10993,31 @@
         <v>32</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>458</v>
+        <v>518</v>
       </c>
       <c r="J133" s="3"/>
       <c r="K133" s="3"/>
       <c r="L133" s="3"/>
-      <c r="M133" s="27"/>
-      <c r="N133" s="6"/>
+      <c r="M133" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="N133" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="O133" s="7" t="s">
         <v>36</v>
       </c>
       <c r="P133" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="Q133" s="13" t="s">
+      <c r="Q133" s="28" t="s">
         <v>39</v>
       </c>
       <c r="R133" s="13" t="s">
         <v>38</v>
       </c>
       <c r="S133" s="13" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T133" s="5" t="s">
         <v>39</v>
@@ -10988,72 +11031,72 @@
       <c r="W133" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="X133" s="2" t="s">
+      <c r="X133" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Y133" s="2" t="s">
+      <c r="Y133" s="3" t="s">
         <v>51</v>
       </c>
       <c r="Z133" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
     </row>
     <row r="134" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="19">
-        <v>133</v>
-      </c>
-      <c r="B134" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B134" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C134" s="9" t="s">
+      <c r="C134" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="D134" s="5" t="s">
+      <c r="D134" s="13" t="s">
         <v>455</v>
       </c>
-      <c r="E134" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F134" s="2" t="s">
+      <c r="E134" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F134" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G134" s="9" t="s">
+      <c r="G134" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="H134" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I134" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="J134" s="2"/>
-      <c r="K134" s="2"/>
-      <c r="L134" s="2"/>
-      <c r="M134" s="2" t="s">
-        <v>461</v>
+      <c r="H134" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I134" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="J134" s="3"/>
+      <c r="K134" s="3"/>
+      <c r="L134" s="3"/>
+      <c r="M134" s="3" t="s">
+        <v>529</v>
       </c>
       <c r="N134" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O134" s="6" t="s">
+      <c r="O134" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="P134" s="6" t="s">
+      <c r="P134" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="Q134" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R134" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S134" s="5" t="s">
-        <v>462</v>
+      <c r="Q134" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="R134" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S134" s="13" t="s">
+        <v>460</v>
       </c>
       <c r="T134" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="U134" s="11">
+      <c r="U134" s="20">
         <v>46356</v>
       </c>
       <c r="V134" s="16">
@@ -11062,13 +11105,15 @@
       <c r="W134" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="X134" s="2"/>
-      <c r="Y134" s="2"/>
-      <c r="Z134" s="2"/>
+      <c r="X134" s="3"/>
+      <c r="Y134" s="3"/>
+      <c r="Z134" s="3" t="s">
+        <v>535</v>
+      </c>
     </row>
     <row r="135" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="19">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B135" s="7" t="s">
         <v>26</v>
@@ -11092,13 +11137,13 @@
         <v>32</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>463</v>
+        <v>520</v>
       </c>
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="3"/>
       <c r="M135" s="3" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="N135" s="6" t="s">
         <v>35</v>
@@ -11109,14 +11154,14 @@
       <c r="P135" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="Q135" s="13" t="s">
+      <c r="Q135" s="28" t="s">
         <v>39</v>
       </c>
       <c r="R135" s="13" t="s">
         <v>39</v>
       </c>
       <c r="S135" s="13" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="T135" s="5" t="s">
         <v>39</v>
@@ -11136,218 +11181,222 @@
     </row>
     <row r="136" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="19">
-        <v>135</v>
-      </c>
-      <c r="B136" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B136" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C136" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="F136" s="2" t="s">
+      <c r="C136" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D136" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="E136" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F136" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G136" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="I136" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="J136" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="K136" s="2"/>
-      <c r="L136" s="2"/>
-      <c r="M136" s="2" t="s">
-        <v>470</v>
+      <c r="G136" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I136" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="J136" s="3"/>
+      <c r="K136" s="3"/>
+      <c r="L136" s="3"/>
+      <c r="M136" s="3" t="s">
+        <v>530</v>
       </c>
       <c r="N136" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O136" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="P136" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q136" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R136" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S136" s="5" t="s">
-        <v>110</v>
+      <c r="O136" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P136" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q136" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="R136" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S136" s="13" t="s">
+        <v>462</v>
       </c>
       <c r="T136" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="U136" s="11">
-        <v>46146</v>
-      </c>
-      <c r="V136" s="16"/>
+        <v>39</v>
+      </c>
+      <c r="U136" s="20">
+        <v>46356</v>
+      </c>
+      <c r="V136" s="16">
+        <v>46286</v>
+      </c>
       <c r="W136" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="X136" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y136" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z136" s="2"/>
+      <c r="X136" s="3"/>
+      <c r="Y136" s="3"/>
+      <c r="Z136" s="3" t="s">
+        <v>536</v>
+      </c>
     </row>
     <row r="137" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="19">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B137" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C137" s="10" t="s">
-        <v>472</v>
+        <v>454</v>
       </c>
       <c r="D137" s="13" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>419</v>
+        <v>93</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>32</v>
+        <v>276</v>
       </c>
       <c r="H137" s="7" t="s">
-        <v>468</v>
+        <v>32</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="J137" s="3" t="s">
-        <v>384</v>
-      </c>
+        <v>522</v>
+      </c>
+      <c r="J137" s="3"/>
       <c r="K137" s="3"/>
       <c r="L137" s="3"/>
       <c r="M137" s="3" t="s">
-        <v>474</v>
+        <v>531</v>
       </c>
       <c r="N137" s="6" t="s">
         <v>35</v>
       </c>
       <c r="O137" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P137" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q137" s="13" t="s">
-        <v>38</v>
+        <v>457</v>
+      </c>
+      <c r="Q137" s="28" t="s">
+        <v>39</v>
       </c>
       <c r="R137" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S137" s="13" t="s">
-        <v>110</v>
+        <v>462</v>
       </c>
       <c r="T137" s="5" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="U137" s="20">
-        <v>46249</v>
-      </c>
-      <c r="V137" s="16"/>
+        <v>46356</v>
+      </c>
+      <c r="V137" s="16">
+        <v>46286</v>
+      </c>
       <c r="W137" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="X137" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y137" s="2" t="s">
-        <v>160</v>
-      </c>
+      <c r="X137" s="3"/>
+      <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
     <row r="138" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="19">
-        <v>137</v>
-      </c>
-      <c r="B138" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B138" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C138" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G138" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I138" s="6" t="s">
-        <v>476</v>
-      </c>
-      <c r="J138" s="2"/>
-      <c r="K138" s="2"/>
-      <c r="L138" s="2"/>
-      <c r="M138" s="2"/>
-      <c r="N138" s="6"/>
-      <c r="O138" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="P138" s="6" t="s">
-        <v>477</v>
-      </c>
-      <c r="Q138" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="R138" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S138" s="5"/>
+      <c r="C138" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D138" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="E138" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I138" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="J138" s="3"/>
+      <c r="K138" s="3"/>
+      <c r="L138" s="3"/>
+      <c r="M138" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="N138" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O138" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P138" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q138" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="R138" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S138" s="13" t="s">
+        <v>462</v>
+      </c>
       <c r="T138" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="U138" s="11">
-        <v>46311</v>
-      </c>
-      <c r="V138" s="16"/>
-      <c r="W138" s="9"/>
-      <c r="X138" s="2"/>
-      <c r="Y138" s="2"/>
-      <c r="Z138" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="U138" s="20">
+        <v>46356</v>
+      </c>
+      <c r="V138" s="16">
+        <v>46286</v>
+      </c>
+      <c r="W138" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X138" s="3"/>
+      <c r="Y138" s="3"/>
+      <c r="Z138" s="3"/>
     </row>
     <row r="139" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="19">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B139" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C139" s="10" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="D139" s="13" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>93</v>
@@ -11356,21 +11405,19 @@
         <v>30</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="H139" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>479</v>
-      </c>
-      <c r="J139" s="3" t="s">
-        <v>480</v>
-      </c>
+        <v>524</v>
+      </c>
+      <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="3"/>
-      <c r="M139" s="24" t="s">
-        <v>481</v>
+      <c r="M139" s="3" t="s">
+        <v>459</v>
       </c>
       <c r="N139" s="6" t="s">
         <v>35</v>
@@ -11379,25 +11426,25 @@
         <v>36</v>
       </c>
       <c r="P139" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="Q139" s="13" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q139" s="28" t="s">
         <v>39</v>
       </c>
       <c r="R139" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="S139" s="13" t="s">
-        <v>226</v>
+        <v>462</v>
       </c>
       <c r="T139" s="5" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="U139" s="20">
-        <v>46305</v>
+        <v>46356</v>
       </c>
       <c r="V139" s="16">
-        <v>46249</v>
+        <v>46286</v>
       </c>
       <c r="W139" s="9" t="s">
         <v>40</v>
@@ -11408,74 +11455,84 @@
     </row>
     <row r="140" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="19">
-        <v>139</v>
-      </c>
-      <c r="B140" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B140" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C140" s="9" t="s">
-        <v>433</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>434</v>
-      </c>
-      <c r="E140" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F140" s="2" t="s">
+      <c r="C140" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D140" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F140" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G140" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I140" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="J140" s="2"/>
-      <c r="K140" s="2"/>
-      <c r="L140" s="2"/>
-      <c r="M140" s="2"/>
-      <c r="N140" s="6"/>
-      <c r="O140" s="6" t="s">
-        <v>46</v>
+      <c r="G140" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I140" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="J140" s="3"/>
+      <c r="K140" s="3"/>
+      <c r="L140" s="3"/>
+      <c r="M140" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="N140" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O140" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="P140" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="Q140" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="R140" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S140" s="5"/>
+        <v>457</v>
+      </c>
+      <c r="Q140" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="R140" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S140" s="13" t="s">
+        <v>462</v>
+      </c>
       <c r="T140" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="U140" s="11">
-        <v>46305</v>
-      </c>
-      <c r="V140" s="16"/>
-      <c r="W140" s="9"/>
-      <c r="X140" s="2"/>
-      <c r="Y140" s="2"/>
-      <c r="Z140" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="U140" s="20">
+        <v>46356</v>
+      </c>
+      <c r="V140" s="16">
+        <v>46286</v>
+      </c>
+      <c r="W140" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X140" s="3"/>
+      <c r="Y140" s="3"/>
+      <c r="Z140" s="3"/>
     </row>
     <row r="141" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="19">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B141" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C141" s="10" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="D141" s="13" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="E141" s="7" t="s">
         <v>93</v>
@@ -11484,116 +11541,134 @@
         <v>30</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>32</v>
+        <v>276</v>
       </c>
       <c r="H141" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>439</v>
+        <v>526</v>
       </c>
       <c r="J141" s="3"/>
       <c r="K141" s="3"/>
       <c r="L141" s="3"/>
-      <c r="M141" s="2" t="s">
-        <v>440</v>
+      <c r="M141" s="3" t="s">
+        <v>532</v>
       </c>
       <c r="N141" s="6" t="s">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="O141" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P141" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="Q141" s="29" t="s">
-        <v>38</v>
+        <v>457</v>
+      </c>
+      <c r="Q141" s="28" t="s">
+        <v>39</v>
       </c>
       <c r="R141" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="S141" s="13"/>
+        <v>39</v>
+      </c>
+      <c r="S141" s="13" t="s">
+        <v>462</v>
+      </c>
       <c r="T141" s="5" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="U141" s="20">
-        <v>46305</v>
-      </c>
-      <c r="V141" s="16"/>
-      <c r="W141" s="9"/>
+        <v>46356</v>
+      </c>
+      <c r="V141" s="16">
+        <v>46286</v>
+      </c>
+      <c r="W141" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="X141" s="3"/>
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
     <row r="142" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="19">
-        <v>141</v>
-      </c>
-      <c r="B142" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B142" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C142" s="9" t="s">
-        <v>483</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="E142" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="F142" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G142" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I142" s="6" t="s">
-        <v>484</v>
-      </c>
-      <c r="J142" s="2"/>
-      <c r="K142" s="2"/>
-      <c r="L142" s="2"/>
-      <c r="M142" s="2"/>
-      <c r="N142" s="6"/>
-      <c r="O142" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="P142" s="6"/>
-      <c r="Q142" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="R142" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S142" s="5"/>
+      <c r="C142" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D142" s="13" t="s">
+        <v>455</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H142" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I142" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="J142" s="3"/>
+      <c r="K142" s="3"/>
+      <c r="L142" s="3"/>
+      <c r="M142" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="N142" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O142" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="P142" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="Q142" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="R142" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S142" s="13" t="s">
+        <v>462</v>
+      </c>
       <c r="T142" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="U142" s="11">
-        <v>46411</v>
-      </c>
-      <c r="V142" s="16"/>
-      <c r="W142" s="9"/>
-      <c r="X142" s="2"/>
-      <c r="Y142" s="2"/>
-      <c r="Z142" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="U142" s="20">
+        <v>46356</v>
+      </c>
+      <c r="V142" s="16">
+        <v>46286</v>
+      </c>
+      <c r="W142" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X142" s="3"/>
+      <c r="Y142" s="3"/>
+      <c r="Z142" s="3"/>
     </row>
     <row r="143" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="19">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B143" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C143" s="10" t="s">
-        <v>485</v>
+        <v>454</v>
       </c>
       <c r="D143" s="13" t="s">
-        <v>486</v>
+        <v>455</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>93</v>
@@ -11602,77 +11677,89 @@
         <v>30</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>32</v>
+        <v>276</v>
       </c>
       <c r="H143" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="J143" s="3"/>
       <c r="K143" s="3"/>
       <c r="L143" s="3"/>
-      <c r="M143" s="3"/>
-      <c r="N143" s="6"/>
+      <c r="M143" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="N143" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="O143" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P143" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="Q143" s="29" t="s">
-        <v>38</v>
+        <v>457</v>
+      </c>
+      <c r="Q143" s="28" t="s">
+        <v>39</v>
       </c>
       <c r="R143" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="S143" s="13"/>
+        <v>39</v>
+      </c>
+      <c r="S143" s="13" t="s">
+        <v>462</v>
+      </c>
       <c r="T143" s="5" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="U143" s="20">
-        <v>46351</v>
-      </c>
-      <c r="V143" s="16"/>
-      <c r="W143" s="9"/>
+        <v>46356</v>
+      </c>
+      <c r="V143" s="16">
+        <v>46286</v>
+      </c>
+      <c r="W143" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="X143" s="3"/>
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
     <row r="144" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="19">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>489</v>
+        <v>464</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>93</v>
+        <v>419</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>395</v>
+        <v>32</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>490</v>
+        <v>465</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="J144" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>384</v>
+      </c>
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
       <c r="M144" s="2" t="s">
-        <v>492</v>
+        <v>467</v>
       </c>
       <c r="N144" s="6" t="s">
         <v>35</v>
@@ -11681,7 +11768,7 @@
         <v>46</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>493</v>
+        <v>468</v>
       </c>
       <c r="Q144" s="5" t="s">
         <v>38</v>
@@ -11696,29 +11783,35 @@
         <v>93</v>
       </c>
       <c r="U144" s="11">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="V144" s="16"/>
-      <c r="W144" s="9"/>
-      <c r="X144" s="2"/>
-      <c r="Y144" s="2"/>
+      <c r="W144" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X144" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y144" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="Z144" s="2"/>
     </row>
     <row r="145" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="19">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B145" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C145" s="10" t="s">
-        <v>485</v>
+        <v>469</v>
       </c>
       <c r="D145" s="13" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>93</v>
+        <v>419</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>30</v>
@@ -11727,16 +11820,18 @@
         <v>32</v>
       </c>
       <c r="H145" s="7" t="s">
-        <v>32</v>
+        <v>465</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>494</v>
-      </c>
-      <c r="J145" s="3"/>
+        <v>470</v>
+      </c>
+      <c r="J145" s="3" t="s">
+        <v>384</v>
+      </c>
       <c r="K145" s="3"/>
       <c r="L145" s="3"/>
       <c r="M145" s="3" t="s">
-        <v>520</v>
+        <v>471</v>
       </c>
       <c r="N145" s="6" t="s">
         <v>35</v>
@@ -11744,46 +11839,54 @@
       <c r="O145" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="P145" s="6" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q145" s="29" t="s">
+      <c r="P145" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q145" s="13" t="s">
         <v>38</v>
       </c>
       <c r="R145" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S145" s="13"/>
+      <c r="S145" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T145" s="5" t="s">
         <v>93</v>
       </c>
       <c r="U145" s="20">
-        <v>46147</v>
+        <v>46249</v>
       </c>
       <c r="V145" s="16"/>
-      <c r="W145" s="9"/>
-      <c r="X145" s="3"/>
-      <c r="Y145" s="3"/>
+      <c r="W145" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X145" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y145" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="Z145" s="3"/>
     </row>
     <row r="146" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="19">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C146" s="9" t="s">
-        <v>409</v>
+        <v>469</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>486</v>
+        <v>87</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="G146" s="9" t="s">
         <v>32</v>
@@ -11792,24 +11895,20 @@
         <v>32</v>
       </c>
       <c r="I146" s="6" t="s">
-        <v>495</v>
+        <v>473</v>
       </c>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
-      <c r="M146" s="25" t="s">
-        <v>496</v>
-      </c>
-      <c r="N146" s="26" t="s">
-        <v>63</v>
-      </c>
+      <c r="M146" s="2"/>
+      <c r="N146" s="6"/>
       <c r="O146" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="Q146" s="29" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q146" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R146" s="5" t="s">
@@ -11820,7 +11919,7 @@
         <v>93</v>
       </c>
       <c r="U146" s="11">
-        <v>46351</v>
+        <v>46311</v>
       </c>
       <c r="V146" s="16"/>
       <c r="W146" s="9"/>
@@ -11830,16 +11929,16 @@
     </row>
     <row r="147" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="19">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B147" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>497</v>
+        <v>433</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>422</v>
+        <v>475</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>93</v>
@@ -11848,56 +11947,68 @@
         <v>30</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="H147" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>498</v>
-      </c>
-      <c r="J147" s="3"/>
+        <v>476</v>
+      </c>
+      <c r="J147" s="3" t="s">
+        <v>477</v>
+      </c>
       <c r="K147" s="3"/>
       <c r="L147" s="3"/>
-      <c r="M147" s="3"/>
-      <c r="N147" s="6"/>
+      <c r="M147" s="24" t="s">
+        <v>478</v>
+      </c>
+      <c r="N147" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="O147" s="7" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="P147" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="Q147" s="29" t="s">
-        <v>38</v>
+        <v>438</v>
+      </c>
+      <c r="Q147" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="R147" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S147" s="13"/>
+      <c r="S147" s="13" t="s">
+        <v>226</v>
+      </c>
       <c r="T147" s="5" t="s">
         <v>93</v>
       </c>
       <c r="U147" s="20">
-        <v>46253</v>
-      </c>
-      <c r="V147" s="16"/>
-      <c r="W147" s="9"/>
+        <v>46305</v>
+      </c>
+      <c r="V147" s="16">
+        <v>46249</v>
+      </c>
+      <c r="W147" s="9" t="s">
+        <v>40</v>
+      </c>
       <c r="X147" s="3"/>
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
     <row r="148" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="19">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>499</v>
+        <v>433</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>500</v>
+        <v>434</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>93</v>
@@ -11906,68 +12017,56 @@
         <v>30</v>
       </c>
       <c r="G148" s="9" t="s">
-        <v>501</v>
-      </c>
-      <c r="H148" s="28">
-        <v>46095</v>
+        <v>32</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>502</v>
-      </c>
-      <c r="J148" s="2" t="s">
-        <v>384</v>
-      </c>
+        <v>479</v>
+      </c>
+      <c r="J148" s="2"/>
       <c r="K148" s="2"/>
       <c r="L148" s="2"/>
-      <c r="M148" s="25" t="s">
-        <v>503</v>
-      </c>
-      <c r="N148" s="26" t="s">
-        <v>35</v>
-      </c>
+      <c r="M148" s="2"/>
+      <c r="N148" s="6"/>
       <c r="O148" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="P148" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="Q148" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
+      </c>
+      <c r="P148" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q148" s="28" t="s">
+        <v>38</v>
       </c>
       <c r="R148" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S148" s="5" t="s">
-        <v>505</v>
-      </c>
+      <c r="S148" s="5"/>
       <c r="T148" s="5" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="U148" s="11">
-        <v>46360</v>
-      </c>
-      <c r="V148" s="16">
-        <v>46286</v>
-      </c>
-      <c r="W148" s="9" t="s">
-        <v>40</v>
-      </c>
+        <v>46305</v>
+      </c>
+      <c r="V148" s="16"/>
+      <c r="W148" s="9"/>
       <c r="X148" s="2"/>
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
     <row r="149" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="19">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B149" s="7" t="s">
         <v>26</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>370</v>
+        <v>433</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>506</v>
+        <v>434</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>93</v>
@@ -11976,39 +12075,41 @@
         <v>30</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>507</v>
+        <v>32</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>508</v>
+        <v>32</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>509</v>
+        <v>439</v>
       </c>
       <c r="J149" s="3"/>
       <c r="K149" s="3"/>
       <c r="L149" s="3"/>
-      <c r="M149" s="3"/>
-      <c r="N149" s="6"/>
+      <c r="M149" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="N149" s="6" t="s">
+        <v>63</v>
+      </c>
       <c r="O149" s="7" t="s">
         <v>46</v>
       </c>
       <c r="P149" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="Q149" s="13" t="s">
+        <v>438</v>
+      </c>
+      <c r="Q149" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R149" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S149" s="13" t="s">
-        <v>110</v>
-      </c>
+      <c r="S149" s="13"/>
       <c r="T149" s="5" t="s">
         <v>93</v>
       </c>
       <c r="U149" s="20">
-        <v>46039</v>
+        <v>46305</v>
       </c>
       <c r="V149" s="16"/>
       <c r="W149" s="9"/>
@@ -12018,528 +12119,512 @@
     </row>
     <row r="150" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="19">
-        <v>150</v>
-      </c>
-      <c r="B150" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B150" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C150" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="D150" s="13" t="s">
+      <c r="C150" s="9" t="s">
+        <v>480</v>
+      </c>
+      <c r="D150" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="E150" s="7" t="s">
+      <c r="E150" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F150" s="3" t="s">
+      <c r="F150" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="G150" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H150" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I150" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="J150" s="3"/>
-      <c r="K150" s="3"/>
-      <c r="L150" s="3"/>
-      <c r="M150" s="3"/>
+      <c r="G150" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I150" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="J150" s="2"/>
+      <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
+      <c r="M150" s="2"/>
       <c r="N150" s="6"/>
-      <c r="O150" s="7" t="s">
+      <c r="O150" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="P150" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="Q150" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="R150" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="S150" s="13"/>
+      <c r="P150" s="6"/>
+      <c r="Q150" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R150" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S150" s="5"/>
       <c r="T150" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="U150" s="20">
-        <v>46341</v>
+      <c r="U150" s="11">
+        <v>46411</v>
       </c>
       <c r="V150" s="16"/>
       <c r="W150" s="9"/>
-      <c r="X150" s="3"/>
-      <c r="Y150" s="3"/>
-      <c r="Z150" s="3"/>
+      <c r="X150" s="2"/>
+      <c r="Y150" s="2"/>
+      <c r="Z150" s="2"/>
     </row>
     <row r="151" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="19">
-        <v>151</v>
-      </c>
-      <c r="B151" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C151" s="9" t="s">
-        <v>466</v>
-      </c>
-      <c r="D151" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="E151" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="F151" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B151" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="D151" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F151" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G151" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H151" s="6" t="s">
-        <v>468</v>
-      </c>
-      <c r="I151" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="J151" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="K151" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L151" s="2"/>
-      <c r="M151" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="N151" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="O151" s="6" t="s">
+      <c r="G151" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="J151" s="3"/>
+      <c r="K151" s="3"/>
+      <c r="L151" s="3"/>
+      <c r="M151" s="3"/>
+      <c r="N151" s="6"/>
+      <c r="O151" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="P151" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="Q151" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="R151" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S151" s="5" t="s">
-        <v>110</v>
-      </c>
+      <c r="P151" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q151" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R151" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S151" s="13"/>
       <c r="T151" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="U151" s="11">
-        <v>46176</v>
+      <c r="U151" s="20">
+        <v>46351</v>
       </c>
       <c r="V151" s="16"/>
       <c r="W151" s="9"/>
-      <c r="X151" s="2"/>
-      <c r="Y151" s="2"/>
-      <c r="Z151" s="2"/>
+      <c r="X151" s="3"/>
+      <c r="Y151" s="3"/>
+      <c r="Z151" s="3"/>
     </row>
     <row r="152" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="19">
-        <v>152</v>
-      </c>
-      <c r="B152" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C152" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="D152" s="13" t="s">
-        <v>467</v>
-      </c>
-      <c r="E152" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="F152" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C152" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="D152" s="5" t="s">
+        <v>486</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F152" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G152" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H152" s="7" t="s">
-        <v>468</v>
-      </c>
-      <c r="I152" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="J152" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="K152" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="L152" s="3"/>
-      <c r="M152" s="3" t="s">
-        <v>474</v>
+      <c r="G152" s="9" t="s">
+        <v>395</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="I152" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="J152" s="2"/>
+      <c r="K152" s="2"/>
+      <c r="L152" s="2"/>
+      <c r="M152" s="2" t="s">
+        <v>489</v>
       </c>
       <c r="N152" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="O152" s="7" t="s">
+      <c r="O152" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="P152" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="Q152" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="R152" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="S152" s="13" t="s">
+      <c r="P152" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="Q152" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="R152" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S152" s="5" t="s">
         <v>110</v>
       </c>
       <c r="T152" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="U152" s="20">
-        <v>46216</v>
+      <c r="U152" s="11">
+        <v>46147</v>
       </c>
       <c r="V152" s="16"/>
       <c r="W152" s="9"/>
-      <c r="X152" s="3"/>
-      <c r="Y152" s="3"/>
-      <c r="Z152" s="3"/>
+      <c r="X152" s="2"/>
+      <c r="Y152" s="2"/>
+      <c r="Z152" s="2"/>
     </row>
     <row r="153" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="19">
-        <v>157</v>
-      </c>
-      <c r="B153" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B153" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C153" s="9" t="s">
-        <v>409</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="E153" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F153" s="2" t="s">
+      <c r="C153" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="D153" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F153" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G153" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H153" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I153" s="6" t="s">
-        <v>513</v>
-      </c>
-      <c r="J153" s="2"/>
-      <c r="K153" s="2"/>
-      <c r="L153" s="2"/>
-      <c r="M153" s="25" t="s">
-        <v>514</v>
-      </c>
-      <c r="N153" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="O153" s="6" t="s">
+      <c r="G153" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H153" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I153" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="J153" s="3"/>
+      <c r="K153" s="3"/>
+      <c r="L153" s="3"/>
+      <c r="M153" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="N153" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O153" s="7" t="s">
         <v>46</v>
       </c>
       <c r="P153" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="Q153" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="R153" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S153" s="5"/>
+        <v>490</v>
+      </c>
+      <c r="Q153" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R153" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S153" s="13"/>
       <c r="T153" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="U153" s="11">
-        <v>46264</v>
+      <c r="U153" s="20">
+        <v>46147</v>
       </c>
       <c r="V153" s="16"/>
       <c r="W153" s="9"/>
-      <c r="X153" s="2"/>
-      <c r="Y153" s="2"/>
-      <c r="Z153" s="2"/>
+      <c r="X153" s="3"/>
+      <c r="Y153" s="3"/>
+      <c r="Z153" s="3"/>
     </row>
     <row r="154" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="19">
-        <v>158</v>
-      </c>
-      <c r="B154" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B154" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C154" s="10" t="s">
+      <c r="C154" s="9" t="s">
         <v>409</v>
       </c>
-      <c r="D154" s="13" t="s">
-        <v>486</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F154" s="3" t="s">
+      <c r="D154" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F154" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G154" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H154" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I154" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="J154" s="3"/>
-      <c r="K154" s="3"/>
-      <c r="L154" s="3"/>
+      <c r="G154" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I154" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="J154" s="2"/>
+      <c r="K154" s="2"/>
+      <c r="L154" s="2"/>
       <c r="M154" s="25" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="N154" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="O154" s="7" t="s">
+      <c r="O154" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="P154" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="Q154" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="R154" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="S154" s="13"/>
+      <c r="P154" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q154" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R154" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S154" s="5"/>
       <c r="T154" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="U154" s="20"/>
+      <c r="U154" s="11">
+        <v>46351</v>
+      </c>
       <c r="V154" s="16"/>
       <c r="W154" s="9"/>
-      <c r="X154" s="3"/>
-      <c r="Y154" s="3"/>
-      <c r="Z154" s="3"/>
+      <c r="X154" s="2"/>
+      <c r="Y154" s="2"/>
+      <c r="Z154" s="2"/>
     </row>
     <row r="155" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="19">
-        <v>159</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C155" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="D155" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F155" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B155" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C155" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="D155" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F155" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G155" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H155" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I155" s="6" t="s">
-        <v>487</v>
-      </c>
-      <c r="J155" s="2"/>
-      <c r="K155" s="2"/>
-      <c r="L155" s="2"/>
-      <c r="M155" s="25" t="s">
-        <v>516</v>
-      </c>
-      <c r="N155" s="26" t="s">
-        <v>35</v>
-      </c>
-      <c r="O155" s="6" t="s">
+      <c r="G155" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H155" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I155" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="J155" s="3"/>
+      <c r="K155" s="3"/>
+      <c r="L155" s="3"/>
+      <c r="M155" s="3"/>
+      <c r="N155" s="6"/>
+      <c r="O155" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="P155" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="Q155" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="R155" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S155" s="5"/>
+      <c r="P155" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q155" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R155" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S155" s="13"/>
       <c r="T155" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="U155" s="11">
-        <v>46241</v>
+      <c r="U155" s="20">
+        <v>46253</v>
       </c>
       <c r="V155" s="16"/>
       <c r="W155" s="9"/>
-      <c r="X155" s="2"/>
-      <c r="Y155" s="2"/>
-      <c r="Z155" s="2"/>
+      <c r="X155" s="3"/>
+      <c r="Y155" s="3"/>
+      <c r="Z155" s="3"/>
     </row>
     <row r="156" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="19">
-        <v>160</v>
-      </c>
-      <c r="B156" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="C156" s="10" t="s">
-        <v>485</v>
-      </c>
-      <c r="D156" s="13" t="s">
-        <v>489</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F156" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C156" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="D156" s="5" t="s">
+        <v>497</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F156" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G156" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="H156" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="I156" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="J156" s="3"/>
-      <c r="K156" s="3"/>
-      <c r="L156" s="3"/>
-      <c r="M156" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="N156" s="6" t="s">
+      <c r="G156" s="9" t="s">
+        <v>498</v>
+      </c>
+      <c r="H156" s="27">
+        <v>46095</v>
+      </c>
+      <c r="I156" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
+      <c r="M156" s="25" t="s">
+        <v>500</v>
+      </c>
+      <c r="N156" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="O156" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="P156" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="Q156" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="R156" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="S156" s="13" t="s">
-        <v>110</v>
+      <c r="O156" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="P156" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="Q156" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R156" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S156" s="5" t="s">
+        <v>502</v>
       </c>
       <c r="T156" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="U156" s="20">
-        <v>46148</v>
-      </c>
-      <c r="V156" s="16"/>
+        <v>39</v>
+      </c>
+      <c r="U156" s="11">
+        <v>46360</v>
+      </c>
+      <c r="V156" s="16">
+        <v>46286</v>
+      </c>
       <c r="W156" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="X156" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y156" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z156" s="3"/>
+      <c r="X156" s="2"/>
+      <c r="Y156" s="2"/>
+      <c r="Z156" s="2"/>
     </row>
     <row r="157" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="19">
-        <v>161</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C157" s="9" t="s">
-        <v>485</v>
-      </c>
-      <c r="D157" s="5" t="s">
-        <v>486</v>
-      </c>
-      <c r="E157" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F157" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B157" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C157" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D157" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F157" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G157" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H157" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I157" s="6" t="s">
-        <v>494</v>
-      </c>
-      <c r="J157" s="2"/>
-      <c r="K157" s="2"/>
-      <c r="L157" s="2"/>
-      <c r="M157" s="2"/>
+      <c r="G157" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="I157" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="J157" s="3"/>
+      <c r="K157" s="3"/>
+      <c r="L157" s="3"/>
+      <c r="M157" s="3"/>
       <c r="N157" s="6"/>
-      <c r="O157" s="6" t="s">
+      <c r="O157" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="P157" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="Q157" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="R157" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S157" s="5"/>
+      <c r="P157" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q157" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R157" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S157" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T157" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="U157" s="11">
-        <v>46148</v>
+      <c r="U157" s="20">
+        <v>46039</v>
       </c>
       <c r="V157" s="16"/>
       <c r="W157" s="9"/>
-      <c r="X157" s="2"/>
-      <c r="Y157" s="2"/>
-      <c r="Z157" s="2"/>
+      <c r="X157" s="3"/>
+      <c r="Y157" s="3"/>
+      <c r="Z157" s="3"/>
     </row>
     <row r="158" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="19">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="B158" s="7" t="s">
-        <v>170</v>
+        <v>26</v>
       </c>
       <c r="C158" s="10" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="D158" s="13" t="s">
-        <v>486</v>
+        <v>87</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>30</v>
+        <v>88</v>
       </c>
       <c r="G158" s="3" t="s">
         <v>32</v>
@@ -12548,24 +12633,20 @@
         <v>32</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="J158" s="3"/>
       <c r="K158" s="3"/>
       <c r="L158" s="3"/>
-      <c r="M158" s="25" t="s">
-        <v>514</v>
-      </c>
-      <c r="N158" s="26" t="s">
-        <v>63</v>
-      </c>
+      <c r="M158" s="3"/>
+      <c r="N158" s="6"/>
       <c r="O158" s="7" t="s">
         <v>46</v>
       </c>
       <c r="P158" s="7" t="s">
-        <v>488</v>
-      </c>
-      <c r="Q158" s="29" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q158" s="28" t="s">
         <v>38</v>
       </c>
       <c r="R158" s="13" t="s">
@@ -12573,10 +12654,10 @@
       </c>
       <c r="S158" s="13"/>
       <c r="T158" s="5" t="s">
-        <v>39</v>
+        <v>93</v>
       </c>
       <c r="U158" s="20">
-        <v>46264</v>
+        <v>46341</v>
       </c>
       <c r="V158" s="16"/>
       <c r="W158" s="9"/>
@@ -12586,19 +12667,19 @@
     </row>
     <row r="159" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="19">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>170</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>497</v>
+        <v>463</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>422</v>
+        <v>464</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>93</v>
+        <v>419</v>
       </c>
       <c r="F159" s="2" t="s">
         <v>30</v>
@@ -12607,34 +12688,44 @@
         <v>32</v>
       </c>
       <c r="H159" s="6" t="s">
-        <v>32</v>
+        <v>465</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>498</v>
-      </c>
-      <c r="J159" s="2"/>
-      <c r="K159" s="2"/>
+        <v>466</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="K159" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="L159" s="2"/>
-      <c r="M159" s="2"/>
-      <c r="N159" s="6"/>
+      <c r="M159" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="N159" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="O159" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P159" s="6" t="s">
-        <v>427</v>
-      </c>
-      <c r="Q159" s="29" t="s">
+        <v>468</v>
+      </c>
+      <c r="Q159" s="5" t="s">
         <v>38</v>
       </c>
       <c r="R159" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S159" s="5"/>
+      <c r="S159" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T159" s="5" t="s">
         <v>93</v>
       </c>
       <c r="U159" s="11">
-        <v>46253</v>
+        <v>46176</v>
       </c>
       <c r="V159" s="16"/>
       <c r="W159" s="9"/>
@@ -12644,42 +12735,50 @@
     </row>
     <row r="160" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="19">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B160" s="7" t="s">
         <v>170</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>370</v>
+        <v>469</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>506</v>
+        <v>464</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>93</v>
+        <v>419</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>507</v>
+        <v>32</v>
       </c>
       <c r="H160" s="7" t="s">
-        <v>508</v>
+        <v>465</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="J160" s="3"/>
-      <c r="K160" s="3"/>
+        <v>470</v>
+      </c>
+      <c r="J160" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="K160" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="L160" s="3"/>
-      <c r="M160" s="3"/>
-      <c r="N160" s="6"/>
+      <c r="M160" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="N160" s="6" t="s">
+        <v>35</v>
+      </c>
       <c r="O160" s="7" t="s">
         <v>46</v>
       </c>
       <c r="P160" s="7" t="s">
-        <v>510</v>
+        <v>472</v>
       </c>
       <c r="Q160" s="13" t="s">
         <v>38</v>
@@ -12694,31 +12793,523 @@
         <v>93</v>
       </c>
       <c r="U160" s="20">
+        <v>46216</v>
+      </c>
+      <c r="V160" s="16"/>
+      <c r="W160" s="9"/>
+      <c r="X160" s="3"/>
+      <c r="Y160" s="3"/>
+      <c r="Z160" s="3"/>
+    </row>
+    <row r="161" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A161" s="19">
+        <v>159</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C161" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="D161" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G161" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H161" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I161" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="J161" s="2"/>
+      <c r="K161" s="2"/>
+      <c r="L161" s="2"/>
+      <c r="M161" s="25" t="s">
+        <v>511</v>
+      </c>
+      <c r="N161" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="O161" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P161" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q161" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R161" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S161" s="5"/>
+      <c r="T161" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U161" s="11">
+        <v>46264</v>
+      </c>
+      <c r="V161" s="16"/>
+      <c r="W161" s="9"/>
+      <c r="X161" s="2"/>
+      <c r="Y161" s="2"/>
+      <c r="Z161" s="2"/>
+    </row>
+    <row r="162" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A162" s="19">
+        <v>160</v>
+      </c>
+      <c r="B162" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C162" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="D162" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H162" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I162" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="J162" s="3"/>
+      <c r="K162" s="3"/>
+      <c r="L162" s="3"/>
+      <c r="M162" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="N162" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="O162" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P162" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q162" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R162" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S162" s="13"/>
+      <c r="T162" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U162" s="20"/>
+      <c r="V162" s="16"/>
+      <c r="W162" s="9"/>
+      <c r="X162" s="3"/>
+      <c r="Y162" s="3"/>
+      <c r="Z162" s="3"/>
+    </row>
+    <row r="163" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A163" s="19">
+        <v>161</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C163" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H163" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I163" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="J163" s="2"/>
+      <c r="K163" s="2"/>
+      <c r="L163" s="2"/>
+      <c r="M163" s="25" t="s">
+        <v>513</v>
+      </c>
+      <c r="N163" s="26" t="s">
+        <v>35</v>
+      </c>
+      <c r="O163" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P163" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q163" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R163" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S163" s="5"/>
+      <c r="T163" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U163" s="11">
+        <v>46241</v>
+      </c>
+      <c r="V163" s="16"/>
+      <c r="W163" s="9"/>
+      <c r="X163" s="2"/>
+      <c r="Y163" s="2"/>
+      <c r="Z163" s="2"/>
+    </row>
+    <row r="164" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A164" s="19">
+        <v>162</v>
+      </c>
+      <c r="B164" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C164" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="D164" s="13" t="s">
+        <v>486</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="H164" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="I164" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="J164" s="3"/>
+      <c r="K164" s="3"/>
+      <c r="L164" s="3"/>
+      <c r="M164" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="N164" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="O164" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P164" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="Q164" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R164" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S164" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="T164" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U164" s="20">
+        <v>46148</v>
+      </c>
+      <c r="V164" s="16"/>
+      <c r="W164" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="X164" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y164" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z164" s="3"/>
+    </row>
+    <row r="165" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A165" s="19">
+        <v>163</v>
+      </c>
+      <c r="B165" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C165" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="D165" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="E165" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G165" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H165" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I165" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="J165" s="2"/>
+      <c r="K165" s="2"/>
+      <c r="L165" s="2"/>
+      <c r="M165" s="2"/>
+      <c r="N165" s="6"/>
+      <c r="O165" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P165" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q165" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R165" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S165" s="5"/>
+      <c r="T165" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U165" s="11">
+        <v>46148</v>
+      </c>
+      <c r="V165" s="16"/>
+      <c r="W165" s="9"/>
+      <c r="X165" s="2"/>
+      <c r="Y165" s="2"/>
+      <c r="Z165" s="2"/>
+    </row>
+    <row r="166" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A166" s="19">
+        <v>164</v>
+      </c>
+      <c r="B166" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C166" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="D166" s="13" t="s">
+        <v>483</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H166" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I166" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="J166" s="3"/>
+      <c r="K166" s="3"/>
+      <c r="L166" s="3"/>
+      <c r="M166" s="25" t="s">
+        <v>511</v>
+      </c>
+      <c r="N166" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="O166" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P166" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="Q166" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R166" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S166" s="13"/>
+      <c r="T166" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="U166" s="20">
+        <v>46264</v>
+      </c>
+      <c r="V166" s="16"/>
+      <c r="W166" s="9"/>
+      <c r="X166" s="3"/>
+      <c r="Y166" s="3"/>
+      <c r="Z166" s="3"/>
+    </row>
+    <row r="167" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A167" s="19">
+        <v>165</v>
+      </c>
+      <c r="B167" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C167" s="9" t="s">
+        <v>494</v>
+      </c>
+      <c r="D167" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="E167" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G167" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H167" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I167" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="J167" s="2"/>
+      <c r="K167" s="2"/>
+      <c r="L167" s="2"/>
+      <c r="M167" s="2"/>
+      <c r="N167" s="6"/>
+      <c r="O167" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="P167" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="Q167" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R167" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S167" s="5"/>
+      <c r="T167" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U167" s="11">
+        <v>46253</v>
+      </c>
+      <c r="V167" s="16"/>
+      <c r="W167" s="9"/>
+      <c r="X167" s="2"/>
+      <c r="Y167" s="2"/>
+      <c r="Z167" s="2"/>
+    </row>
+    <row r="168" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A168" s="19">
+        <v>166</v>
+      </c>
+      <c r="B168" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C168" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="D168" s="13" t="s">
+        <v>503</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="H168" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="I168" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="J168" s="3"/>
+      <c r="K168" s="3"/>
+      <c r="L168" s="3"/>
+      <c r="M168" s="3"/>
+      <c r="N168" s="6"/>
+      <c r="O168" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="P168" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q168" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R168" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S168" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="T168" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="U168" s="20">
         <v>46133</v>
       </c>
-      <c r="V160" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="W160" s="9" t="s">
+      <c r="V168" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="W168" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="X160" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y160" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="Z160" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="161" spans="24:24" x14ac:dyDescent="0.3">
-      <c r="X161">
+      <c r="X168" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y168" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z168" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="169" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="X169">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z161" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:Z169" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>

--- a/KAFD00330_Delivery_Master.xlsx
+++ b/KAFD00330_Delivery_Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbcmsa-my.sharepoint.com/personal/mohammed_b_sbcm-sa_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="198" documentId="11_B464D923760B716A87BF040CED6C1C7D597CE204" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DA99C87-1D7D-467E-916C-7505EFA14259}"/>
+  <xr:revisionPtr revIDLastSave="345" documentId="11_B464D923760B716A87BF040CED6C1C7D597CE204" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C53D48F-8C81-42ED-8F43-AC02DA567653}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Delivery" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2940" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3009" uniqueCount="558">
   <si>
     <t>KAFD00330 — RO Plant: Material Delivery Master (edit here; sync to the report)</t>
   </si>
@@ -378,9 +378,6 @@
   </si>
   <si>
     <t>KAFD-636-SBC-ELE-MAR-00041</t>
-  </si>
-  <si>
-    <t>SCHNEIDER / BAHRA</t>
   </si>
   <si>
     <t>2026-08-13</t>
@@ -1737,6 +1734,12 @@
   </si>
   <si>
     <t>KAFD-636-SBC-ICT-MIR-00004</t>
+  </si>
+  <si>
+    <t>UK</t>
+  </si>
+  <si>
+    <t>BAHRA</t>
   </si>
 </sst>
 </file>
@@ -2235,7 +2238,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z180"/>
@@ -2379,7 +2382,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19">
         <v>1</v>
       </c>
@@ -2428,7 +2431,9 @@
       <c r="R3" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S3" s="5"/>
+      <c r="S3" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="T3" s="5" t="s">
         <v>39</v>
       </c>
@@ -2498,7 +2503,9 @@
       <c r="R4" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="13"/>
+      <c r="S4" s="13" t="s">
+        <v>556</v>
+      </c>
       <c r="T4" s="5" t="s">
         <v>39</v>
       </c>
@@ -2585,7 +2592,7 @@
       <c r="Y5" s="2"/>
       <c r="Z5" s="2"/>
     </row>
-    <row r="6" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19">
         <v>4</v>
       </c>
@@ -2634,7 +2641,9 @@
       <c r="R6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="S6" s="13"/>
+      <c r="S6" s="13" t="s">
+        <v>556</v>
+      </c>
       <c r="T6" s="5" t="s">
         <v>39</v>
       </c>
@@ -2651,7 +2660,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="19">
         <v>5</v>
       </c>
@@ -2782,7 +2791,7 @@
         <v>51</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2854,7 +2863,7 @@
         <v>51</v>
       </c>
       <c r="Z9" s="2" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2926,7 +2935,7 @@
         <v>51</v>
       </c>
       <c r="Z10" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -2978,7 +2987,9 @@
       <c r="R11" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S11" s="5"/>
+      <c r="S11" s="5" t="s">
+        <v>458</v>
+      </c>
       <c r="T11" s="5" t="s">
         <v>39</v>
       </c>
@@ -2989,9 +3000,11 @@
         <v>46310</v>
       </c>
       <c r="W11" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="X11" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
@@ -3059,7 +3072,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="19">
         <v>11</v>
       </c>
@@ -3108,7 +3121,9 @@
       <c r="R13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S13" s="5"/>
+      <c r="S13" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T13" s="5" t="s">
         <v>93</v>
       </c>
@@ -3123,7 +3138,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19">
         <v>12</v>
       </c>
@@ -3172,7 +3187,9 @@
       <c r="R14" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="S14" s="13"/>
+      <c r="S14" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T14" s="13" t="s">
         <v>93</v>
       </c>
@@ -3187,7 +3204,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="19">
         <v>13</v>
       </c>
@@ -3236,7 +3253,9 @@
       <c r="R15" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S15" s="5"/>
+      <c r="S15" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T15" s="5" t="s">
         <v>93</v>
       </c>
@@ -3251,7 +3270,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="19">
         <v>14</v>
       </c>
@@ -3300,7 +3319,9 @@
       <c r="R16" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="S16" s="13"/>
+      <c r="S16" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T16" s="5" t="s">
         <v>93</v>
       </c>
@@ -3315,7 +3336,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="19">
         <v>15</v>
       </c>
@@ -3364,7 +3385,9 @@
       <c r="R17" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S17" s="5"/>
+      <c r="S17" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T17" s="5" t="s">
         <v>93</v>
       </c>
@@ -3379,7 +3402,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="19">
         <v>16</v>
       </c>
@@ -3428,7 +3451,9 @@
       <c r="R18" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="S18" s="13"/>
+      <c r="S18" s="13" t="s">
+        <v>556</v>
+      </c>
       <c r="T18" s="5" t="s">
         <v>39</v>
       </c>
@@ -3445,7 +3470,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19">
         <v>17</v>
       </c>
@@ -3513,7 +3538,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="19">
         <v>18</v>
       </c>
@@ -3562,7 +3587,9 @@
       <c r="R20" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="S20" s="13"/>
+      <c r="S20" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T20" s="5" t="s">
         <v>93</v>
       </c>
@@ -3577,7 +3604,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="19">
         <v>19</v>
       </c>
@@ -3618,7 +3645,7 @@
         <v>46</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>117</v>
+        <v>557</v>
       </c>
       <c r="Q21" s="5" t="s">
         <v>38</v>
@@ -3626,7 +3653,9 @@
       <c r="R21" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S21" s="5"/>
+      <c r="S21" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T21" s="5" t="s">
         <v>93</v>
       </c>
@@ -3641,7 +3670,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="19">
         <v>20</v>
       </c>
@@ -3661,19 +3690,19 @@
         <v>88</v>
       </c>
       <c r="G22" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>119</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="N22" s="6" t="s">
         <v>35</v>
@@ -3682,7 +3711,7 @@
         <v>46</v>
       </c>
       <c r="P22" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q22" s="5" t="s">
         <v>38</v>
@@ -3690,7 +3719,9 @@
       <c r="R22" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S22" s="13"/>
+      <c r="S22" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T22" s="5" t="s">
         <v>93</v>
       </c>
@@ -3707,13 +3738,13 @@
         <v>50</v>
       </c>
       <c r="Y22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z22" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="19">
         <v>21</v>
       </c>
@@ -3727,7 +3758,7 @@
         <v>28</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>30</v>
@@ -3739,13 +3770,13 @@
         <v>32</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="N23" s="6" t="s">
         <v>35</v>
@@ -3754,7 +3785,7 @@
         <v>46</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q23" s="5" t="s">
         <v>38</v>
@@ -3762,7 +3793,9 @@
       <c r="R23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S23" s="5"/>
+      <c r="S23" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T23" s="5" t="s">
         <v>93</v>
       </c>
@@ -3782,10 +3815,10 @@
         <v>51</v>
       </c>
       <c r="Z23" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="19">
         <v>22</v>
       </c>
@@ -3799,25 +3832,25 @@
         <v>28</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="N24" s="6" t="s">
         <v>35</v>
@@ -3826,7 +3859,7 @@
         <v>46</v>
       </c>
       <c r="P24" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q24" s="5" t="s">
         <v>38</v>
@@ -3834,7 +3867,9 @@
       <c r="R24" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S24" s="13"/>
+      <c r="S24" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T24" s="5" t="s">
         <v>93</v>
       </c>
@@ -3854,10 +3889,10 @@
         <v>51</v>
       </c>
       <c r="Z24" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="19">
         <v>23</v>
       </c>
@@ -3871,25 +3906,25 @@
         <v>28</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I25" s="6" t="s">
         <v>135</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>35</v>
@@ -3898,7 +3933,7 @@
         <v>46</v>
       </c>
       <c r="P25" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q25" s="5" t="s">
         <v>38</v>
@@ -3906,7 +3941,9 @@
       <c r="R25" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S25" s="5"/>
+      <c r="S25" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T25" s="5" t="s">
         <v>93</v>
       </c>
@@ -3923,10 +3960,10 @@
         <v>50</v>
       </c>
       <c r="Y25" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z25" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -3943,7 +3980,7 @@
         <v>28</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>30</v>
@@ -3955,13 +3992,13 @@
         <v>32</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="N26" s="6" t="s">
         <v>35</v>
@@ -3970,7 +4007,7 @@
         <v>46</v>
       </c>
       <c r="P26" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q26" s="5" t="s">
         <v>38</v>
@@ -3978,7 +4015,9 @@
       <c r="R26" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S26" s="13"/>
+      <c r="S26" s="13" t="s">
+        <v>458</v>
+      </c>
       <c r="T26" s="5" t="s">
         <v>93</v>
       </c>
@@ -3993,10 +4032,10 @@
         <v>50</v>
       </c>
       <c r="Y26" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Z26" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4025,13 +4064,13 @@
         <v>32</v>
       </c>
       <c r="I27" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N27" s="6" t="s">
         <v>35</v>
@@ -4040,7 +4079,7 @@
         <v>46</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q27" s="5" t="s">
         <v>38</v>
@@ -4048,7 +4087,9 @@
       <c r="R27" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S27" s="5"/>
+      <c r="S27" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T27" s="5" t="s">
         <v>93</v>
       </c>
@@ -4063,7 +4104,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="19">
         <v>26</v>
       </c>
@@ -4077,25 +4118,25 @@
         <v>28</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G28" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I28" s="7" t="s">
         <v>149</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>150</v>
       </c>
       <c r="J28" s="13"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N28" s="6" t="s">
         <v>35</v>
@@ -4104,7 +4145,7 @@
         <v>36</v>
       </c>
       <c r="P28" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q28" s="5" t="s">
         <v>38</v>
@@ -4132,10 +4173,10 @@
         <v>51</v>
       </c>
       <c r="Z28" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="19">
         <v>27</v>
       </c>
@@ -4161,7 +4202,7 @@
         <v>32</v>
       </c>
       <c r="I29" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="2"/>
@@ -4172,7 +4213,7 @@
         <v>46</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q29" s="5" t="s">
         <v>38</v>
@@ -4180,7 +4221,9 @@
       <c r="R29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="S29" s="5"/>
+      <c r="S29" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T29" s="5" t="s">
         <v>93</v>
       </c>
@@ -4195,7 +4238,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="19">
         <v>28</v>
       </c>
@@ -4215,13 +4258,13 @@
         <v>88</v>
       </c>
       <c r="G30" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>156</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>157</v>
       </c>
       <c r="J30" s="13"/>
       <c r="K30" s="3"/>
@@ -4232,7 +4275,7 @@
         <v>46</v>
       </c>
       <c r="P30" s="7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q30" s="5" t="s">
         <v>38</v>
@@ -4240,7 +4283,9 @@
       <c r="R30" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S30" s="13"/>
+      <c r="S30" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T30" s="5" t="s">
         <v>93</v>
       </c>
@@ -4255,11 +4300,11 @@
       </c>
       <c r="X30" s="3"/>
       <c r="Y30" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="19">
         <v>29</v>
       </c>
@@ -4279,19 +4324,19 @@
         <v>30</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="N31" s="6" t="s">
         <v>35</v>
@@ -4300,7 +4345,7 @@
         <v>46</v>
       </c>
       <c r="P31" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q31" s="5" t="s">
         <v>38</v>
@@ -4308,7 +4353,9 @@
       <c r="R31" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S31" s="5"/>
+      <c r="S31" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T31" s="5" t="s">
         <v>93</v>
       </c>
@@ -4326,7 +4373,7 @@
         <v>51</v>
       </c>
       <c r="Z31" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4355,7 +4402,7 @@
         <v>32</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="J32" s="13"/>
       <c r="K32" s="3"/>
@@ -4366,7 +4413,7 @@
         <v>46</v>
       </c>
       <c r="P32" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q32" s="5" t="s">
         <v>38</v>
@@ -4415,11 +4462,11 @@
         <v>32</v>
       </c>
       <c r="I33" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L33" s="2" t="s">
         <v>35</v>
@@ -4430,7 +4477,7 @@
         <v>46</v>
       </c>
       <c r="P33" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="Q33" s="5" t="s">
         <v>38</v>
@@ -4438,7 +4485,9 @@
       <c r="R33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S33" s="5"/>
+      <c r="S33" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T33" s="5" t="s">
         <v>93</v>
       </c>
@@ -4453,21 +4502,21 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="19">
         <v>32</v>
       </c>
       <c r="B34" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C34" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="D34" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="E34" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>172</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>30</v>
@@ -4479,13 +4528,13 @@
         <v>32</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="J34" s="13"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N34" s="6" t="s">
         <v>35</v>
@@ -4494,7 +4543,7 @@
         <v>46</v>
       </c>
       <c r="P34" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q34" s="5" t="s">
         <v>38</v>
@@ -4502,7 +4551,9 @@
       <c r="R34" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S34" s="13"/>
+      <c r="S34" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T34" s="5" t="s">
         <v>93</v>
       </c>
@@ -4522,42 +4573,42 @@
         <v>51</v>
       </c>
       <c r="Z34" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="35" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="19">
         <v>33</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C35" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C35" s="9" t="s">
+      <c r="D35" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="E35" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I35" s="6" t="s">
         <v>178</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="N35" s="6" t="s">
         <v>35</v>
@@ -4566,7 +4617,7 @@
         <v>36</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q35" s="5" t="s">
         <v>38</v>
@@ -4596,42 +4647,42 @@
         <v>51</v>
       </c>
       <c r="Z35" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="36" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="19">
         <v>34</v>
       </c>
       <c r="B36" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="D36" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="D36" s="13" t="s">
-        <v>171</v>
-      </c>
       <c r="E36" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G36" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H36" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="7" t="s">
         <v>183</v>
-      </c>
-      <c r="H36" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>184</v>
       </c>
       <c r="J36" s="13"/>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N36" s="6" t="s">
         <v>35</v>
@@ -4640,7 +4691,7 @@
         <v>36</v>
       </c>
       <c r="P36" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q36" s="13" t="s">
         <v>38</v>
@@ -4670,24 +4721,24 @@
         <v>51</v>
       </c>
       <c r="Z36" s="3" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="37" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="19">
         <v>35</v>
       </c>
       <c r="B37" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C37" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="D37" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D37" s="5" t="s">
-        <v>171</v>
-      </c>
       <c r="E37" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>30</v>
@@ -4699,13 +4750,13 @@
         <v>32</v>
       </c>
       <c r="I37" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N37" s="6" t="s">
         <v>35</v>
@@ -4714,7 +4765,7 @@
         <v>46</v>
       </c>
       <c r="P37" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q37" s="13" t="s">
         <v>38</v>
@@ -4722,7 +4773,9 @@
       <c r="R37" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S37" s="5"/>
+      <c r="S37" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T37" s="5" t="s">
         <v>93</v>
       </c>
@@ -4742,7 +4795,7 @@
         <v>51</v>
       </c>
       <c r="Z37" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -4750,34 +4803,34 @@
         <v>36</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="C38" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C38" s="10" t="s">
+      <c r="D38" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="D38" s="13" t="s">
-        <v>171</v>
-      </c>
       <c r="E38" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J38" s="13"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="N38" s="6" t="s">
         <v>35</v>
@@ -4786,16 +4839,16 @@
         <v>36</v>
       </c>
       <c r="P38" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q38" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="R38" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S38" s="13" t="s">
         <v>195</v>
-      </c>
-      <c r="Q38" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="R38" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="S38" s="13" t="s">
-        <v>196</v>
       </c>
       <c r="T38" s="5" t="s">
         <v>39</v>
@@ -4815,18 +4868,18 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="19">
         <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E39" s="6">
         <v>939</v>
@@ -4835,19 +4888,19 @@
         <v>30</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>197</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="6" t="s">
         <v>198</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="2"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N39" s="6" t="s">
         <v>35</v>
@@ -4856,7 +4909,7 @@
         <v>36</v>
       </c>
       <c r="P39" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q39" s="13" t="s">
         <v>38</v>
@@ -4884,42 +4937,42 @@
         <v>51</v>
       </c>
       <c r="Z39" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="40" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="19">
+        <v>38</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C40" s="9" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="40" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="19">
-        <v>38</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="C40" s="9" t="s">
+      <c r="D40" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E40" s="6" t="s">
         <v>203</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>204</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G40" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I40" s="6" t="s">
         <v>205</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>206</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="2"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="N40" s="6" t="s">
         <v>35</v>
@@ -4928,7 +4981,7 @@
         <v>46</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="Q40" s="13" t="s">
         <v>38</v>
@@ -4956,42 +5009,42 @@
         <v>51</v>
       </c>
       <c r="Z40" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="41" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="41" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="19">
         <v>39</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D41" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>171</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>172</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="J41" s="13"/>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="N41" s="6" t="s">
         <v>35</v>
@@ -5000,7 +5053,7 @@
         <v>46</v>
       </c>
       <c r="P41" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q41" s="13" t="s">
         <v>38</v>
@@ -5008,7 +5061,9 @@
       <c r="R41" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="S41" s="13"/>
+      <c r="S41" s="13" t="s">
+        <v>494</v>
+      </c>
       <c r="T41" s="5" t="s">
         <v>93</v>
       </c>
@@ -5028,10 +5083,10 @@
         <v>51</v>
       </c>
       <c r="Z41" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="42" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="42" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="19">
         <v>40</v>
       </c>
@@ -5039,10 +5094,10 @@
         <v>26</v>
       </c>
       <c r="C42" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D42" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>215</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>87</v>
@@ -5051,13 +5106,13 @@
         <v>88</v>
       </c>
       <c r="G42" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="6" t="s">
         <v>216</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>217</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="2"/>
@@ -5068,7 +5123,7 @@
         <v>46</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q42" s="13" t="s">
         <v>38</v>
@@ -5089,7 +5144,7 @@
       <c r="Y42" s="2"/>
       <c r="Z42" s="2"/>
     </row>
-    <row r="43" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="19">
         <v>41</v>
       </c>
@@ -5097,10 +5152,10 @@
         <v>26</v>
       </c>
       <c r="C43" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="D43" s="13" t="s">
         <v>214</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>215</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>87</v>
@@ -5109,13 +5164,13 @@
         <v>88</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H43" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J43" s="13"/>
       <c r="K43" s="3"/>
@@ -5126,7 +5181,7 @@
         <v>46</v>
       </c>
       <c r="P43" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q43" s="13" t="s">
         <v>38</v>
@@ -5155,31 +5210,31 @@
         <v>26</v>
       </c>
       <c r="C44" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="D44" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="D44" s="5" t="s">
-        <v>215</v>
-      </c>
       <c r="E44" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G44" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="N44" s="6" t="s">
         <v>35</v>
@@ -5188,16 +5243,16 @@
         <v>46</v>
       </c>
       <c r="P44" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q44" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S44" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="Q44" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="R44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S44" s="5" t="s">
-        <v>225</v>
       </c>
       <c r="T44" s="5" t="s">
         <v>93</v>
@@ -5215,7 +5270,7 @@
       <c r="Y44" s="2"/>
       <c r="Z44" s="2"/>
     </row>
-    <row r="45" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="19">
         <v>43</v>
       </c>
@@ -5223,10 +5278,10 @@
         <v>26</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E45" s="7" t="s">
         <v>87</v>
@@ -5241,7 +5296,7 @@
         <v>32</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J45" s="13"/>
       <c r="K45" s="3"/>
@@ -5252,7 +5307,7 @@
         <v>46</v>
       </c>
       <c r="P45" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="Q45" s="13" t="s">
         <v>38</v>
@@ -5281,31 +5336,31 @@
         <v>26</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G46" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I46" s="6" t="s">
         <v>230</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>231</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N46" s="6" t="s">
         <v>35</v>
@@ -5314,16 +5369,16 @@
         <v>36</v>
       </c>
       <c r="P46" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R46" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S46" s="5" t="s">
         <v>233</v>
-      </c>
-      <c r="Q46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R46" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S46" s="5" t="s">
-        <v>234</v>
       </c>
       <c r="T46" s="5" t="s">
         <v>39</v>
@@ -5332,12 +5387,14 @@
         <v>46313</v>
       </c>
       <c r="V46" s="16">
-        <v>46296</v>
+        <v>46317</v>
       </c>
       <c r="W46" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="X46" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="X46" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="Y46" s="2"/>
       <c r="Z46" s="2"/>
     </row>
@@ -5349,31 +5406,31 @@
         <v>26</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H47" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J47" s="13"/>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="N47" s="6" t="s">
         <v>35</v>
@@ -5382,16 +5439,16 @@
         <v>36</v>
       </c>
       <c r="P47" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q47" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R47" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S47" s="13" t="s">
         <v>237</v>
-      </c>
-      <c r="Q47" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="R47" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="S47" s="13" t="s">
-        <v>238</v>
       </c>
       <c r="T47" s="5" t="s">
         <v>39</v>
@@ -5400,7 +5457,7 @@
         <v>46299</v>
       </c>
       <c r="V47" s="16">
-        <v>46285</v>
+        <v>46315</v>
       </c>
       <c r="W47" s="9" t="s">
         <v>49</v>
@@ -5411,7 +5468,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="19">
         <v>46</v>
       </c>
@@ -5419,31 +5476,31 @@
         <v>26</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I48" s="6" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="2"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N48" s="6" t="s">
         <v>35</v>
@@ -5452,7 +5509,7 @@
         <v>46</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q48" s="13" t="s">
         <v>38</v>
@@ -5468,18 +5525,16 @@
         <v>46299</v>
       </c>
       <c r="V48" s="16">
-        <v>46259</v>
+        <v>46054</v>
       </c>
       <c r="W48" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>50</v>
-      </c>
+      <c r="X48" s="3"/>
       <c r="Y48" s="2"/>
       <c r="Z48" s="2"/>
     </row>
-    <row r="49" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="19">
         <v>47</v>
       </c>
@@ -5487,31 +5542,31 @@
         <v>26</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H49" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J49" s="13"/>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N49" s="6" t="s">
         <v>35</v>
@@ -5520,7 +5575,7 @@
         <v>46</v>
       </c>
       <c r="P49" s="7" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q49" s="13" t="s">
         <v>38</v>
@@ -5536,7 +5591,7 @@
         <v>46299</v>
       </c>
       <c r="V49" s="16">
-        <v>46285</v>
+        <v>46331</v>
       </c>
       <c r="W49" s="9" t="s">
         <v>49</v>
@@ -5555,31 +5610,31 @@
         <v>26</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G50" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I50" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="2"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N50" s="6" t="s">
         <v>35</v>
@@ -5588,7 +5643,7 @@
         <v>36</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Q50" s="13" t="s">
         <v>38</v>
@@ -5597,7 +5652,7 @@
         <v>39</v>
       </c>
       <c r="S50" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="T50" s="5" t="s">
         <v>39</v>
@@ -5625,31 +5680,31 @@
         <v>26</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J51" s="13"/>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="N51" s="6" t="s">
         <v>35</v>
@@ -5658,16 +5713,16 @@
         <v>36</v>
       </c>
       <c r="P51" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q51" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R51" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="S51" s="13" t="s">
         <v>224</v>
-      </c>
-      <c r="Q51" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="R51" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="S51" s="13" t="s">
-        <v>225</v>
       </c>
       <c r="T51" s="5" t="s">
         <v>93</v>
@@ -5676,7 +5731,7 @@
         <v>46312</v>
       </c>
       <c r="V51" s="16">
-        <v>46280</v>
+        <v>46310</v>
       </c>
       <c r="W51" s="9" t="s">
         <v>49</v>
@@ -5684,7 +5739,9 @@
       <c r="X51" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="Y51" s="3"/>
+      <c r="Y51" s="3" t="s">
+        <v>158</v>
+      </c>
       <c r="Z51" s="3"/>
     </row>
     <row r="52" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -5695,31 +5752,31 @@
         <v>26</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G52" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I52" s="6" t="s">
         <v>249</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I52" s="6" t="s">
-        <v>250</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="2"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N52" s="6" t="s">
         <v>35</v>
@@ -5728,16 +5785,16 @@
         <v>36</v>
       </c>
       <c r="P52" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q52" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R52" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S52" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="Q52" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="R52" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S52" s="5" t="s">
-        <v>225</v>
       </c>
       <c r="T52" s="5" t="s">
         <v>93</v>
@@ -5746,7 +5803,7 @@
         <v>46344</v>
       </c>
       <c r="V52" s="16">
-        <v>46280</v>
+        <v>46320</v>
       </c>
       <c r="W52" s="9" t="s">
         <v>49</v>
@@ -5757,7 +5814,7 @@
       <c r="Y52" s="2"/>
       <c r="Z52" s="2"/>
     </row>
-    <row r="53" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="19">
         <v>51</v>
       </c>
@@ -5765,31 +5822,31 @@
         <v>26</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G53" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="H53" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I53" s="7" t="s">
         <v>252</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I53" s="7" t="s">
-        <v>253</v>
       </c>
       <c r="J53" s="13"/>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N53" s="6" t="s">
         <v>35</v>
@@ -5798,16 +5855,16 @@
         <v>36</v>
       </c>
       <c r="P53" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q53" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R53" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S53" s="13" t="s">
         <v>255</v>
-      </c>
-      <c r="Q53" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="R53" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="S53" s="13" t="s">
-        <v>256</v>
       </c>
       <c r="T53" s="5" t="s">
         <v>39</v>
@@ -5816,18 +5873,16 @@
         <v>46380</v>
       </c>
       <c r="V53" s="16">
-        <v>46291</v>
+        <v>46352</v>
       </c>
       <c r="W53" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="X53" s="3" t="s">
-        <v>50</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="X53" s="3"/>
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="19">
         <v>52</v>
       </c>
@@ -5835,31 +5890,31 @@
         <v>26</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G54" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I54" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="2"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="N54" s="6" t="s">
         <v>35</v>
@@ -5868,16 +5923,16 @@
         <v>36</v>
       </c>
       <c r="P54" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q54" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="R54" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S54" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="Q54" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="R54" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S54" s="5" t="s">
-        <v>225</v>
       </c>
       <c r="T54" s="5" t="s">
         <v>93</v>
@@ -5886,18 +5941,16 @@
         <v>46312</v>
       </c>
       <c r="V54" s="16">
-        <v>46280</v>
+        <v>46341</v>
       </c>
       <c r="W54" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="X54" s="3" t="s">
-        <v>50</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="X54" s="3"/>
       <c r="Y54" s="2"/>
       <c r="Z54" s="2"/>
     </row>
-    <row r="55" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="19">
         <v>53</v>
       </c>
@@ -5905,31 +5958,31 @@
         <v>26</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D55" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H55" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J55" s="13"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="N55" s="6" t="s">
         <v>35</v>
@@ -5938,7 +5991,7 @@
         <v>36</v>
       </c>
       <c r="P55" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q55" s="13" t="s">
         <v>39</v>
@@ -5947,7 +6000,7 @@
         <v>39</v>
       </c>
       <c r="S55" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="T55" s="5" t="s">
         <v>39</v>
@@ -5956,7 +6009,7 @@
         <v>46271</v>
       </c>
       <c r="V55" s="16">
-        <v>46290</v>
+        <v>46381</v>
       </c>
       <c r="W55" s="9" t="s">
         <v>40</v>
@@ -5965,7 +6018,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="19">
         <v>54</v>
       </c>
@@ -5973,31 +6026,31 @@
         <v>26</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G56" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I56" s="6" t="s">
         <v>265</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I56" s="6" t="s">
-        <v>266</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="2"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N56" s="6" t="s">
         <v>35</v>
@@ -6006,7 +6059,7 @@
         <v>46</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q56" s="13" t="s">
         <v>38</v>
@@ -6022,7 +6075,7 @@
         <v>46271</v>
       </c>
       <c r="V56" s="16">
-        <v>46277</v>
+        <v>46337</v>
       </c>
       <c r="W56" s="9" t="s">
         <v>40</v>
@@ -6031,7 +6084,7 @@
       <c r="Y56" s="2"/>
       <c r="Z56" s="2"/>
     </row>
-    <row r="57" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="19">
         <v>55</v>
       </c>
@@ -6039,10 +6092,10 @@
         <v>26</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D57" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>87</v>
@@ -6051,19 +6104,19 @@
         <v>88</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H57" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J57" s="13"/>
       <c r="K57" s="3"/>
       <c r="L57" s="3"/>
       <c r="M57" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="N57" s="6" t="s">
         <v>35</v>
@@ -6072,7 +6125,7 @@
         <v>46</v>
       </c>
       <c r="P57" s="7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q57" s="13" t="s">
         <v>38</v>
@@ -6095,7 +6148,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="19">
         <v>56</v>
       </c>
@@ -6103,31 +6156,31 @@
         <v>26</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F58" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G58" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I58" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N58" s="6" t="s">
         <v>35</v>
@@ -6136,7 +6189,7 @@
         <v>46</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q58" s="13" t="s">
         <v>38</v>
@@ -6152,7 +6205,7 @@
         <v>46271</v>
       </c>
       <c r="V58" s="16">
-        <v>46277</v>
+        <v>46337</v>
       </c>
       <c r="W58" s="9" t="s">
         <v>40</v>
@@ -6161,7 +6214,7 @@
       <c r="Y58" s="2"/>
       <c r="Z58" s="2"/>
     </row>
-    <row r="59" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="19">
         <v>57</v>
       </c>
@@ -6169,31 +6222,31 @@
         <v>26</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D59" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J59" s="13"/>
       <c r="K59" s="3"/>
       <c r="L59" s="3"/>
       <c r="M59" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N59" s="6" t="s">
         <v>35</v>
@@ -6202,7 +6255,7 @@
         <v>46</v>
       </c>
       <c r="P59" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q59" s="13" t="s">
         <v>38</v>
@@ -6218,7 +6271,7 @@
         <v>46271</v>
       </c>
       <c r="V59" s="16">
-        <v>46277</v>
+        <v>46337</v>
       </c>
       <c r="W59" s="9" t="s">
         <v>40</v>
@@ -6235,31 +6288,31 @@
         <v>26</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G60" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I60" s="6" t="s">
         <v>275</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I60" s="6" t="s">
-        <v>276</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="2"/>
       <c r="L60" s="2"/>
       <c r="M60" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N60" s="6" t="s">
         <v>35</v>
@@ -6268,16 +6321,16 @@
         <v>36</v>
       </c>
       <c r="P60" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q60" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R60" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="S60" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="Q60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R60" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="S60" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="T60" s="5" t="s">
         <v>39</v>
@@ -6286,7 +6339,7 @@
         <v>46313</v>
       </c>
       <c r="V60" s="16">
-        <v>46296</v>
+        <v>46320</v>
       </c>
       <c r="W60" s="9" t="s">
         <v>40</v>
@@ -6303,31 +6356,31 @@
         <v>26</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J61" s="13"/>
       <c r="K61" s="3"/>
       <c r="L61" s="3"/>
       <c r="M61" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="N61" s="6" t="s">
         <v>35</v>
@@ -6336,16 +6389,16 @@
         <v>36</v>
       </c>
       <c r="P61" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q61" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="R61" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S61" s="13" t="s">
         <v>283</v>
-      </c>
-      <c r="Q61" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="R61" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="S61" s="13" t="s">
-        <v>284</v>
       </c>
       <c r="T61" s="5" t="s">
         <v>39</v>
@@ -6363,7 +6416,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="19">
         <v>60</v>
       </c>
@@ -6371,13 +6424,13 @@
         <v>26</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>30</v>
@@ -6389,13 +6442,13 @@
         <v>32</v>
       </c>
       <c r="I62" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="2"/>
       <c r="L62" s="2"/>
       <c r="M62" s="2" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="N62" s="6" t="s">
         <v>35</v>
@@ -6404,7 +6457,7 @@
         <v>36</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q62" s="5" t="s">
         <v>39</v>
@@ -6431,7 +6484,7 @@
       <c r="Y62" s="2"/>
       <c r="Z62" s="2"/>
     </row>
-    <row r="63" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="19">
         <v>61</v>
       </c>
@@ -6439,10 +6492,10 @@
         <v>26</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D63" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>87</v>
@@ -6451,19 +6504,19 @@
         <v>88</v>
       </c>
       <c r="G63" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I63" s="7" t="s">
         <v>289</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>290</v>
       </c>
       <c r="J63" s="13"/>
       <c r="K63" s="3"/>
       <c r="L63" s="3"/>
       <c r="M63" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="N63" s="6" t="s">
         <v>35</v>
@@ -6472,7 +6525,7 @@
         <v>46</v>
       </c>
       <c r="P63" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Q63" s="13" t="s">
         <v>38</v>
@@ -6498,10 +6551,10 @@
         <v>51</v>
       </c>
       <c r="Z63" s="3" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="64" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="19">
         <v>62</v>
       </c>
@@ -6509,25 +6562,25 @@
         <v>26</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G64" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I64" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="2"/>
@@ -6538,7 +6591,7 @@
         <v>36</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q64" s="13" t="s">
         <v>38</v>
@@ -6561,7 +6614,7 @@
       <c r="Y64" s="2"/>
       <c r="Z64" s="2"/>
     </row>
-    <row r="65" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="19">
         <v>63</v>
       </c>
@@ -6569,10 +6622,10 @@
         <v>26</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D65" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>87</v>
@@ -6581,19 +6634,19 @@
         <v>88</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J65" s="13"/>
       <c r="K65" s="3"/>
       <c r="L65" s="3"/>
       <c r="M65" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="N65" s="6" t="s">
         <v>35</v>
@@ -6602,7 +6655,7 @@
         <v>46</v>
       </c>
       <c r="P65" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q65" s="13" t="s">
         <v>38</v>
@@ -6623,7 +6676,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="19">
         <v>64</v>
       </c>
@@ -6631,10 +6684,10 @@
         <v>26</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>87</v>
@@ -6643,13 +6696,13 @@
         <v>88</v>
       </c>
       <c r="G66" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I66" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="2"/>
@@ -6687,31 +6740,31 @@
         <v>26</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D67" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J67" s="13"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N67" s="6" t="s">
         <v>35</v>
@@ -6720,7 +6773,7 @@
         <v>36</v>
       </c>
       <c r="P67" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q67" s="13" t="s">
         <v>39</v>
@@ -6738,16 +6791,16 @@
         <v>46313</v>
       </c>
       <c r="V67" s="16">
-        <v>46247</v>
+        <v>46326</v>
       </c>
       <c r="W67" s="9" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="19">
         <v>66</v>
       </c>
@@ -6755,10 +6808,10 @@
         <v>26</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>87</v>
@@ -6767,13 +6820,13 @@
         <v>88</v>
       </c>
       <c r="G68" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I68" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J68" s="5"/>
       <c r="K68" s="2"/>
@@ -6784,7 +6837,7 @@
         <v>46</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q68" s="13" t="s">
         <v>38</v>
@@ -6813,31 +6866,31 @@
         <v>26</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H69" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J69" s="13"/>
       <c r="K69" s="3"/>
       <c r="L69" s="3"/>
       <c r="M69" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="N69" s="6" t="s">
         <v>35</v>
@@ -6846,7 +6899,7 @@
         <v>36</v>
       </c>
       <c r="P69" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q69" s="13" t="s">
         <v>39</v>
@@ -6855,7 +6908,7 @@
         <v>38</v>
       </c>
       <c r="S69" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="T69" s="5" t="s">
         <v>39</v>
@@ -6864,7 +6917,7 @@
         <v>46313</v>
       </c>
       <c r="V69" s="16">
-        <v>46277</v>
+        <v>46317</v>
       </c>
       <c r="W69" s="9" t="s">
         <v>40</v>
@@ -6881,31 +6934,31 @@
         <v>26</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G70" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I70" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J70" s="5"/>
       <c r="K70" s="2"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N70" s="6" t="s">
         <v>35</v>
@@ -6914,7 +6967,7 @@
         <v>36</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q70" s="5" t="s">
         <v>39</v>
@@ -6932,10 +6985,10 @@
         <v>46313</v>
       </c>
       <c r="V70" s="16">
-        <v>46247</v>
+        <v>46326</v>
       </c>
       <c r="W70" s="9" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="X70" s="2"/>
       <c r="Y70" s="2"/>
@@ -6949,31 +7002,31 @@
         <v>26</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D71" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H71" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="J71" s="13"/>
       <c r="K71" s="3"/>
       <c r="L71" s="3"/>
       <c r="M71" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N71" s="6" t="s">
         <v>35</v>
@@ -6982,7 +7035,7 @@
         <v>36</v>
       </c>
       <c r="P71" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q71" s="13" t="s">
         <v>39</v>
@@ -7000,16 +7053,16 @@
         <v>46313</v>
       </c>
       <c r="V71" s="16">
-        <v>46247</v>
+        <v>46326</v>
       </c>
       <c r="W71" s="9" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="X71" s="3"/>
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="19">
         <v>70</v>
       </c>
@@ -7017,10 +7070,10 @@
         <v>26</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>93</v>
@@ -7029,19 +7082,19 @@
         <v>88</v>
       </c>
       <c r="G72" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I72" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="J72" s="5"/>
       <c r="K72" s="2"/>
       <c r="L72" s="2"/>
       <c r="M72" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N72" s="6" t="s">
         <v>35</v>
@@ -7050,7 +7103,7 @@
         <v>46</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="Q72" s="13" t="s">
         <v>38</v>
@@ -7079,31 +7132,31 @@
         <v>26</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D73" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H73" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J73" s="13"/>
       <c r="K73" s="3"/>
       <c r="L73" s="3"/>
       <c r="M73" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="N73" s="6" t="s">
         <v>35</v>
@@ -7112,7 +7165,7 @@
         <v>36</v>
       </c>
       <c r="P73" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q73" s="13" t="s">
         <v>39</v>
@@ -7130,10 +7183,10 @@
         <v>46328</v>
       </c>
       <c r="V73" s="16">
-        <v>46239</v>
+        <v>46315</v>
       </c>
       <c r="W73" s="9" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="X73" s="3"/>
       <c r="Y73" s="3"/>
@@ -7147,13 +7200,13 @@
         <v>26</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>30</v>
@@ -7165,13 +7218,13 @@
         <v>32</v>
       </c>
       <c r="I74" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J74" s="5"/>
       <c r="K74" s="2"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N74" s="6" t="s">
         <v>35</v>
@@ -7180,7 +7233,7 @@
         <v>36</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Q74" s="5" t="s">
         <v>39</v>
@@ -7196,7 +7249,7 @@
         <v>46313</v>
       </c>
       <c r="V74" s="16">
-        <v>46296</v>
+        <v>46320</v>
       </c>
       <c r="W74" s="9" t="s">
         <v>40</v>
@@ -7205,7 +7258,7 @@
       <c r="Y74" s="2"/>
       <c r="Z74" s="2"/>
     </row>
-    <row r="75" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="19">
         <v>73</v>
       </c>
@@ -7213,13 +7266,13 @@
         <v>26</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D75" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>30</v>
@@ -7231,13 +7284,13 @@
         <v>32</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="J75" s="13"/>
       <c r="K75" s="3"/>
       <c r="L75" s="3"/>
       <c r="M75" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="N75" s="6" t="s">
         <v>35</v>
@@ -7246,7 +7299,7 @@
         <v>36</v>
       </c>
       <c r="P75" s="7" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q75" s="13" t="s">
         <v>39</v>
@@ -7255,7 +7308,7 @@
         <v>38</v>
       </c>
       <c r="S75" s="13" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="T75" s="5" t="s">
         <v>39</v>
@@ -7264,7 +7317,7 @@
         <v>46271</v>
       </c>
       <c r="V75" s="16">
-        <v>46290</v>
+        <v>46381</v>
       </c>
       <c r="W75" s="9" t="s">
         <v>40</v>
@@ -7273,7 +7326,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="19">
         <v>74</v>
       </c>
@@ -7281,31 +7334,31 @@
         <v>26</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E76" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="G76" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="G76" s="9" t="s">
+      <c r="H76" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I76" s="6" t="s">
         <v>324</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I76" s="6" t="s">
-        <v>325</v>
       </c>
       <c r="J76" s="5"/>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
       <c r="M76" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N76" s="6" t="s">
         <v>35</v>
@@ -7314,7 +7367,7 @@
         <v>46</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q76" s="13" t="s">
         <v>38</v>
@@ -7330,7 +7383,7 @@
         <v>46296</v>
       </c>
       <c r="V76" s="16">
-        <v>46247</v>
+        <v>46054</v>
       </c>
       <c r="W76" s="9" t="s">
         <v>40</v>
@@ -7339,7 +7392,7 @@
       <c r="Y76" s="2"/>
       <c r="Z76" s="2"/>
     </row>
-    <row r="77" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="19">
         <v>75</v>
       </c>
@@ -7347,31 +7400,31 @@
         <v>26</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D77" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E77" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="F77" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="G77" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="G77" s="3" t="s">
-        <v>324</v>
-      </c>
       <c r="H77" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J77" s="13"/>
       <c r="K77" s="3"/>
       <c r="L77" s="3"/>
       <c r="M77" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="N77" s="6" t="s">
         <v>35</v>
@@ -7380,7 +7433,7 @@
         <v>46</v>
       </c>
       <c r="P77" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q77" s="13" t="s">
         <v>38</v>
@@ -7396,7 +7449,7 @@
         <v>46296</v>
       </c>
       <c r="V77" s="16">
-        <v>46247</v>
+        <v>46054</v>
       </c>
       <c r="W77" s="9" t="s">
         <v>49</v>
@@ -7408,10 +7461,10 @@
         <v>51</v>
       </c>
       <c r="Z77" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="78" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="19">
         <v>76</v>
       </c>
@@ -7419,31 +7472,31 @@
         <v>26</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="F78" s="2" t="s">
+      <c r="G78" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="G78" s="9" t="s">
-        <v>324</v>
-      </c>
       <c r="H78" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I78" s="6" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J78" s="5"/>
       <c r="K78" s="2"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N78" s="6" t="s">
         <v>35</v>
@@ -7452,7 +7505,7 @@
         <v>46</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="Q78" s="13" t="s">
         <v>38</v>
@@ -7468,7 +7521,7 @@
         <v>46296</v>
       </c>
       <c r="V78" s="16">
-        <v>46247</v>
+        <v>46054</v>
       </c>
       <c r="W78" s="9" t="s">
         <v>40</v>
@@ -7477,7 +7530,7 @@
       <c r="Y78" s="2"/>
       <c r="Z78" s="2"/>
     </row>
-    <row r="79" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="19">
         <v>77</v>
       </c>
@@ -7485,13 +7538,13 @@
         <v>26</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D79" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>30</v>
@@ -7503,13 +7556,13 @@
         <v>32</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J79" s="13"/>
       <c r="K79" s="3"/>
       <c r="L79" s="3"/>
       <c r="M79" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N79" s="6" t="s">
         <v>35</v>
@@ -7518,7 +7571,7 @@
         <v>36</v>
       </c>
       <c r="P79" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q79" s="13" t="s">
         <v>38</v>
@@ -7534,7 +7587,7 @@
         <v>46315</v>
       </c>
       <c r="V79" s="16">
-        <v>46247</v>
+        <v>46339</v>
       </c>
       <c r="W79" s="9" t="s">
         <v>40</v>
@@ -7543,7 +7596,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="19">
         <v>78</v>
       </c>
@@ -7551,31 +7604,31 @@
         <v>26</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G80" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I80" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J80" s="5"/>
       <c r="K80" s="2"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="N80" s="6" t="s">
         <v>35</v>
@@ -7584,7 +7637,7 @@
         <v>46</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Q80" s="13" t="s">
         <v>38</v>
@@ -7600,7 +7653,7 @@
         <v>46296</v>
       </c>
       <c r="V80" s="16">
-        <v>46247</v>
+        <v>46327</v>
       </c>
       <c r="W80" s="9" t="s">
         <v>49</v>
@@ -7611,7 +7664,7 @@
       <c r="Y80" s="2"/>
       <c r="Z80" s="2"/>
     </row>
-    <row r="81" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="19">
         <v>79</v>
       </c>
@@ -7619,31 +7672,31 @@
         <v>26</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H81" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="J81" s="13"/>
       <c r="K81" s="3"/>
       <c r="L81" s="3"/>
       <c r="M81" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N81" s="6" t="s">
         <v>35</v>
@@ -7652,7 +7705,7 @@
         <v>46</v>
       </c>
       <c r="P81" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q81" s="13" t="s">
         <v>38</v>
@@ -7679,7 +7732,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="19">
         <v>80</v>
       </c>
@@ -7687,31 +7740,31 @@
         <v>26</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I82" s="6" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="J82" s="5"/>
       <c r="K82" s="2"/>
       <c r="L82" s="2"/>
       <c r="M82" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N82" s="6" t="s">
         <v>35</v>
@@ -7720,7 +7773,7 @@
         <v>46</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q82" s="13" t="s">
         <v>38</v>
@@ -7747,7 +7800,7 @@
       <c r="Y82" s="2"/>
       <c r="Z82" s="2"/>
     </row>
-    <row r="83" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="19">
         <v>81</v>
       </c>
@@ -7755,31 +7808,31 @@
         <v>26</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D83" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J83" s="13"/>
       <c r="K83" s="3"/>
       <c r="L83" s="3"/>
       <c r="M83" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N83" s="6" t="s">
         <v>35</v>
@@ -7788,7 +7841,7 @@
         <v>46</v>
       </c>
       <c r="P83" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q83" s="13" t="s">
         <v>38</v>
@@ -7815,7 +7868,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="19">
         <v>82</v>
       </c>
@@ -7823,13 +7876,13 @@
         <v>26</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>30</v>
@@ -7841,13 +7894,13 @@
         <v>32</v>
       </c>
       <c r="I84" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J84" s="5"/>
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
       <c r="M84" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N84" s="6" t="s">
         <v>35</v>
@@ -7856,7 +7909,7 @@
         <v>46</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q84" s="13" t="s">
         <v>38</v>
@@ -7883,7 +7936,7 @@
       <c r="Y84" s="2"/>
       <c r="Z84" s="2"/>
     </row>
-    <row r="85" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="19">
         <v>83</v>
       </c>
@@ -7891,13 +7944,13 @@
         <v>26</v>
       </c>
       <c r="C85" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D85" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>30</v>
@@ -7909,13 +7962,13 @@
         <v>32</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="J85" s="13"/>
       <c r="K85" s="3"/>
       <c r="L85" s="3"/>
       <c r="M85" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="N85" s="6" t="s">
         <v>35</v>
@@ -7924,7 +7977,7 @@
         <v>46</v>
       </c>
       <c r="P85" s="7" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q85" s="13" t="s">
         <v>38</v>
@@ -7951,7 +8004,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="19">
         <v>84</v>
       </c>
@@ -7959,13 +8012,13 @@
         <v>26</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>30</v>
@@ -7977,13 +8030,13 @@
         <v>32</v>
       </c>
       <c r="I86" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="J86" s="5"/>
       <c r="K86" s="2"/>
       <c r="L86" s="2"/>
       <c r="M86" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="N86" s="6" t="s">
         <v>35</v>
@@ -7992,7 +8045,7 @@
         <v>46</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="Q86" s="13" t="s">
         <v>38</v>
@@ -8027,31 +8080,31 @@
         <v>26</v>
       </c>
       <c r="C87" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D87" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>30</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J87" s="13"/>
       <c r="K87" s="3"/>
       <c r="L87" s="3"/>
       <c r="M87" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="N87" s="6" t="s">
         <v>35</v>
@@ -8060,16 +8113,16 @@
         <v>36</v>
       </c>
       <c r="P87" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q87" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="R87" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="S87" s="13" t="s">
         <v>345</v>
-      </c>
-      <c r="Q87" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="R87" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="S87" s="13" t="s">
-        <v>346</v>
       </c>
       <c r="T87" s="5" t="s">
         <v>39</v>
@@ -8078,16 +8131,16 @@
         <v>46313</v>
       </c>
       <c r="V87" s="16">
-        <v>46247</v>
+        <v>46326</v>
       </c>
       <c r="W87" s="9" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="X87" s="3"/>
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="19">
         <v>86</v>
       </c>
@@ -8095,31 +8148,31 @@
         <v>26</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>30</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I88" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J88" s="5"/>
       <c r="K88" s="2"/>
       <c r="L88" s="2"/>
       <c r="M88" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="N88" s="6" t="s">
         <v>35</v>
@@ -8128,16 +8181,16 @@
         <v>36</v>
       </c>
       <c r="P88" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="Q88" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R88" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S88" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="Q88" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R88" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S88" s="5" t="s">
-        <v>279</v>
       </c>
       <c r="T88" s="5" t="s">
         <v>39</v>
@@ -8146,7 +8199,7 @@
         <v>46313</v>
       </c>
       <c r="V88" s="16">
-        <v>46278</v>
+        <v>46431</v>
       </c>
       <c r="W88" s="9" t="s">
         <v>40</v>
@@ -8163,13 +8216,13 @@
         <v>26</v>
       </c>
       <c r="C89" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D89" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>30</v>
@@ -8181,13 +8234,13 @@
         <v>32</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J89" s="13"/>
       <c r="K89" s="3"/>
       <c r="L89" s="3"/>
       <c r="M89" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N89" s="6" t="s">
         <v>35</v>
@@ -8196,7 +8249,7 @@
         <v>36</v>
       </c>
       <c r="P89" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q89" s="13" t="s">
         <v>39</v>
@@ -8226,10 +8279,10 @@
         <v>51</v>
       </c>
       <c r="Z89" s="3" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="90" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="90" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="19">
         <v>88</v>
       </c>
@@ -8237,13 +8290,13 @@
         <v>26</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>30</v>
@@ -8255,13 +8308,13 @@
         <v>32</v>
       </c>
       <c r="I90" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="J90" s="5"/>
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
       <c r="M90" s="2" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N90" s="6" t="s">
         <v>35</v>
@@ -8270,7 +8323,7 @@
         <v>36</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q90" s="5" t="s">
         <v>39</v>
@@ -8288,7 +8341,7 @@
         <v>46318</v>
       </c>
       <c r="V90" s="16">
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="W90" s="9" t="s">
         <v>49</v>
@@ -8299,7 +8352,7 @@
       <c r="Y90" s="2"/>
       <c r="Z90" s="2"/>
     </row>
-    <row r="91" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="19">
         <v>89</v>
       </c>
@@ -8307,13 +8360,13 @@
         <v>26</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D91" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>30</v>
@@ -8325,13 +8378,13 @@
         <v>32</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J91" s="13"/>
       <c r="K91" s="3"/>
       <c r="L91" s="3"/>
       <c r="M91" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N91" s="6" t="s">
         <v>35</v>
@@ -8340,7 +8393,7 @@
         <v>36</v>
       </c>
       <c r="P91" s="7" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Q91" s="13" t="s">
         <v>39</v>
@@ -8358,7 +8411,7 @@
         <v>46318</v>
       </c>
       <c r="V91" s="16">
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="W91" s="9" t="s">
         <v>49</v>
@@ -8377,13 +8430,13 @@
         <v>26</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>30</v>
@@ -8395,13 +8448,13 @@
         <v>32</v>
       </c>
       <c r="I92" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="J92" s="5"/>
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
       <c r="M92" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N92" s="6" t="s">
         <v>35</v>
@@ -8410,7 +8463,7 @@
         <v>36</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q92" s="5" t="s">
         <v>39</v>
@@ -8419,7 +8472,7 @@
         <v>39</v>
       </c>
       <c r="S92" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="T92" s="5" t="s">
         <v>39</v>
@@ -8439,7 +8492,7 @@
       <c r="Y92" s="2"/>
       <c r="Z92" s="2"/>
     </row>
-    <row r="93" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="19">
         <v>91</v>
       </c>
@@ -8447,13 +8500,13 @@
         <v>26</v>
       </c>
       <c r="C93" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>30</v>
@@ -8465,13 +8518,13 @@
         <v>32</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J93" s="13"/>
       <c r="K93" s="3"/>
       <c r="L93" s="3"/>
       <c r="M93" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="N93" s="6" t="s">
         <v>35</v>
@@ -8480,7 +8533,7 @@
         <v>36</v>
       </c>
       <c r="P93" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q93" s="13" t="s">
         <v>39</v>
@@ -8489,7 +8542,7 @@
         <v>38</v>
       </c>
       <c r="S93" s="13" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="T93" s="5" t="s">
         <v>93</v>
@@ -8498,16 +8551,18 @@
         <v>46348</v>
       </c>
       <c r="V93" s="16">
-        <v>46310</v>
+        <v>46371</v>
       </c>
       <c r="W93" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="X93" s="3"/>
+        <v>49</v>
+      </c>
+      <c r="X93" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="19">
         <v>92</v>
       </c>
@@ -8515,13 +8570,13 @@
         <v>26</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>30</v>
@@ -8533,13 +8588,13 @@
         <v>32</v>
       </c>
       <c r="I94" s="6" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J94" s="5"/>
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
       <c r="M94" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="N94" s="6" t="s">
         <v>35</v>
@@ -8548,7 +8603,7 @@
         <v>36</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="Q94" s="5" t="s">
         <v>39</v>
@@ -8557,7 +8612,7 @@
         <v>38</v>
       </c>
       <c r="S94" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="T94" s="5" t="s">
         <v>93</v>
@@ -8566,12 +8621,14 @@
         <v>46348</v>
       </c>
       <c r="V94" s="16">
-        <v>46310</v>
+        <v>46371</v>
       </c>
       <c r="W94" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="X94" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="X94" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="Y94" s="2"/>
       <c r="Z94" s="2"/>
     </row>
@@ -8583,13 +8640,13 @@
         <v>26</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>30</v>
@@ -8601,13 +8658,13 @@
         <v>32</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="J95" s="13"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="N95" s="6" t="s">
         <v>35</v>
@@ -8616,7 +8673,7 @@
         <v>36</v>
       </c>
       <c r="P95" s="7" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="Q95" s="13" t="s">
         <v>39</v>
@@ -8625,7 +8682,7 @@
         <v>39</v>
       </c>
       <c r="S95" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="T95" s="5" t="s">
         <v>39</v>
@@ -8634,16 +8691,16 @@
         <v>46348</v>
       </c>
       <c r="V95" s="16">
-        <v>46247</v>
+        <v>46326</v>
       </c>
       <c r="W95" s="9" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="19">
         <v>94</v>
       </c>
@@ -8651,13 +8708,13 @@
         <v>26</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>30</v>
@@ -8669,13 +8726,13 @@
         <v>32</v>
       </c>
       <c r="I96" s="6" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="J96" s="5"/>
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
       <c r="M96" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="N96" s="6" t="s">
         <v>35</v>
@@ -8684,7 +8741,7 @@
         <v>36</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="Q96" s="5" t="s">
         <v>39</v>
@@ -8702,12 +8759,14 @@
         <v>46348</v>
       </c>
       <c r="V96" s="16">
-        <v>46310</v>
+        <v>46341</v>
       </c>
       <c r="W96" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="X96" s="2"/>
+        <v>49</v>
+      </c>
+      <c r="X96" s="3" t="s">
+        <v>50</v>
+      </c>
       <c r="Y96" s="2"/>
       <c r="Z96" s="2"/>
     </row>
@@ -8719,13 +8778,13 @@
         <v>26</v>
       </c>
       <c r="C97" s="10" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>30</v>
@@ -8737,13 +8796,13 @@
         <v>32</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="J97" s="13"/>
       <c r="K97" s="3"/>
       <c r="L97" s="3"/>
       <c r="M97" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N97" s="6" t="s">
         <v>35</v>
@@ -8752,7 +8811,7 @@
         <v>36</v>
       </c>
       <c r="P97" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="Q97" s="13" t="s">
         <v>39</v>
@@ -8761,7 +8820,7 @@
         <v>39</v>
       </c>
       <c r="S97" s="13" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="T97" s="5" t="s">
         <v>39</v>
@@ -8779,7 +8838,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" spans="1:26" ht="79.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:26" ht="79.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="19">
         <v>96</v>
       </c>
@@ -8787,10 +8846,10 @@
         <v>26</v>
       </c>
       <c r="C98" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D98" s="5" t="s">
         <v>369</v>
-      </c>
-      <c r="D98" s="5" t="s">
-        <v>370</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>93</v>
@@ -8805,10 +8864,10 @@
         <v>32</v>
       </c>
       <c r="I98" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="J98" s="5" t="s">
         <v>371</v>
-      </c>
-      <c r="J98" s="5" t="s">
-        <v>372</v>
       </c>
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
@@ -8818,7 +8877,7 @@
         <v>46</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="Q98" s="5" t="s">
         <v>38</v>
@@ -8838,10 +8897,10 @@
         <v>49</v>
       </c>
       <c r="X98" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Y98" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="Z98" s="2"/>
     </row>
@@ -8851,10 +8910,10 @@
       </c>
       <c r="B99" s="7"/>
       <c r="C99" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>93</v>
@@ -8863,21 +8922,21 @@
         <v>30</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H99" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="I99" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="I99" s="7" t="s">
+      <c r="J99" s="13" t="s">
         <v>377</v>
-      </c>
-      <c r="J99" s="13" t="s">
-        <v>378</v>
       </c>
       <c r="K99" s="3"/>
       <c r="L99" s="3"/>
       <c r="M99" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N99" s="6" t="s">
         <v>35</v>
@@ -8886,7 +8945,7 @@
         <v>36</v>
       </c>
       <c r="P99" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q99" s="13" t="s">
         <v>39</v>
@@ -8911,7 +8970,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="19">
         <v>98</v>
       </c>
@@ -8919,10 +8978,10 @@
         <v>26</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>93</v>
@@ -8937,15 +8996,15 @@
         <v>32</v>
       </c>
       <c r="I100" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="J100" s="5" t="s">
         <v>382</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>383</v>
       </c>
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
       <c r="M100" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="N100" s="6" t="s">
         <v>35</v>
@@ -8954,7 +9013,7 @@
         <v>36</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q100" s="28" t="s">
         <v>38</v>
@@ -8962,7 +9021,9 @@
       <c r="R100" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S100" s="5"/>
+      <c r="S100" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T100" s="5" t="s">
         <v>93</v>
       </c>
@@ -8977,7 +9038,7 @@
       <c r="Y100" s="2"/>
       <c r="Z100" s="2"/>
     </row>
-    <row r="101" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="19">
         <v>99</v>
       </c>
@@ -8985,10 +9046,10 @@
         <v>26</v>
       </c>
       <c r="C101" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>93</v>
@@ -9003,15 +9064,15 @@
         <v>32</v>
       </c>
       <c r="I101" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="J101" s="13" t="s">
         <v>385</v>
-      </c>
-      <c r="J101" s="13" t="s">
-        <v>386</v>
       </c>
       <c r="K101" s="3"/>
       <c r="L101" s="3"/>
       <c r="M101" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N101" s="6" t="s">
         <v>35</v>
@@ -9020,7 +9081,7 @@
         <v>46</v>
       </c>
       <c r="P101" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q101" s="28" t="s">
         <v>38</v>
@@ -9028,7 +9089,9 @@
       <c r="R101" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S101" s="13"/>
+      <c r="S101" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T101" s="5" t="s">
         <v>93</v>
       </c>
@@ -9043,7 +9106,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="19">
         <v>100</v>
       </c>
@@ -9051,10 +9114,10 @@
         <v>26</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>93</v>
@@ -9069,15 +9132,15 @@
         <v>32</v>
       </c>
       <c r="I102" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="J102" s="5" t="s">
         <v>389</v>
-      </c>
-      <c r="J102" s="5" t="s">
-        <v>390</v>
       </c>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
       <c r="M102" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N102" s="6" t="s">
         <v>35</v>
@@ -9086,7 +9149,7 @@
         <v>46</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q102" s="28" t="s">
         <v>38</v>
@@ -9094,7 +9157,9 @@
       <c r="R102" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S102" s="5"/>
+      <c r="S102" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T102" s="5" t="s">
         <v>93</v>
       </c>
@@ -9117,13 +9182,13 @@
         <v>26</v>
       </c>
       <c r="C103" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>30</v>
@@ -9135,15 +9200,15 @@
         <v>32</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J103" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K103" s="3"/>
       <c r="L103" s="3"/>
       <c r="M103" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N103" s="6" t="s">
         <v>35</v>
@@ -9152,7 +9217,7 @@
         <v>36</v>
       </c>
       <c r="P103" s="7" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="Q103" s="28" t="s">
         <v>38</v>
@@ -9160,7 +9225,9 @@
       <c r="R103" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="S103" s="13"/>
+      <c r="S103" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T103" s="5" t="s">
         <v>93</v>
       </c>
@@ -9182,13 +9249,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C104" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D104" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="C104" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>393</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>93</v>
@@ -9197,21 +9264,21 @@
         <v>30</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H104" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="I104" s="6" t="s">
         <v>394</v>
       </c>
-      <c r="I104" s="6" t="s">
+      <c r="J104" s="5" t="s">
         <v>395</v>
-      </c>
-      <c r="J104" s="5" t="s">
-        <v>396</v>
       </c>
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
       <c r="M104" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N104" s="6" t="s">
         <v>35</v>
@@ -9220,7 +9287,7 @@
         <v>36</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q104" s="5" t="s">
         <v>39</v>
@@ -9254,13 +9321,13 @@
         <v>103</v>
       </c>
       <c r="B105" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D105" s="13" t="s">
         <v>392</v>
-      </c>
-      <c r="C105" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D105" s="13" t="s">
-        <v>393</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>93</v>
@@ -9269,21 +9336,21 @@
         <v>30</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H105" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I105" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="J105" s="13" t="s">
         <v>397</v>
-      </c>
-      <c r="J105" s="13" t="s">
-        <v>398</v>
       </c>
       <c r="K105" s="3"/>
       <c r="L105" s="3"/>
       <c r="M105" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N105" s="6" t="s">
         <v>35</v>
@@ -9292,7 +9359,7 @@
         <v>36</v>
       </c>
       <c r="P105" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q105" s="13" t="s">
         <v>39</v>
@@ -9326,13 +9393,13 @@
         <v>104</v>
       </c>
       <c r="B106" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C106" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D106" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="C106" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>393</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>93</v>
@@ -9341,21 +9408,21 @@
         <v>30</v>
       </c>
       <c r="G106" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I106" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="J106" s="5" t="s">
         <v>399</v>
-      </c>
-      <c r="J106" s="5" t="s">
-        <v>400</v>
       </c>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
       <c r="M106" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N106" s="6" t="s">
         <v>35</v>
@@ -9364,7 +9431,7 @@
         <v>36</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q106" s="5" t="s">
         <v>39</v>
@@ -9396,13 +9463,13 @@
         <v>105</v>
       </c>
       <c r="B107" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D107" s="13" t="s">
         <v>392</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D107" s="13" t="s">
-        <v>393</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>93</v>
@@ -9411,21 +9478,21 @@
         <v>30</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H107" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="J107" s="13" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K107" s="3"/>
       <c r="L107" s="3"/>
       <c r="M107" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N107" s="6" t="s">
         <v>35</v>
@@ -9434,7 +9501,7 @@
         <v>36</v>
       </c>
       <c r="P107" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q107" s="13" t="s">
         <v>39</v>
@@ -9468,13 +9535,13 @@
         <v>106</v>
       </c>
       <c r="B108" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C108" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D108" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="C108" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>393</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>93</v>
@@ -9483,21 +9550,21 @@
         <v>30</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I108" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="J108" s="5" t="s">
         <v>402</v>
-      </c>
-      <c r="J108" s="5" t="s">
-        <v>403</v>
       </c>
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
       <c r="M108" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N108" s="6" t="s">
         <v>35</v>
@@ -9506,7 +9573,7 @@
         <v>36</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q108" s="5" t="s">
         <v>39</v>
@@ -9538,13 +9605,13 @@
         <v>107</v>
       </c>
       <c r="B109" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D109" s="13" t="s">
         <v>392</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D109" s="13" t="s">
-        <v>393</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>93</v>
@@ -9553,21 +9620,21 @@
         <v>30</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H109" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="J109" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K109" s="3"/>
       <c r="L109" s="3"/>
       <c r="M109" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N109" s="6" t="s">
         <v>35</v>
@@ -9576,7 +9643,7 @@
         <v>36</v>
       </c>
       <c r="P109" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q109" s="13" t="s">
         <v>39</v>
@@ -9608,13 +9675,13 @@
         <v>108</v>
       </c>
       <c r="B110" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="C110" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="D110" s="5" t="s">
         <v>392</v>
-      </c>
-      <c r="C110" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="D110" s="5" t="s">
-        <v>393</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>93</v>
@@ -9623,21 +9690,21 @@
         <v>30</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I110" s="6" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="J110" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
       <c r="M110" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N110" s="6" t="s">
         <v>35</v>
@@ -9646,7 +9713,7 @@
         <v>36</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q110" s="5" t="s">
         <v>39</v>
@@ -9680,13 +9747,13 @@
         <v>109</v>
       </c>
       <c r="B111" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="D111" s="13" t="s">
         <v>392</v>
-      </c>
-      <c r="C111" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>393</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>93</v>
@@ -9695,21 +9762,21 @@
         <v>30</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H111" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J111" s="13" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="K111" s="3"/>
       <c r="L111" s="3"/>
       <c r="M111" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N111" s="6" t="s">
         <v>35</v>
@@ -9718,7 +9785,7 @@
         <v>36</v>
       </c>
       <c r="P111" s="7" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q111" s="13" t="s">
         <v>39</v>
@@ -9750,13 +9817,13 @@
         <v>110</v>
       </c>
       <c r="B112" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C112" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C112" s="9" t="s">
-        <v>170</v>
-      </c>
       <c r="D112" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>93</v>
@@ -9765,21 +9832,21 @@
         <v>30</v>
       </c>
       <c r="G112" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I112" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="J112" s="5" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
       <c r="M112" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="N112" s="6" t="s">
         <v>35</v>
@@ -9788,7 +9855,7 @@
         <v>36</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="Q112" s="5" t="s">
         <v>39</v>
@@ -9815,7 +9882,7 @@
       <c r="Y112" s="2"/>
       <c r="Z112" s="2"/>
     </row>
-    <row r="113" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="19">
         <v>111</v>
       </c>
@@ -9823,10 +9890,10 @@
         <v>26</v>
       </c>
       <c r="C113" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D113" s="13" t="s">
         <v>408</v>
-      </c>
-      <c r="D113" s="13" t="s">
-        <v>409</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>93</v>
@@ -9835,19 +9902,19 @@
         <v>88</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H113" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J113" s="13"/>
       <c r="K113" s="3"/>
       <c r="L113" s="3"/>
       <c r="M113" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N113" s="6" t="s">
         <v>63</v>
@@ -9856,7 +9923,7 @@
         <v>36</v>
       </c>
       <c r="P113" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q113" s="28" t="s">
         <v>38</v>
@@ -9879,7 +9946,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="19">
         <v>112</v>
       </c>
@@ -9887,10 +9954,10 @@
         <v>26</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>93</v>
@@ -9899,21 +9966,21 @@
         <v>30</v>
       </c>
       <c r="G114" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H114" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I114" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J114" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
       <c r="M114" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N114" s="6" t="s">
         <v>63</v>
@@ -9922,7 +9989,7 @@
         <v>36</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q114" s="28" t="s">
         <v>38</v>
@@ -9945,7 +10012,7 @@
       <c r="Y114" s="2"/>
       <c r="Z114" s="2"/>
     </row>
-    <row r="115" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="19">
         <v>113</v>
       </c>
@@ -9953,10 +10020,10 @@
         <v>26</v>
       </c>
       <c r="C115" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D115" s="13" t="s">
         <v>408</v>
-      </c>
-      <c r="D115" s="13" t="s">
-        <v>409</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>93</v>
@@ -9965,21 +10032,21 @@
         <v>88</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H115" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I115" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="J115" s="13" t="s">
         <v>417</v>
-      </c>
-      <c r="J115" s="13" t="s">
-        <v>418</v>
       </c>
       <c r="K115" s="3"/>
       <c r="L115" s="3"/>
       <c r="M115" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N115" s="6" t="s">
         <v>63</v>
@@ -9988,7 +10055,7 @@
         <v>36</v>
       </c>
       <c r="P115" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q115" s="28" t="s">
         <v>38</v>
@@ -10011,18 +10078,18 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="19">
         <v>114</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C116" s="9" t="s">
+        <v>407</v>
+      </c>
+      <c r="D116" s="5" t="s">
         <v>408</v>
-      </c>
-      <c r="D116" s="5" t="s">
-        <v>409</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>93</v>
@@ -10031,19 +10098,19 @@
         <v>88</v>
       </c>
       <c r="G116" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H116" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I116" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="J116" s="5"/>
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
       <c r="M116" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N116" s="6" t="s">
         <v>63</v>
@@ -10052,7 +10119,7 @@
         <v>36</v>
       </c>
       <c r="P116" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q116" s="28" t="s">
         <v>38</v>
@@ -10075,18 +10142,18 @@
       <c r="Y116" s="2"/>
       <c r="Z116" s="2"/>
     </row>
-    <row r="117" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="19">
         <v>115</v>
       </c>
       <c r="B117" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C117" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="D117" s="13" t="s">
         <v>408</v>
-      </c>
-      <c r="D117" s="13" t="s">
-        <v>409</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>93</v>
@@ -10095,21 +10162,21 @@
         <v>88</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H117" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I117" s="7" t="s">
+        <v>416</v>
+      </c>
+      <c r="J117" s="13" t="s">
         <v>417</v>
-      </c>
-      <c r="J117" s="13" t="s">
-        <v>418</v>
       </c>
       <c r="K117" s="3"/>
       <c r="L117" s="3"/>
       <c r="M117" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N117" s="6" t="s">
         <v>63</v>
@@ -10118,7 +10185,7 @@
         <v>36</v>
       </c>
       <c r="P117" s="7" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q117" s="28" t="s">
         <v>38</v>
@@ -10141,7 +10208,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="19">
         <v>116</v>
       </c>
@@ -10149,7 +10216,7 @@
         <v>26</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D118" s="5" t="s">
         <v>87</v>
@@ -10167,7 +10234,7 @@
         <v>32</v>
       </c>
       <c r="I118" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J118" s="5"/>
       <c r="K118" s="2"/>
@@ -10184,7 +10251,9 @@
       <c r="R118" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S118" s="5"/>
+      <c r="S118" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T118" s="5" t="s">
         <v>93</v>
       </c>
@@ -10197,7 +10266,7 @@
       <c r="Y118" s="2"/>
       <c r="Z118" s="2"/>
     </row>
-    <row r="119" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="19">
         <v>117</v>
       </c>
@@ -10205,10 +10274,10 @@
         <v>26</v>
       </c>
       <c r="C119" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D119" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>93</v>
@@ -10217,28 +10286,28 @@
         <v>30</v>
       </c>
       <c r="G119" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="H119" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I119" s="7" t="s">
         <v>422</v>
-      </c>
-      <c r="H119" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I119" s="7" t="s">
-        <v>423</v>
       </c>
       <c r="J119" s="13"/>
       <c r="K119" s="3"/>
       <c r="L119" s="3"/>
       <c r="M119" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="N119" s="6" t="s">
         <v>424</v>
-      </c>
-      <c r="N119" s="6" t="s">
-        <v>425</v>
       </c>
       <c r="O119" s="7" t="s">
         <v>46</v>
       </c>
       <c r="P119" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q119" s="28" t="s">
         <v>38</v>
@@ -10246,7 +10315,9 @@
       <c r="R119" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S119" s="13"/>
+      <c r="S119" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T119" s="5" t="s">
         <v>93</v>
       </c>
@@ -10257,18 +10328,18 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="19">
         <v>118</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>93</v>
@@ -10277,28 +10348,28 @@
         <v>30</v>
       </c>
       <c r="G120" s="9" t="s">
+        <v>421</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I120" s="6" t="s">
         <v>422</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I120" s="6" t="s">
-        <v>423</v>
       </c>
       <c r="J120" s="5"/>
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
       <c r="M120" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="N120" s="6" t="s">
         <v>424</v>
-      </c>
-      <c r="N120" s="6" t="s">
-        <v>425</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q120" s="28" t="s">
         <v>38</v>
@@ -10306,7 +10377,9 @@
       <c r="R120" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S120" s="5"/>
+      <c r="S120" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T120" s="5" t="s">
         <v>93</v>
       </c>
@@ -10317,7 +10390,7 @@
       <c r="Y120" s="2"/>
       <c r="Z120" s="2"/>
     </row>
-    <row r="121" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="19">
         <v>119</v>
       </c>
@@ -10325,10 +10398,10 @@
         <v>26</v>
       </c>
       <c r="C121" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D121" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>93</v>
@@ -10337,13 +10410,13 @@
         <v>30</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H121" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J121" s="13"/>
       <c r="K121" s="3"/>
@@ -10354,7 +10427,7 @@
         <v>46</v>
       </c>
       <c r="P121" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q121" s="28" t="s">
         <v>38</v>
@@ -10362,7 +10435,9 @@
       <c r="R121" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S121" s="13"/>
+      <c r="S121" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T121" s="5" t="s">
         <v>93</v>
       </c>
@@ -10375,18 +10450,18 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="19">
         <v>120</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>93</v>
@@ -10395,13 +10470,13 @@
         <v>30</v>
       </c>
       <c r="G122" s="9" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H122" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I122" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="J122" s="5"/>
       <c r="K122" s="2"/>
@@ -10412,7 +10487,7 @@
         <v>46</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q122" s="28" t="s">
         <v>38</v>
@@ -10420,7 +10495,9 @@
       <c r="R122" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S122" s="5"/>
+      <c r="S122" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T122" s="5" t="s">
         <v>93</v>
       </c>
@@ -10433,15 +10510,15 @@
       <c r="Y122" s="2"/>
       <c r="Z122" s="2"/>
     </row>
-    <row r="123" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="19">
         <v>121</v>
       </c>
       <c r="B123" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D123" s="13" t="s">
         <v>87</v>
@@ -10459,7 +10536,7 @@
         <v>32</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J123" s="13"/>
       <c r="K123" s="3"/>
@@ -10470,7 +10547,7 @@
         <v>46</v>
       </c>
       <c r="P123" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q123" s="28" t="s">
         <v>38</v>
@@ -10491,7 +10568,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="19">
         <v>122</v>
       </c>
@@ -10507,13 +10584,13 @@
         <v>88</v>
       </c>
       <c r="G124" s="9" t="s">
+        <v>429</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I124" s="6" t="s">
         <v>430</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I124" s="6" t="s">
-        <v>431</v>
       </c>
       <c r="J124" s="5"/>
       <c r="K124" s="2"/>
@@ -10541,7 +10618,7 @@
       <c r="Y124" s="2"/>
       <c r="Z124" s="2"/>
     </row>
-    <row r="125" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="19">
         <v>123</v>
       </c>
@@ -10549,10 +10626,10 @@
         <v>26</v>
       </c>
       <c r="C125" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="D125" s="13" t="s">
         <v>432</v>
-      </c>
-      <c r="D125" s="13" t="s">
-        <v>433</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>93</v>
@@ -10561,19 +10638,19 @@
         <v>30</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H125" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J125" s="13"/>
       <c r="K125" s="3"/>
       <c r="L125" s="3"/>
       <c r="M125" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N125" s="6" t="s">
         <v>35</v>
@@ -10582,7 +10659,7 @@
         <v>46</v>
       </c>
       <c r="P125" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q125" s="28" t="s">
         <v>38</v>
@@ -10590,7 +10667,9 @@
       <c r="R125" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S125" s="13"/>
+      <c r="S125" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T125" s="5" t="s">
         <v>93</v>
       </c>
@@ -10603,7 +10682,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="19">
         <v>124</v>
       </c>
@@ -10611,10 +10690,10 @@
         <v>26</v>
       </c>
       <c r="C126" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="D126" s="5" t="s">
         <v>432</v>
-      </c>
-      <c r="D126" s="5" t="s">
-        <v>433</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>93</v>
@@ -10629,13 +10708,13 @@
         <v>32</v>
       </c>
       <c r="I126" s="6" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="J126" s="5"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
       <c r="M126" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="N126" s="6" t="s">
         <v>63</v>
@@ -10644,7 +10723,7 @@
         <v>46</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q126" s="28" t="s">
         <v>38</v>
@@ -10652,7 +10731,9 @@
       <c r="R126" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S126" s="5"/>
+      <c r="S126" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T126" s="5" t="s">
         <v>93</v>
       </c>
@@ -10665,7 +10746,7 @@
       <c r="Y126" s="2"/>
       <c r="Z126" s="2"/>
     </row>
-    <row r="127" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="19">
         <v>125</v>
       </c>
@@ -10673,10 +10754,10 @@
         <v>26</v>
       </c>
       <c r="C127" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="D127" s="13" t="s">
         <v>432</v>
-      </c>
-      <c r="D127" s="13" t="s">
-        <v>433</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>93</v>
@@ -10691,13 +10772,13 @@
         <v>32</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J127" s="13"/>
       <c r="K127" s="3"/>
       <c r="L127" s="3"/>
       <c r="M127" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N127" s="6" t="s">
         <v>63</v>
@@ -10706,7 +10787,7 @@
         <v>46</v>
       </c>
       <c r="P127" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q127" s="28" t="s">
         <v>38</v>
@@ -10714,7 +10795,9 @@
       <c r="R127" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S127" s="13"/>
+      <c r="S127" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T127" s="5" t="s">
         <v>93</v>
       </c>
@@ -10727,7 +10810,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="19">
         <v>126</v>
       </c>
@@ -10735,10 +10818,10 @@
         <v>26</v>
       </c>
       <c r="C128" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="D128" s="5" t="s">
         <v>432</v>
-      </c>
-      <c r="D128" s="5" t="s">
-        <v>433</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>93</v>
@@ -10753,13 +10836,13 @@
         <v>32</v>
       </c>
       <c r="I128" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="J128" s="5"/>
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
       <c r="M128" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N128" s="6" t="s">
         <v>63</v>
@@ -10768,7 +10851,7 @@
         <v>46</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q128" s="28" t="s">
         <v>38</v>
@@ -10776,7 +10859,9 @@
       <c r="R128" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S128" s="5"/>
+      <c r="S128" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T128" s="5" t="s">
         <v>93</v>
       </c>
@@ -10789,18 +10874,18 @@
       <c r="Y128" s="2"/>
       <c r="Z128" s="2"/>
     </row>
-    <row r="129" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="19">
         <v>123</v>
       </c>
       <c r="B129" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C129" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="D129" s="13" t="s">
         <v>432</v>
-      </c>
-      <c r="D129" s="13" t="s">
-        <v>433</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>93</v>
@@ -10809,19 +10894,19 @@
         <v>30</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H129" s="7" t="s">
         <v>32</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="J129" s="13"/>
       <c r="K129" s="3"/>
       <c r="L129" s="3"/>
       <c r="M129" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="N129" s="6" t="s">
         <v>35</v>
@@ -10830,7 +10915,7 @@
         <v>46</v>
       </c>
       <c r="P129" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q129" s="28" t="s">
         <v>38</v>
@@ -10838,7 +10923,9 @@
       <c r="R129" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S129" s="13"/>
+      <c r="S129" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T129" s="5" t="s">
         <v>93</v>
       </c>
@@ -10851,18 +10938,18 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="19">
         <v>125</v>
       </c>
       <c r="B130" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C130" s="10" t="s">
+        <v>431</v>
+      </c>
+      <c r="D130" s="13" t="s">
         <v>432</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>433</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>93</v>
@@ -10877,13 +10964,13 @@
         <v>32</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="J130" s="13"/>
       <c r="K130" s="3"/>
       <c r="L130" s="3"/>
       <c r="M130" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N130" s="6" t="s">
         <v>63</v>
@@ -10892,7 +10979,7 @@
         <v>46</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q130" s="28" t="s">
         <v>38</v>
@@ -10900,7 +10987,9 @@
       <c r="R130" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S130" s="13"/>
+      <c r="S130" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T130" s="5" t="s">
         <v>93</v>
       </c>
@@ -10913,7 +11002,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="19">
         <v>127</v>
       </c>
@@ -10921,10 +11010,10 @@
         <v>26</v>
       </c>
       <c r="C131" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D131" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>93</v>
@@ -10939,7 +11028,7 @@
         <v>32</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="J131" s="13"/>
       <c r="K131" s="3"/>
@@ -10950,7 +11039,7 @@
         <v>46</v>
       </c>
       <c r="P131" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q131" s="28" t="s">
         <v>38</v>
@@ -10958,7 +11047,9 @@
       <c r="R131" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S131" s="13"/>
+      <c r="S131" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T131" s="5" t="s">
         <v>93</v>
       </c>
@@ -10971,7 +11062,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="19">
         <v>128</v>
       </c>
@@ -10979,10 +11070,10 @@
         <v>26</v>
       </c>
       <c r="C132" s="9" t="s">
+        <v>441</v>
+      </c>
+      <c r="D132" s="5" t="s">
         <v>442</v>
-      </c>
-      <c r="D132" s="5" t="s">
-        <v>443</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>93</v>
@@ -10997,13 +11088,13 @@
         <v>32</v>
       </c>
       <c r="I132" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="J132" s="5"/>
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
       <c r="M132" s="2" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="N132" s="6" t="s">
         <v>35</v>
@@ -11012,7 +11103,7 @@
         <v>36</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Q132" s="28" t="s">
         <v>38</v>
@@ -11020,7 +11111,9 @@
       <c r="R132" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S132" s="5"/>
+      <c r="S132" s="5" t="s">
+        <v>458</v>
+      </c>
       <c r="T132" s="5" t="s">
         <v>39</v>
       </c>
@@ -11033,7 +11126,7 @@
       <c r="Y132" s="2"/>
       <c r="Z132" s="2"/>
     </row>
-    <row r="133" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="19">
         <v>129</v>
       </c>
@@ -11041,10 +11134,10 @@
         <v>26</v>
       </c>
       <c r="C133" s="10" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="D133" s="13" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>93</v>
@@ -11059,13 +11152,13 @@
         <v>32</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="J133" s="13"/>
       <c r="K133" s="3"/>
       <c r="L133" s="3"/>
       <c r="M133" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="N133" s="6" t="s">
         <v>35</v>
@@ -11074,7 +11167,7 @@
         <v>36</v>
       </c>
       <c r="P133" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="Q133" s="28" t="s">
         <v>38</v>
@@ -11082,7 +11175,9 @@
       <c r="R133" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S133" s="13"/>
+      <c r="S133" s="13" t="s">
+        <v>345</v>
+      </c>
       <c r="T133" s="5" t="s">
         <v>39</v>
       </c>
@@ -11103,10 +11198,10 @@
         <v>26</v>
       </c>
       <c r="C134" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D134" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>93</v>
@@ -11115,13 +11210,13 @@
         <v>30</v>
       </c>
       <c r="G134" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H134" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I134" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="J134" s="5">
         <v>4</v>
@@ -11129,7 +11224,7 @@
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
       <c r="M134" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N134" s="6" t="s">
         <v>35</v>
@@ -11138,7 +11233,7 @@
         <v>36</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q134" s="5" t="s">
         <v>39</v>
@@ -11147,7 +11242,7 @@
         <v>38</v>
       </c>
       <c r="S134" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="T134" s="5" t="s">
         <v>39</v>
@@ -11168,7 +11263,7 @@
         <v>51</v>
       </c>
       <c r="Z134" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="135" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11179,10 +11274,10 @@
         <v>26</v>
       </c>
       <c r="C135" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D135" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D135" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E135" s="6" t="s">
         <v>93</v>
@@ -11191,13 +11286,13 @@
         <v>30</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H135" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I135" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="J135" s="5">
         <v>4</v>
@@ -11205,7 +11300,7 @@
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
       <c r="M135" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N135" s="6" t="s">
         <v>35</v>
@@ -11214,16 +11309,16 @@
         <v>36</v>
       </c>
       <c r="P135" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="Q135" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R135" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S135" s="5" t="s">
         <v>454</v>
-      </c>
-      <c r="Q135" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R135" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S135" s="5" t="s">
-        <v>455</v>
       </c>
       <c r="T135" s="5" t="s">
         <v>39</v>
@@ -11244,7 +11339,7 @@
         <v>51</v>
       </c>
       <c r="Z135" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="136" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11255,10 +11350,10 @@
         <v>26</v>
       </c>
       <c r="C136" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D136" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D136" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>93</v>
@@ -11267,13 +11362,13 @@
         <v>30</v>
       </c>
       <c r="G136" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H136" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I136" s="6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J136" s="5">
         <v>2</v>
@@ -11281,7 +11376,7 @@
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
       <c r="M136" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="N136" s="6" t="s">
         <v>35</v>
@@ -11290,7 +11385,7 @@
         <v>36</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q136" s="5" t="s">
         <v>39</v>
@@ -11299,7 +11394,7 @@
         <v>39</v>
       </c>
       <c r="S136" s="5" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T136" s="5" t="s">
         <v>39</v>
@@ -11316,7 +11411,7 @@
       <c r="X136" s="2"/>
       <c r="Y136" s="2"/>
       <c r="Z136" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="137" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11327,10 +11422,10 @@
         <v>26</v>
       </c>
       <c r="C137" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D137" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D137" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>93</v>
@@ -11339,13 +11434,13 @@
         <v>30</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H137" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I137" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="J137" s="5">
         <v>8</v>
@@ -11353,7 +11448,7 @@
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
       <c r="M137" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N137" s="6" t="s">
         <v>35</v>
@@ -11362,7 +11457,7 @@
         <v>36</v>
       </c>
       <c r="P137" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q137" s="5" t="s">
         <v>39</v>
@@ -11371,7 +11466,7 @@
         <v>39</v>
       </c>
       <c r="S137" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T137" s="5" t="s">
         <v>39</v>
@@ -11397,10 +11492,10 @@
         <v>26</v>
       </c>
       <c r="C138" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D138" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D138" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>93</v>
@@ -11409,13 +11504,13 @@
         <v>30</v>
       </c>
       <c r="G138" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H138" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I138" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="J138" s="5">
         <v>3</v>
@@ -11423,7 +11518,7 @@
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
       <c r="M138" s="2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="N138" s="6" t="s">
         <v>35</v>
@@ -11432,7 +11527,7 @@
         <v>36</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q138" s="5" t="s">
         <v>39</v>
@@ -11441,7 +11536,7 @@
         <v>39</v>
       </c>
       <c r="S138" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T138" s="5" t="s">
         <v>39</v>
@@ -11458,7 +11553,7 @@
       <c r="X138" s="2"/>
       <c r="Y138" s="2"/>
       <c r="Z138" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="139" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -11469,10 +11564,10 @@
         <v>26</v>
       </c>
       <c r="C139" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D139" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D139" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E139" s="6" t="s">
         <v>93</v>
@@ -11481,13 +11576,13 @@
         <v>30</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H139" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I139" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J139" s="5">
         <v>4</v>
@@ -11495,7 +11590,7 @@
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
       <c r="M139" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="N139" s="6" t="s">
         <v>35</v>
@@ -11504,7 +11599,7 @@
         <v>36</v>
       </c>
       <c r="P139" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q139" s="5" t="s">
         <v>39</v>
@@ -11513,7 +11608,7 @@
         <v>39</v>
       </c>
       <c r="S139" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T139" s="5" t="s">
         <v>39</v>
@@ -11539,10 +11634,10 @@
         <v>26</v>
       </c>
       <c r="C140" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D140" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D140" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>93</v>
@@ -11551,13 +11646,13 @@
         <v>30</v>
       </c>
       <c r="G140" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H140" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I140" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="J140" s="5">
         <v>4</v>
@@ -11565,7 +11660,7 @@
       <c r="K140" s="2"/>
       <c r="L140" s="2"/>
       <c r="M140" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N140" s="6" t="s">
         <v>35</v>
@@ -11574,7 +11669,7 @@
         <v>36</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q140" s="5" t="s">
         <v>39</v>
@@ -11583,7 +11678,7 @@
         <v>39</v>
       </c>
       <c r="S140" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T140" s="5" t="s">
         <v>39</v>
@@ -11609,10 +11704,10 @@
         <v>26</v>
       </c>
       <c r="C141" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D141" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D141" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E141" s="6" t="s">
         <v>93</v>
@@ -11621,13 +11716,13 @@
         <v>30</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H141" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I141" s="6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="J141" s="5">
         <v>3</v>
@@ -11635,7 +11730,7 @@
       <c r="K141" s="2"/>
       <c r="L141" s="2"/>
       <c r="M141" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N141" s="6" t="s">
         <v>35</v>
@@ -11644,7 +11739,7 @@
         <v>36</v>
       </c>
       <c r="P141" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q141" s="5" t="s">
         <v>39</v>
@@ -11653,7 +11748,7 @@
         <v>39</v>
       </c>
       <c r="S141" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T141" s="5" t="s">
         <v>39</v>
@@ -11679,10 +11774,10 @@
         <v>26</v>
       </c>
       <c r="C142" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D142" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D142" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>93</v>
@@ -11691,13 +11786,13 @@
         <v>30</v>
       </c>
       <c r="G142" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H142" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I142" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="J142" s="5">
         <v>4</v>
@@ -11705,7 +11800,7 @@
       <c r="K142" s="2"/>
       <c r="L142" s="2"/>
       <c r="M142" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="N142" s="6" t="s">
         <v>35</v>
@@ -11714,7 +11809,7 @@
         <v>36</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q142" s="5" t="s">
         <v>39</v>
@@ -11723,7 +11818,7 @@
         <v>39</v>
       </c>
       <c r="S142" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T142" s="5" t="s">
         <v>39</v>
@@ -11749,10 +11844,10 @@
         <v>26</v>
       </c>
       <c r="C143" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D143" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D143" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E143" s="6" t="s">
         <v>93</v>
@@ -11761,13 +11856,13 @@
         <v>30</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H143" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I143" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="J143" s="5">
         <v>2</v>
@@ -11775,7 +11870,7 @@
       <c r="K143" s="2"/>
       <c r="L143" s="2"/>
       <c r="M143" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="N143" s="6" t="s">
         <v>35</v>
@@ -11784,7 +11879,7 @@
         <v>36</v>
       </c>
       <c r="P143" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q143" s="5" t="s">
         <v>39</v>
@@ -11793,7 +11888,7 @@
         <v>39</v>
       </c>
       <c r="S143" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T143" s="5" t="s">
         <v>39</v>
@@ -11819,10 +11914,10 @@
         <v>26</v>
       </c>
       <c r="C144" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D144" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D144" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>93</v>
@@ -11831,13 +11926,13 @@
         <v>30</v>
       </c>
       <c r="G144" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H144" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I144" s="6" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="J144" s="5">
         <v>2</v>
@@ -11845,7 +11940,7 @@
       <c r="K144" s="2"/>
       <c r="L144" s="2"/>
       <c r="M144" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="N144" s="6" t="s">
         <v>35</v>
@@ -11854,7 +11949,7 @@
         <v>36</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q144" s="5" t="s">
         <v>39</v>
@@ -11863,7 +11958,7 @@
         <v>39</v>
       </c>
       <c r="S144" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T144" s="5" t="s">
         <v>39</v>
@@ -11889,10 +11984,10 @@
         <v>26</v>
       </c>
       <c r="C145" s="9" t="s">
+        <v>450</v>
+      </c>
+      <c r="D145" s="5" t="s">
         <v>451</v>
-      </c>
-      <c r="D145" s="5" t="s">
-        <v>452</v>
       </c>
       <c r="E145" s="6" t="s">
         <v>93</v>
@@ -11901,13 +11996,13 @@
         <v>30</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H145" s="6" t="s">
         <v>32</v>
       </c>
       <c r="I145" s="6" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J145" s="5">
         <v>8</v>
@@ -11915,7 +12010,7 @@
       <c r="K145" s="2"/>
       <c r="L145" s="2"/>
       <c r="M145" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="N145" s="6" t="s">
         <v>35</v>
@@ -11924,7 +12019,7 @@
         <v>36</v>
       </c>
       <c r="P145" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q145" s="5" t="s">
         <v>39</v>
@@ -11933,7 +12028,7 @@
         <v>39</v>
       </c>
       <c r="S145" s="5" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T145" s="5" t="s">
         <v>39</v>
@@ -11951,7 +12046,7 @@
       <c r="Y145" s="2"/>
       <c r="Z145" s="2"/>
     </row>
-    <row r="146" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="19">
         <v>142</v>
       </c>
@@ -11959,13 +12054,13 @@
         <v>26</v>
       </c>
       <c r="C146" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D146" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D146" s="5" t="s">
-        <v>461</v>
-      </c>
       <c r="E146" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>30</v>
@@ -11974,16 +12069,16 @@
         <v>32</v>
       </c>
       <c r="H146" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="I146" s="6" t="s">
         <v>462</v>
-      </c>
-      <c r="I146" s="6" t="s">
-        <v>463</v>
       </c>
       <c r="J146" s="5"/>
       <c r="K146" s="2"/>
       <c r="L146" s="2"/>
       <c r="M146" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N146" s="6" t="s">
         <v>35</v>
@@ -11992,7 +12087,7 @@
         <v>46</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q146" s="5" t="s">
         <v>38</v>
@@ -12017,11 +12112,11 @@
         <v>50</v>
       </c>
       <c r="Y146" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z146" s="2"/>
     </row>
-    <row r="147" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="19">
         <v>143</v>
       </c>
@@ -12029,13 +12124,13 @@
         <v>26</v>
       </c>
       <c r="C147" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D147" s="13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>30</v>
@@ -12044,16 +12139,16 @@
         <v>32</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J147" s="13"/>
       <c r="K147" s="3"/>
       <c r="L147" s="3"/>
       <c r="M147" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N147" s="6" t="s">
         <v>35</v>
@@ -12062,7 +12157,7 @@
         <v>46</v>
       </c>
       <c r="P147" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Q147" s="13" t="s">
         <v>38</v>
@@ -12087,11 +12182,11 @@
         <v>50</v>
       </c>
       <c r="Y147" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="19">
         <v>144</v>
       </c>
@@ -12099,7 +12194,7 @@
         <v>26</v>
       </c>
       <c r="C148" s="9" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D148" s="5" t="s">
         <v>87</v>
@@ -12117,7 +12212,7 @@
         <v>32</v>
       </c>
       <c r="I148" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="J148" s="5"/>
       <c r="K148" s="2"/>
@@ -12128,7 +12223,7 @@
         <v>46</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="Q148" s="28" t="s">
         <v>38</v>
@@ -12149,7 +12244,7 @@
       <c r="Y148" s="2"/>
       <c r="Z148" s="2"/>
     </row>
-    <row r="149" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="19">
         <v>145</v>
       </c>
@@ -12157,10 +12252,10 @@
         <v>26</v>
       </c>
       <c r="C149" s="10" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D149" s="13" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>93</v>
@@ -12175,13 +12270,13 @@
         <v>32</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="J149" s="13"/>
       <c r="K149" s="3"/>
       <c r="L149" s="3"/>
       <c r="M149" s="24" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="N149" s="6" t="s">
         <v>35</v>
@@ -12190,7 +12285,7 @@
         <v>36</v>
       </c>
       <c r="P149" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q149" s="13" t="s">
         <v>39</v>
@@ -12199,7 +12294,7 @@
         <v>38</v>
       </c>
       <c r="S149" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="T149" s="5" t="s">
         <v>93</v>
@@ -12208,7 +12303,7 @@
         <v>46305</v>
       </c>
       <c r="V149" s="16">
-        <v>46249</v>
+        <v>46402</v>
       </c>
       <c r="W149" s="9" t="s">
         <v>40</v>
@@ -12217,7 +12312,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="19">
         <v>146</v>
       </c>
@@ -12225,10 +12320,10 @@
         <v>26</v>
       </c>
       <c r="C150" s="9" t="s">
+        <v>431</v>
+      </c>
+      <c r="D150" s="5" t="s">
         <v>432</v>
-      </c>
-      <c r="D150" s="5" t="s">
-        <v>433</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>93</v>
@@ -12243,7 +12338,7 @@
         <v>32</v>
       </c>
       <c r="I150" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="J150" s="5"/>
       <c r="K150" s="2"/>
@@ -12254,7 +12349,7 @@
         <v>46</v>
       </c>
       <c r="P150" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="Q150" s="28" t="s">
         <v>38</v>
@@ -12262,7 +12357,9 @@
       <c r="R150" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S150" s="5"/>
+      <c r="S150" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T150" s="5" t="s">
         <v>93</v>
       </c>
@@ -12275,7 +12372,7 @@
       <c r="Y150" s="2"/>
       <c r="Z150" s="2"/>
     </row>
-    <row r="151" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="19">
         <v>148</v>
       </c>
@@ -12283,7 +12380,7 @@
         <v>26</v>
       </c>
       <c r="C151" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D151" s="5" t="s">
         <v>87</v>
@@ -12301,7 +12398,7 @@
         <v>32</v>
       </c>
       <c r="I151" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="J151" s="5"/>
       <c r="K151" s="2"/>
@@ -12318,7 +12415,9 @@
       <c r="R151" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S151" s="5"/>
+      <c r="S151" s="13" t="s">
+        <v>110</v>
+      </c>
       <c r="T151" s="5" t="s">
         <v>93</v>
       </c>
@@ -12331,7 +12430,7 @@
       <c r="Y151" s="2"/>
       <c r="Z151" s="2"/>
     </row>
-    <row r="152" spans="1:26" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="19">
         <v>149</v>
       </c>
@@ -12339,10 +12438,10 @@
         <v>26</v>
       </c>
       <c r="C152" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D152" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="D152" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>93</v>
@@ -12357,13 +12456,13 @@
         <v>32</v>
       </c>
       <c r="I152" s="6" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J152" s="5"/>
       <c r="K152" s="2"/>
       <c r="L152" s="2"/>
       <c r="M152" s="2" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="N152" s="6" t="s">
         <v>35</v>
@@ -12372,7 +12471,7 @@
         <v>46</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q152" s="5" t="s">
         <v>38</v>
@@ -12380,7 +12479,9 @@
       <c r="R152" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S152" s="5"/>
+      <c r="S152" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T152" s="5" t="s">
         <v>93</v>
       </c>
@@ -12393,7 +12494,7 @@
       <c r="Y152" s="2"/>
       <c r="Z152" s="2"/>
     </row>
-    <row r="153" spans="1:26" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="19">
         <v>149</v>
       </c>
@@ -12401,10 +12502,10 @@
         <v>26</v>
       </c>
       <c r="C153" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D153" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="D153" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="E153" s="6" t="s">
         <v>93</v>
@@ -12419,13 +12520,13 @@
         <v>32</v>
       </c>
       <c r="I153" s="6" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="J153" s="5"/>
       <c r="K153" s="2"/>
       <c r="L153" s="2"/>
       <c r="M153" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N153" s="6" t="s">
         <v>35</v>
@@ -12434,7 +12535,7 @@
         <v>46</v>
       </c>
       <c r="P153" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q153" s="5" t="s">
         <v>38</v>
@@ -12442,7 +12543,9 @@
       <c r="R153" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S153" s="5"/>
+      <c r="S153" s="5" t="s">
+        <v>494</v>
+      </c>
       <c r="T153" s="5" t="s">
         <v>93</v>
       </c>
@@ -12455,7 +12558,7 @@
       <c r="Y153" s="2"/>
       <c r="Z153" s="2"/>
     </row>
-    <row r="154" spans="1:26" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="19">
         <v>150</v>
       </c>
@@ -12463,10 +12566,10 @@
         <v>26</v>
       </c>
       <c r="C154" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>93</v>
@@ -12475,19 +12578,19 @@
         <v>30</v>
       </c>
       <c r="G154" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H154" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="I154" s="6" t="s">
         <v>482</v>
-      </c>
-      <c r="I154" s="6" t="s">
-        <v>483</v>
       </c>
       <c r="J154" s="5"/>
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
       <c r="M154" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N154" s="6" t="s">
         <v>35</v>
@@ -12496,7 +12599,7 @@
         <v>46</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q154" s="5" t="s">
         <v>38</v>
@@ -12519,7 +12622,7 @@
       <c r="Y154" s="2"/>
       <c r="Z154" s="2"/>
     </row>
-    <row r="155" spans="1:26" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="32.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="19">
         <v>151</v>
       </c>
@@ -12527,10 +12630,10 @@
         <v>26</v>
       </c>
       <c r="C155" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="D155" s="13" t="s">
         <v>478</v>
-      </c>
-      <c r="D155" s="13" t="s">
-        <v>479</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>93</v>
@@ -12545,13 +12648,13 @@
         <v>32</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J155" s="13"/>
       <c r="K155" s="3"/>
       <c r="L155" s="3"/>
       <c r="M155" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="N155" s="6" t="s">
         <v>35</v>
@@ -12560,7 +12663,7 @@
         <v>46</v>
       </c>
       <c r="P155" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q155" s="28" t="s">
         <v>38</v>
@@ -12568,7 +12671,9 @@
       <c r="R155" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S155" s="13"/>
+      <c r="S155" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T155" s="5" t="s">
         <v>93</v>
       </c>
@@ -12581,7 +12686,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="19">
         <v>152</v>
       </c>
@@ -12589,10 +12694,10 @@
         <v>26</v>
       </c>
       <c r="C156" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>93</v>
@@ -12607,13 +12712,13 @@
         <v>32</v>
       </c>
       <c r="I156" s="6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="J156" s="5"/>
       <c r="K156" s="2"/>
       <c r="L156" s="2"/>
       <c r="M156" s="25" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="N156" s="6" t="s">
         <v>35</v>
@@ -12622,7 +12727,7 @@
         <v>46</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q156" s="28" t="s">
         <v>38</v>
@@ -12630,7 +12735,9 @@
       <c r="R156" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S156" s="5"/>
+      <c r="S156" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T156" s="5" t="s">
         <v>93</v>
       </c>
@@ -12643,7 +12750,7 @@
       <c r="Y156" s="2"/>
       <c r="Z156" s="2"/>
     </row>
-    <row r="157" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="19">
         <v>152</v>
       </c>
@@ -12651,10 +12758,10 @@
         <v>26</v>
       </c>
       <c r="C157" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E157" s="6" t="s">
         <v>93</v>
@@ -12669,22 +12776,22 @@
         <v>32</v>
       </c>
       <c r="I157" s="6" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="J157" s="5"/>
       <c r="K157" s="2"/>
       <c r="L157" s="2"/>
       <c r="M157" s="25" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="N157" s="26" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="O157" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P157" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q157" s="28" t="s">
         <v>38</v>
@@ -12692,7 +12799,9 @@
       <c r="R157" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S157" s="5"/>
+      <c r="S157" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T157" s="5" t="s">
         <v>93</v>
       </c>
@@ -12705,7 +12814,7 @@
       <c r="Y157" s="2"/>
       <c r="Z157" s="2"/>
     </row>
-    <row r="158" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="19">
         <v>152</v>
       </c>
@@ -12713,10 +12822,10 @@
         <v>26</v>
       </c>
       <c r="C158" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>93</v>
@@ -12731,13 +12840,13 @@
         <v>32</v>
       </c>
       <c r="I158" s="6" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="J158" s="5"/>
       <c r="K158" s="2"/>
       <c r="L158" s="2"/>
       <c r="M158" s="25" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="N158" s="26" t="s">
         <v>63</v>
@@ -12746,7 +12855,7 @@
         <v>46</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q158" s="28" t="s">
         <v>38</v>
@@ -12754,7 +12863,9 @@
       <c r="R158" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S158" s="5"/>
+      <c r="S158" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T158" s="5" t="s">
         <v>93</v>
       </c>
@@ -12767,7 +12878,7 @@
       <c r="Y158" s="2"/>
       <c r="Z158" s="2"/>
     </row>
-    <row r="159" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="19">
         <v>152</v>
       </c>
@@ -12775,10 +12886,10 @@
         <v>26</v>
       </c>
       <c r="C159" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E159" s="6" t="s">
         <v>93</v>
@@ -12793,13 +12904,13 @@
         <v>32</v>
       </c>
       <c r="I159" s="6" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="J159" s="5"/>
       <c r="K159" s="2"/>
       <c r="L159" s="2"/>
       <c r="M159" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="N159" s="6" t="s">
         <v>35</v>
@@ -12808,7 +12919,7 @@
         <v>46</v>
       </c>
       <c r="P159" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q159" s="28" t="s">
         <v>38</v>
@@ -12816,7 +12927,9 @@
       <c r="R159" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S159" s="5"/>
+      <c r="S159" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T159" s="5" t="s">
         <v>93</v>
       </c>
@@ -12829,7 +12942,7 @@
       <c r="Y159" s="2"/>
       <c r="Z159" s="2"/>
     </row>
-    <row r="160" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="19">
         <v>153</v>
       </c>
@@ -12837,10 +12950,10 @@
         <v>26</v>
       </c>
       <c r="C160" s="10" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D160" s="13" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>93</v>
@@ -12855,7 +12968,7 @@
         <v>32</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J160" s="13"/>
       <c r="K160" s="3"/>
@@ -12866,7 +12979,7 @@
         <v>46</v>
       </c>
       <c r="P160" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q160" s="28" t="s">
         <v>38</v>
@@ -12874,7 +12987,9 @@
       <c r="R160" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S160" s="13"/>
+      <c r="S160" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T160" s="5" t="s">
         <v>93</v>
       </c>
@@ -12887,7 +13002,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="19">
         <v>154</v>
       </c>
@@ -12895,10 +13010,10 @@
         <v>26</v>
       </c>
       <c r="C161" s="9" t="s">
+        <v>488</v>
+      </c>
+      <c r="D161" s="5" t="s">
         <v>489</v>
-      </c>
-      <c r="D161" s="5" t="s">
-        <v>490</v>
       </c>
       <c r="E161" s="6" t="s">
         <v>93</v>
@@ -12907,21 +13022,21 @@
         <v>30</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H161" s="27">
         <v>46095</v>
       </c>
       <c r="I161" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="J161" s="5" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K161" s="2"/>
       <c r="L161" s="2"/>
       <c r="M161" s="25" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="N161" s="26" t="s">
         <v>35</v>
@@ -12930,16 +13045,16 @@
         <v>36</v>
       </c>
       <c r="P161" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="Q161" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="R161" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="S161" s="5" t="s">
         <v>494</v>
-      </c>
-      <c r="Q161" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="R161" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="S161" s="5" t="s">
-        <v>495</v>
       </c>
       <c r="T161" s="5" t="s">
         <v>39</v>
@@ -12948,7 +13063,7 @@
         <v>46360</v>
       </c>
       <c r="V161" s="16">
-        <v>46286</v>
+        <v>46414</v>
       </c>
       <c r="W161" s="9" t="s">
         <v>40</v>
@@ -12957,7 +13072,7 @@
       <c r="Y161" s="2"/>
       <c r="Z161" s="2"/>
     </row>
-    <row r="162" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="19">
         <v>155</v>
       </c>
@@ -12965,10 +13080,10 @@
         <v>26</v>
       </c>
       <c r="C162" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D162" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>93</v>
@@ -12977,13 +13092,13 @@
         <v>30</v>
       </c>
       <c r="G162" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H162" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="H162" s="7" t="s">
+      <c r="I162" s="7" t="s">
         <v>498</v>
-      </c>
-      <c r="I162" s="7" t="s">
-        <v>499</v>
       </c>
       <c r="J162" s="13"/>
       <c r="K162" s="3"/>
@@ -12994,7 +13109,7 @@
         <v>46</v>
       </c>
       <c r="P162" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q162" s="13" t="s">
         <v>38</v>
@@ -13017,7 +13132,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="19">
         <v>156</v>
       </c>
@@ -13025,7 +13140,7 @@
         <v>26</v>
       </c>
       <c r="C163" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D163" s="13" t="s">
         <v>87</v>
@@ -13043,13 +13158,13 @@
         <v>32</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J163" s="13"/>
       <c r="K163" s="3"/>
       <c r="L163" s="3"/>
       <c r="M163" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N163" s="26" t="s">
         <v>35</v>
@@ -13058,7 +13173,7 @@
         <v>46</v>
       </c>
       <c r="P163" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q163" s="28" t="s">
         <v>38</v>
@@ -13066,7 +13181,9 @@
       <c r="R163" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S163" s="13"/>
+      <c r="S163" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T163" s="5" t="s">
         <v>93</v>
       </c>
@@ -13081,15 +13198,15 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="19">
         <v>156</v>
       </c>
       <c r="B164" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C164" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="D164" s="13" t="s">
         <v>87</v>
@@ -13107,13 +13224,13 @@
         <v>32</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="J164" s="13"/>
       <c r="K164" s="3"/>
       <c r="L164" s="3"/>
       <c r="M164" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N164" s="26" t="s">
         <v>35</v>
@@ -13122,7 +13239,7 @@
         <v>46</v>
       </c>
       <c r="P164" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q164" s="28" t="s">
         <v>38</v>
@@ -13130,7 +13247,9 @@
       <c r="R164" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S164" s="13"/>
+      <c r="S164" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T164" s="5" t="s">
         <v>93</v>
       </c>
@@ -13145,7 +13264,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="19">
         <v>156</v>
       </c>
@@ -13153,7 +13272,7 @@
         <v>26</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D165" s="13" t="s">
         <v>87</v>
@@ -13171,13 +13290,13 @@
         <v>32</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="J165" s="13"/>
       <c r="K165" s="3"/>
       <c r="L165" s="3"/>
       <c r="M165" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N165" s="26" t="s">
         <v>35</v>
@@ -13186,7 +13305,7 @@
         <v>46</v>
       </c>
       <c r="P165" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q165" s="28" t="s">
         <v>38</v>
@@ -13194,7 +13313,9 @@
       <c r="R165" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S165" s="13"/>
+      <c r="S165" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T165" s="5" t="s">
         <v>93</v>
       </c>
@@ -13209,15 +13330,15 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="19">
         <v>156</v>
       </c>
       <c r="B166" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C166" s="9" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D166" s="13" t="s">
         <v>87</v>
@@ -13235,13 +13356,13 @@
         <v>32</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="J166" s="13"/>
       <c r="K166" s="3"/>
       <c r="L166" s="3"/>
       <c r="M166" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="N166" s="26" t="s">
         <v>35</v>
@@ -13250,7 +13371,7 @@
         <v>46</v>
       </c>
       <c r="P166" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="Q166" s="28" t="s">
         <v>38</v>
@@ -13258,7 +13379,9 @@
       <c r="R166" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S166" s="13"/>
+      <c r="S166" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T166" s="5" t="s">
         <v>93</v>
       </c>
@@ -13273,21 +13396,21 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="19">
         <v>157</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C167" s="9" t="s">
+        <v>459</v>
+      </c>
+      <c r="D167" s="5" t="s">
         <v>460</v>
       </c>
-      <c r="D167" s="5" t="s">
-        <v>461</v>
-      </c>
       <c r="E167" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>30</v>
@@ -13296,10 +13419,10 @@
         <v>32</v>
       </c>
       <c r="H167" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="I167" s="6" t="s">
         <v>462</v>
-      </c>
-      <c r="I167" s="6" t="s">
-        <v>463</v>
       </c>
       <c r="J167" s="5"/>
       <c r="K167" s="6" t="s">
@@ -13307,7 +13430,7 @@
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="N167" s="6" t="s">
         <v>35</v>
@@ -13316,7 +13439,7 @@
         <v>46</v>
       </c>
       <c r="P167" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q167" s="5" t="s">
         <v>38</v>
@@ -13339,21 +13462,21 @@
       <c r="Y167" s="2"/>
       <c r="Z167" s="2"/>
     </row>
-    <row r="168" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="19">
         <v>158</v>
       </c>
       <c r="B168" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C168" s="10" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D168" s="13" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>30</v>
@@ -13362,10 +13485,10 @@
         <v>32</v>
       </c>
       <c r="H168" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="J168" s="13"/>
       <c r="K168" s="6" t="s">
@@ -13373,7 +13496,7 @@
       </c>
       <c r="L168" s="3"/>
       <c r="M168" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="N168" s="6" t="s">
         <v>35</v>
@@ -13382,7 +13505,7 @@
         <v>46</v>
       </c>
       <c r="P168" s="7" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="Q168" s="13" t="s">
         <v>38</v>
@@ -13405,7 +13528,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="19">
         <v>159</v>
       </c>
@@ -13413,10 +13536,10 @@
         <v>26</v>
       </c>
       <c r="C169" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E169" s="6" t="s">
         <v>93</v>
@@ -13431,7 +13554,7 @@
         <v>32</v>
       </c>
       <c r="I169" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="J169" s="5"/>
       <c r="K169" s="2"/>
@@ -13442,7 +13565,7 @@
         <v>46</v>
       </c>
       <c r="P169" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q169" s="28" t="s">
         <v>38</v>
@@ -13450,7 +13573,9 @@
       <c r="R169" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S169" s="5"/>
+      <c r="S169" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T169" s="5" t="s">
         <v>93</v>
       </c>
@@ -13463,7 +13588,7 @@
       <c r="Y169" s="2"/>
       <c r="Z169" s="2"/>
     </row>
-    <row r="170" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="19">
         <v>159</v>
       </c>
@@ -13471,10 +13596,10 @@
         <v>26</v>
       </c>
       <c r="C170" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>93</v>
@@ -13489,13 +13614,13 @@
         <v>32</v>
       </c>
       <c r="I170" s="6" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="J170" s="5"/>
       <c r="K170" s="2"/>
       <c r="L170" s="2"/>
       <c r="M170" s="25" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="N170" s="6" t="s">
         <v>35</v>
@@ -13504,7 +13629,7 @@
         <v>46</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q170" s="28" t="s">
         <v>38</v>
@@ -13512,7 +13637,9 @@
       <c r="R170" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S170" s="5"/>
+      <c r="S170" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T170" s="5" t="s">
         <v>93</v>
       </c>
@@ -13525,7 +13652,7 @@
       <c r="Y170" s="2"/>
       <c r="Z170" s="2"/>
     </row>
-    <row r="171" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="19">
         <v>159</v>
       </c>
@@ -13533,10 +13660,10 @@
         <v>26</v>
       </c>
       <c r="C171" s="9" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E171" s="6" t="s">
         <v>93</v>
@@ -13551,13 +13678,13 @@
         <v>32</v>
       </c>
       <c r="I171" s="6" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J171" s="5"/>
       <c r="K171" s="2"/>
       <c r="L171" s="2"/>
       <c r="M171" s="25" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="N171" s="6" t="s">
         <v>35</v>
@@ -13566,7 +13693,7 @@
         <v>46</v>
       </c>
       <c r="P171" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q171" s="28" t="s">
         <v>38</v>
@@ -13574,7 +13701,9 @@
       <c r="R171" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S171" s="5"/>
+      <c r="S171" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T171" s="5" t="s">
         <v>93</v>
       </c>
@@ -13587,7 +13716,7 @@
       <c r="Y171" s="2"/>
       <c r="Z171" s="2"/>
     </row>
-    <row r="172" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="19">
         <v>160</v>
       </c>
@@ -13595,10 +13724,10 @@
         <v>26</v>
       </c>
       <c r="C172" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D172" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>93</v>
@@ -13613,7 +13742,7 @@
         <v>32</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J172" s="13"/>
       <c r="K172" s="3"/>
@@ -13624,7 +13753,7 @@
         <v>46</v>
       </c>
       <c r="P172" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q172" s="28" t="s">
         <v>38</v>
@@ -13632,7 +13761,9 @@
       <c r="R172" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S172" s="13"/>
+      <c r="S172" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T172" s="5" t="s">
         <v>93</v>
       </c>
@@ -13643,18 +13774,18 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="19">
         <v>161</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C173" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D173" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="D173" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="E173" s="6" t="s">
         <v>93</v>
@@ -13669,7 +13800,7 @@
         <v>32</v>
       </c>
       <c r="I173" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J173" s="5"/>
       <c r="K173" s="2"/>
@@ -13680,7 +13811,7 @@
         <v>46</v>
       </c>
       <c r="P173" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q173" s="28" t="s">
         <v>38</v>
@@ -13688,7 +13819,9 @@
       <c r="R173" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S173" s="5"/>
+      <c r="S173" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T173" s="5" t="s">
         <v>93</v>
       </c>
@@ -13701,18 +13834,18 @@
       <c r="Y173" s="2"/>
       <c r="Z173" s="2"/>
     </row>
-    <row r="174" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="19">
         <v>161</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C174" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D174" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="D174" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>93</v>
@@ -13727,22 +13860,22 @@
         <v>32</v>
       </c>
       <c r="I174" s="6" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="J174" s="5"/>
       <c r="K174" s="2"/>
       <c r="L174" s="2"/>
       <c r="M174" s="25" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N174" s="26" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>46</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q174" s="28" t="s">
         <v>38</v>
@@ -13750,7 +13883,9 @@
       <c r="R174" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S174" s="5"/>
+      <c r="S174" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T174" s="5" t="s">
         <v>93</v>
       </c>
@@ -13763,18 +13898,18 @@
       <c r="Y174" s="2"/>
       <c r="Z174" s="2"/>
     </row>
-    <row r="175" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="19">
         <v>162</v>
       </c>
       <c r="B175" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C175" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D175" s="13" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E175" s="7" t="s">
         <v>93</v>
@@ -13783,19 +13918,19 @@
         <v>30</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H175" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="I175" s="7" t="s">
         <v>482</v>
-      </c>
-      <c r="I175" s="7" t="s">
-        <v>483</v>
       </c>
       <c r="J175" s="13"/>
       <c r="K175" s="3"/>
       <c r="L175" s="3"/>
       <c r="M175" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="N175" s="6" t="s">
         <v>35</v>
@@ -13804,7 +13939,7 @@
         <v>46</v>
       </c>
       <c r="P175" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q175" s="13" t="s">
         <v>38</v>
@@ -13829,22 +13964,22 @@
         <v>50</v>
       </c>
       <c r="Y175" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="19">
         <v>163</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C176" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="D176" s="5" t="s">
         <v>478</v>
-      </c>
-      <c r="D176" s="5" t="s">
-        <v>479</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>93</v>
@@ -13859,13 +13994,13 @@
         <v>32</v>
       </c>
       <c r="I176" s="6" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J176" s="5"/>
       <c r="K176" s="2"/>
       <c r="L176" s="2"/>
       <c r="M176" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="N176" s="6" t="s">
         <v>35</v>
@@ -13874,7 +14009,7 @@
         <v>46</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q176" s="28" t="s">
         <v>38</v>
@@ -13882,7 +14017,9 @@
       <c r="R176" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S176" s="5"/>
+      <c r="S176" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T176" s="5" t="s">
         <v>93</v>
       </c>
@@ -13895,18 +14032,18 @@
       <c r="Y176" s="2"/>
       <c r="Z176" s="2"/>
     </row>
-    <row r="177" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="19">
         <v>164</v>
       </c>
       <c r="B177" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C177" s="10" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D177" s="13" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="E177" s="7" t="s">
         <v>93</v>
@@ -13921,13 +14058,13 @@
         <v>32</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="J177" s="13"/>
       <c r="K177" s="3"/>
       <c r="L177" s="3"/>
       <c r="M177" s="25" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="N177" s="26" t="s">
         <v>63</v>
@@ -13936,7 +14073,7 @@
         <v>46</v>
       </c>
       <c r="P177" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q177" s="28" t="s">
         <v>38</v>
@@ -13944,7 +14081,9 @@
       <c r="R177" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="S177" s="13"/>
+      <c r="S177" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T177" s="5" t="s">
         <v>39</v>
       </c>
@@ -13957,18 +14096,18 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="19">
         <v>165</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>93</v>
@@ -13983,7 +14122,7 @@
         <v>32</v>
       </c>
       <c r="I178" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J178" s="5"/>
       <c r="K178" s="2"/>
@@ -13994,7 +14133,7 @@
         <v>46</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="Q178" s="28" t="s">
         <v>38</v>
@@ -14002,7 +14141,9 @@
       <c r="R178" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="S178" s="5"/>
+      <c r="S178" s="5" t="s">
+        <v>110</v>
+      </c>
       <c r="T178" s="5" t="s">
         <v>93</v>
       </c>
@@ -14015,18 +14156,18 @@
       <c r="Y178" s="2"/>
       <c r="Z178" s="2"/>
     </row>
-    <row r="179" spans="1:26" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:26" ht="49.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="19">
         <v>166</v>
       </c>
       <c r="B179" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C179" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D179" s="13" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E179" s="7" t="s">
         <v>93</v>
@@ -14035,13 +14176,13 @@
         <v>30</v>
       </c>
       <c r="G179" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="H179" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="H179" s="7" t="s">
+      <c r="I179" s="7" t="s">
         <v>498</v>
-      </c>
-      <c r="I179" s="7" t="s">
-        <v>499</v>
       </c>
       <c r="J179" s="13"/>
       <c r="K179" s="3"/>
@@ -14052,7 +14193,7 @@
         <v>46</v>
       </c>
       <c r="P179" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="Q179" s="13" t="s">
         <v>38</v>
@@ -14085,13 +14226,22 @@
         <v>93</v>
       </c>
     </row>
-    <row r="180" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="X180">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Z180" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:Z180" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="21">
+      <filters>
+        <dateGroupItem year="2026" month="7" dateTimeGrouping="month"/>
+        <dateGroupItem year="2026" month="8" dateTimeGrouping="month"/>
+        <dateGroupItem year="2026" month="9" dateTimeGrouping="month"/>
+        <dateGroupItem year="2026" month="10" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>

--- a/KAFD00330_Delivery_Master.xlsx
+++ b/KAFD00330_Delivery_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbcmsa-my.sharepoint.com/personal/mohammed_b_sbcm-sa_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="226" documentId="8_{EC754920-70D6-43A1-BAB8-A0090A78B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BE55D66-3440-4EA0-B496-4998CE32B82D}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="8_{EC754920-70D6-43A1-BAB8-A0090A78B4E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1147F9C-117A-434D-A336-128FCA7FBD56}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2453,10 +2453,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z232"/>
+  <dimension ref="A1:Z233"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
@@ -2599,7 +2599,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11">
         <v>1</v>
       </c>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="Z6" s="18"/>
     </row>
-    <row r="7" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11">
         <v>5</v>
       </c>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="Z7" s="18"/>
     </row>
-    <row r="8" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11">
         <v>6</v>
       </c>
@@ -3031,7 +3031,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
         <v>8</v>
       </c>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="Z11" s="18"/>
     </row>
-    <row r="12" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11">
         <v>10</v>
       </c>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="Z12" s="18"/>
     </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11">
         <v>11</v>
       </c>
@@ -3376,7 +3376,7 @@
         <v>46319</v>
       </c>
       <c r="V13" s="14">
-        <v>46356</v>
+        <v>46417</v>
       </c>
       <c r="W13" s="12" t="s">
         <v>354</v>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="Z13" s="18"/>
     </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11">
         <v>12</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>46344</v>
       </c>
       <c r="V14" s="14">
-        <v>46356</v>
+        <v>46417</v>
       </c>
       <c r="W14" s="12" t="s">
         <v>354</v>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="Z14" s="18"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11">
         <v>13</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>46344</v>
       </c>
       <c r="V15" s="14">
-        <v>46356</v>
+        <v>46417</v>
       </c>
       <c r="W15" s="12" t="s">
         <v>354</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="Z15" s="18"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11">
         <v>14</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>46344</v>
       </c>
       <c r="V16" s="14">
-        <v>46356</v>
+        <v>46417</v>
       </c>
       <c r="W16" s="12" t="s">
         <v>354</v>
@@ -3605,7 +3605,7 @@
       </c>
       <c r="Z16" s="18"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11">
         <v>15</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>46330</v>
       </c>
       <c r="V17" s="14">
-        <v>46356</v>
+        <v>46417</v>
       </c>
       <c r="W17" s="12" t="s">
         <v>354</v>
@@ -3677,7 +3677,7 @@
       </c>
       <c r="Z17" s="18"/>
     </row>
-    <row r="18" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11">
         <v>16</v>
       </c>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="Z18" s="18"/>
     </row>
-    <row r="19" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11">
         <v>17</v>
       </c>
@@ -3808,7 +3808,7 @@
         <v>46362</v>
       </c>
       <c r="V19" s="14">
-        <v>46351</v>
+        <v>46412</v>
       </c>
       <c r="W19" s="12" t="s">
         <v>40</v>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="Z19" s="18"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11">
         <v>18</v>
       </c>
@@ -3965,7 +3965,7 @@
       </c>
       <c r="Z21" s="18"/>
     </row>
-    <row r="22" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11">
         <v>20</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="138" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:26" ht="138" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11">
         <v>21</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="24" spans="1:26" ht="386.4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="386.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11">
         <v>22</v>
       </c>
@@ -4187,7 +4187,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="25" spans="1:26" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:26" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="11">
         <v>23</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="11">
         <v>24</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="11">
         <v>25</v>
       </c>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="Z27" s="18"/>
     </row>
-    <row r="28" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="11">
         <v>26</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="29" spans="1:26" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:26" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="11">
         <v>27</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>46353</v>
       </c>
       <c r="V29" s="14">
-        <v>46356</v>
+        <v>46403</v>
       </c>
       <c r="W29" s="12" t="s">
         <v>354</v>
@@ -4547,7 +4547,7 @@
       </c>
       <c r="Z29" s="18"/>
     </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="11">
         <v>28</v>
       </c>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Z30" s="18"/>
     </row>
-    <row r="31" spans="1:26" ht="138" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:26" ht="138" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="11">
         <v>29</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11">
         <v>30</v>
       </c>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z32" s="18"/>
     </row>
-    <row r="33" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="11">
         <v>31</v>
       </c>
@@ -4827,7 +4827,7 @@
       </c>
       <c r="Z33" s="18"/>
     </row>
-    <row r="34" spans="1:26" ht="303.60000000000002" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:26" ht="303.60000000000002" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="11">
         <v>32</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="35" spans="1:26" ht="165.6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:26" ht="165.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="11">
         <v>33</v>
       </c>
@@ -4975,7 +4975,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="36" spans="1:26" ht="248.4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:26" ht="248.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="11">
         <v>34</v>
       </c>
@@ -5049,7 +5049,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="37" spans="1:26" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:26" ht="82.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="11">
         <v>35</v>
       </c>
@@ -5182,7 +5182,7 @@
         <v>46199</v>
       </c>
       <c r="V38" s="14">
-        <v>46296</v>
+        <v>46320</v>
       </c>
       <c r="W38" s="12" t="s">
         <v>49</v>
@@ -5195,7 +5195,7 @@
       </c>
       <c r="Z38" s="18"/>
     </row>
-    <row r="39" spans="1:26" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:26" ht="96.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="11">
         <v>37</v>
       </c>
@@ -5267,7 +5267,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="40" spans="1:26" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:26" ht="55.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="11">
         <v>38</v>
       </c>
@@ -5339,7 +5339,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="41" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="11">
         <v>39</v>
       </c>
@@ -5413,7 +5413,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="42" spans="1:26" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:26" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="11">
         <v>40</v>
       </c>
@@ -5477,7 +5477,7 @@
       </c>
       <c r="Z42" s="18"/>
     </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="11">
         <v>41</v>
       </c>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="Z43" s="18"/>
     </row>
-    <row r="44" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="11">
         <v>42</v>
       </c>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="Z44" s="18"/>
     </row>
-    <row r="45" spans="1:26" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:26" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="11">
         <v>43</v>
       </c>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="Z47" s="18"/>
     </row>
-    <row r="48" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="11">
         <v>46</v>
       </c>
@@ -5893,8 +5893,10 @@
       </c>
       <c r="Z48" s="18"/>
     </row>
-    <row r="49" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
+    <row r="49" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="11">
+        <v>47</v>
+      </c>
       <c r="B49" s="11" t="s">
         <v>26</v>
       </c>
@@ -5963,8 +5965,10 @@
       </c>
       <c r="Z49" s="18"/>
     </row>
-    <row r="50" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
+    <row r="50" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11">
+        <v>48</v>
+      </c>
       <c r="B50" s="11" t="s">
         <v>26</v>
       </c>
@@ -6033,8 +6037,10 @@
       </c>
       <c r="Z50" s="18"/>
     </row>
-    <row r="51" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
+    <row r="51" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="11">
+        <v>49</v>
+      </c>
       <c r="B51" s="11" t="s">
         <v>26</v>
       </c>
@@ -6103,8 +6109,10 @@
       </c>
       <c r="Z51" s="18"/>
     </row>
-    <row r="52" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
+    <row r="52" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="11">
+        <v>50</v>
+      </c>
       <c r="B52" s="11" t="s">
         <v>26</v>
       </c>
@@ -6173,8 +6181,10 @@
       </c>
       <c r="Z52" s="18"/>
     </row>
-    <row r="53" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
+    <row r="53" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="11">
+        <v>51</v>
+      </c>
       <c r="B53" s="11" t="s">
         <v>26</v>
       </c>
@@ -6243,8 +6253,10 @@
       </c>
       <c r="Z53" s="18"/>
     </row>
-    <row r="54" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
+    <row r="54" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="11">
+        <v>52</v>
+      </c>
       <c r="B54" s="11" t="s">
         <v>26</v>
       </c>
@@ -6313,8 +6325,10 @@
       </c>
       <c r="Z54" s="18"/>
     </row>
-    <row r="55" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
+    <row r="55" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="11">
+        <v>53</v>
+      </c>
       <c r="B55" s="11" t="s">
         <v>26</v>
       </c>
@@ -6385,7 +6399,7 @@
     </row>
     <row r="56" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A56" s="11">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>26</v>
@@ -6453,9 +6467,9 @@
       </c>
       <c r="Z56" s="18"/>
     </row>
-    <row r="57" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="11">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>26</v>
@@ -6527,7 +6541,7 @@
     </row>
     <row r="58" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A58" s="11">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>26</v>
@@ -6599,7 +6613,7 @@
     </row>
     <row r="59" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A59" s="11">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>26</v>
@@ -6671,7 +6685,7 @@
     </row>
     <row r="60" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A60" s="11">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>26</v>
@@ -6744,7 +6758,9 @@
       <c r="Z60" s="18"/>
     </row>
     <row r="61" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
+      <c r="A61" s="11">
+        <v>59</v>
+      </c>
       <c r="B61" s="11" t="s">
         <v>26</v>
       </c>
@@ -6816,7 +6832,9 @@
       <c r="Z61" s="18"/>
     </row>
     <row r="62" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
+      <c r="A62" s="11">
+        <v>60</v>
+      </c>
       <c r="B62" s="11" t="s">
         <v>26</v>
       </c>
@@ -6888,7 +6906,9 @@
       <c r="Z62" s="18"/>
     </row>
     <row r="63" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
+      <c r="A63" s="11">
+        <v>61</v>
+      </c>
       <c r="B63" s="11" t="s">
         <v>26</v>
       </c>
@@ -6960,7 +6980,9 @@
       <c r="Z63" s="18"/>
     </row>
     <row r="64" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
+      <c r="A64" s="11">
+        <v>62</v>
+      </c>
       <c r="B64" s="11" t="s">
         <v>26</v>
       </c>
@@ -7032,7 +7054,9 @@
       <c r="Z64" s="18"/>
     </row>
     <row r="65" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
+      <c r="A65" s="11">
+        <v>63</v>
+      </c>
       <c r="B65" s="11" t="s">
         <v>26</v>
       </c>
@@ -7105,7 +7129,7 @@
     </row>
     <row r="66" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A66" s="11">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>26</v>
@@ -7175,9 +7199,9 @@
       </c>
       <c r="Z66" s="18"/>
     </row>
-    <row r="67" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="11">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>26</v>
@@ -7249,7 +7273,7 @@
     </row>
     <row r="68" spans="1:26" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A68" s="11">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>26</v>
@@ -7317,9 +7341,9 @@
       </c>
       <c r="Z68" s="18"/>
     </row>
-    <row r="69" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="11">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>26</v>
@@ -7387,7 +7411,7 @@
     </row>
     <row r="70" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A70" s="11">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>26</v>
@@ -7457,7 +7481,7 @@
     </row>
     <row r="71" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A71" s="11">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>26</v>
@@ -7527,7 +7551,7 @@
     </row>
     <row r="72" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A72" s="11">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>26</v>
@@ -7599,7 +7623,7 @@
     </row>
     <row r="73" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A73" s="11">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>26</v>
@@ -7669,9 +7693,9 @@
       </c>
       <c r="Z73" s="18"/>
     </row>
-    <row r="74" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="11">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>26</v>
@@ -7741,9 +7765,9 @@
       </c>
       <c r="Z74" s="18"/>
     </row>
-    <row r="75" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="11">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>26</v>
@@ -7811,9 +7835,9 @@
         <v>280</v>
       </c>
     </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="11">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>26</v>
@@ -7877,9 +7901,9 @@
       </c>
       <c r="Z76" s="18"/>
     </row>
-    <row r="77" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="11">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>26</v>
@@ -7945,9 +7969,9 @@
       </c>
       <c r="Z77" s="18"/>
     </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="11">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="B78" s="11" t="s">
         <v>26</v>
@@ -8009,7 +8033,7 @@
     </row>
     <row r="79" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A79" s="11">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>26</v>
@@ -8081,9 +8105,9 @@
       </c>
       <c r="Z79" s="18"/>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="11">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>26</v>
@@ -8147,7 +8171,7 @@
     </row>
     <row r="81" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A81" s="11">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>26</v>
@@ -8219,7 +8243,7 @@
     </row>
     <row r="82" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A82" s="11">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>26</v>
@@ -8293,7 +8317,7 @@
     </row>
     <row r="83" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A83" s="11">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>26</v>
@@ -8365,9 +8389,9 @@
       </c>
       <c r="Z83" s="18"/>
     </row>
-    <row r="84" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="11">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>26</v>
@@ -8433,9 +8457,9 @@
       </c>
       <c r="Z84" s="18"/>
     </row>
-    <row r="85" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="11">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>26</v>
@@ -8503,8 +8527,10 @@
       </c>
       <c r="Z85" s="18"/>
     </row>
-    <row r="86" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A86" s="11"/>
+    <row r="86" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="11">
+        <v>84</v>
+      </c>
       <c r="B86" s="11" t="s">
         <v>26</v>
       </c>
@@ -8571,8 +8597,10 @@
       </c>
       <c r="Z86" s="18"/>
     </row>
-    <row r="87" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A87" s="11"/>
+    <row r="87" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="11">
+        <v>85</v>
+      </c>
       <c r="B87" s="11" t="s">
         <v>26</v>
       </c>
@@ -8639,8 +8667,10 @@
       </c>
       <c r="Z87" s="18"/>
     </row>
-    <row r="88" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A88" s="11"/>
+    <row r="88" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="11">
+        <v>86</v>
+      </c>
       <c r="B88" s="11" t="s">
         <v>26</v>
       </c>
@@ -8707,8 +8737,10 @@
       </c>
       <c r="Z88" s="18"/>
     </row>
-    <row r="89" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A89" s="11"/>
+    <row r="89" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="11">
+        <v>87</v>
+      </c>
       <c r="B89" s="11" t="s">
         <v>26</v>
       </c>
@@ -8775,8 +8807,10 @@
       </c>
       <c r="Z89" s="18"/>
     </row>
-    <row r="90" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A90" s="11"/>
+    <row r="90" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="11">
+        <v>88</v>
+      </c>
       <c r="B90" s="11" t="s">
         <v>26</v>
       </c>
@@ -8843,8 +8877,10 @@
       </c>
       <c r="Z90" s="18"/>
     </row>
-    <row r="91" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A91" s="11"/>
+    <row r="91" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="11">
+        <v>89</v>
+      </c>
       <c r="B91" s="11" t="s">
         <v>26</v>
       </c>
@@ -8911,8 +8947,10 @@
       </c>
       <c r="Z91" s="18"/>
     </row>
-    <row r="92" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A92" s="11"/>
+    <row r="92" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="11">
+        <v>90</v>
+      </c>
       <c r="B92" s="11" t="s">
         <v>26</v>
       </c>
@@ -8979,8 +9017,10 @@
       </c>
       <c r="Z92" s="18"/>
     </row>
-    <row r="93" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A93" s="11"/>
+    <row r="93" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="11">
+        <v>91</v>
+      </c>
       <c r="B93" s="11" t="s">
         <v>26</v>
       </c>
@@ -9049,7 +9089,7 @@
     </row>
     <row r="94" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A94" s="11">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>26</v>
@@ -9121,7 +9161,7 @@
     </row>
     <row r="95" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A95" s="11">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>26</v>
@@ -9189,9 +9229,9 @@
       </c>
       <c r="Z95" s="18"/>
     </row>
-    <row r="96" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="11">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>26</v>
@@ -9261,9 +9301,9 @@
       </c>
       <c r="Z96" s="18"/>
     </row>
-    <row r="97" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="11">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>26</v>
@@ -9331,9 +9371,9 @@
       </c>
       <c r="Z97" s="18"/>
     </row>
-    <row r="98" spans="1:26" ht="303.60000000000002" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:26" ht="303.60000000000002" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="11">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>26</v>
@@ -9403,9 +9443,9 @@
         <v>543</v>
       </c>
     </row>
-    <row r="99" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="11">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>26</v>
@@ -9475,7 +9515,7 @@
     </row>
     <row r="100" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A100" s="11">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>26</v>
@@ -9545,7 +9585,7 @@
     </row>
     <row r="101" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A101" s="11">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>26</v>
@@ -9615,7 +9655,7 @@
     </row>
     <row r="102" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A102" s="11">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>26</v>
@@ -9687,7 +9727,7 @@
     </row>
     <row r="103" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A103" s="11">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="B103" s="11" t="s">
         <v>26</v>
@@ -9759,7 +9799,7 @@
     </row>
     <row r="104" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A104" s="11">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>26</v>
@@ -9830,7 +9870,9 @@
       <c r="Z104" s="18"/>
     </row>
     <row r="105" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A105" s="11"/>
+      <c r="A105" s="11">
+        <v>103</v>
+      </c>
       <c r="B105" s="11" t="s">
         <v>26</v>
       </c>
@@ -9900,7 +9942,9 @@
       <c r="Z105" s="18"/>
     </row>
     <row r="106" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A106" s="11"/>
+      <c r="A106" s="11">
+        <v>104</v>
+      </c>
       <c r="B106" s="11" t="s">
         <v>26</v>
       </c>
@@ -9970,7 +10014,9 @@
       <c r="Z106" s="18"/>
     </row>
     <row r="107" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A107" s="11"/>
+      <c r="A107" s="11">
+        <v>105</v>
+      </c>
       <c r="B107" s="11" t="s">
         <v>26</v>
       </c>
@@ -10040,7 +10086,9 @@
       <c r="Z107" s="18"/>
     </row>
     <row r="108" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A108" s="11"/>
+      <c r="A108" s="11">
+        <v>106</v>
+      </c>
       <c r="B108" s="11" t="s">
         <v>26</v>
       </c>
@@ -10110,7 +10158,9 @@
       <c r="Z108" s="18"/>
     </row>
     <row r="109" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A109" s="11"/>
+      <c r="A109" s="11">
+        <v>107</v>
+      </c>
       <c r="B109" s="11" t="s">
         <v>26</v>
       </c>
@@ -10180,7 +10230,9 @@
       <c r="Z109" s="18"/>
     </row>
     <row r="110" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A110" s="11"/>
+      <c r="A110" s="11">
+        <v>108</v>
+      </c>
       <c r="B110" s="11" t="s">
         <v>26</v>
       </c>
@@ -10250,7 +10302,9 @@
       <c r="Z110" s="18"/>
     </row>
     <row r="111" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A111" s="11"/>
+      <c r="A111" s="11">
+        <v>109</v>
+      </c>
       <c r="B111" s="11" t="s">
         <v>26</v>
       </c>
@@ -10320,7 +10374,9 @@
       <c r="Z111" s="18"/>
     </row>
     <row r="112" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A112" s="11"/>
+      <c r="A112" s="11">
+        <v>110</v>
+      </c>
       <c r="B112" s="11" t="s">
         <v>26</v>
       </c>
@@ -10390,7 +10446,9 @@
       <c r="Z112" s="18"/>
     </row>
     <row r="113" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A113" s="11"/>
+      <c r="A113" s="11">
+        <v>111</v>
+      </c>
       <c r="B113" s="11" t="s">
         <v>26</v>
       </c>
@@ -10460,7 +10518,9 @@
       <c r="Z113" s="18"/>
     </row>
     <row r="114" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A114" s="11"/>
+      <c r="A114" s="11">
+        <v>112</v>
+      </c>
       <c r="B114" s="11" t="s">
         <v>26</v>
       </c>
@@ -10530,7 +10590,9 @@
       <c r="Z114" s="18"/>
     </row>
     <row r="115" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A115" s="11"/>
+      <c r="A115" s="11">
+        <v>113</v>
+      </c>
       <c r="B115" s="11" t="s">
         <v>26</v>
       </c>
@@ -10600,7 +10662,9 @@
       <c r="Z115" s="18"/>
     </row>
     <row r="116" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A116" s="11"/>
+      <c r="A116" s="11">
+        <v>114</v>
+      </c>
       <c r="B116" s="11" t="s">
         <v>26</v>
       </c>
@@ -10670,7 +10734,9 @@
       <c r="Z116" s="18"/>
     </row>
     <row r="117" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A117" s="11"/>
+      <c r="A117" s="11">
+        <v>115</v>
+      </c>
       <c r="B117" s="11" t="s">
         <v>26</v>
       </c>
@@ -10740,7 +10806,9 @@
       <c r="Z117" s="18"/>
     </row>
     <row r="118" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A118" s="11"/>
+      <c r="A118" s="11">
+        <v>116</v>
+      </c>
       <c r="B118" s="11" t="s">
         <v>26</v>
       </c>
@@ -10810,7 +10878,9 @@
       <c r="Z118" s="18"/>
     </row>
     <row r="119" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A119" s="11"/>
+      <c r="A119" s="11">
+        <v>117</v>
+      </c>
       <c r="B119" s="11" t="s">
         <v>26</v>
       </c>
@@ -10880,7 +10950,9 @@
       <c r="Z119" s="18"/>
     </row>
     <row r="120" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A120" s="11"/>
+      <c r="A120" s="11">
+        <v>118</v>
+      </c>
       <c r="B120" s="11" t="s">
         <v>26</v>
       </c>
@@ -10951,7 +11023,7 @@
     </row>
     <row r="121" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A121" s="11">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="B121" s="11" t="s">
         <v>26</v>
@@ -11021,7 +11093,7 @@
     </row>
     <row r="122" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A122" s="11">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="B122" s="11" t="s">
         <v>26</v>
@@ -11091,7 +11163,7 @@
     </row>
     <row r="123" spans="1:26" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A123" s="11">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="B123" s="11" t="s">
         <v>26</v>
@@ -11161,7 +11233,7 @@
     </row>
     <row r="124" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A124" s="11">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="B124" s="11" t="s">
         <v>26</v>
@@ -11233,9 +11305,9 @@
       </c>
       <c r="Z124" s="18"/>
     </row>
-    <row r="125" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="11">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="B125" s="11" t="s">
         <v>26</v>
@@ -11307,7 +11379,7 @@
     </row>
     <row r="126" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A126" s="11">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>26</v>
@@ -11383,7 +11455,7 @@
     </row>
     <row r="127" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A127" s="11">
-        <v>88</v>
+        <v>125</v>
       </c>
       <c r="B127" s="11" t="s">
         <v>26</v>
@@ -11459,7 +11531,7 @@
     </row>
     <row r="128" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A128" s="11">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="B128" s="11" t="s">
         <v>26</v>
@@ -11535,7 +11607,7 @@
     </row>
     <row r="129" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A129" s="11">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="B129" s="11" t="s">
         <v>26</v>
@@ -11611,7 +11683,7 @@
     </row>
     <row r="130" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A130" s="11">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B130" s="11" t="s">
         <v>26</v>
@@ -11687,7 +11759,7 @@
     </row>
     <row r="131" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A131" s="11">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="B131" s="11" t="s">
         <v>26</v>
@@ -11763,7 +11835,7 @@
     </row>
     <row r="132" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A132" s="11">
-        <v>93</v>
+        <v>130</v>
       </c>
       <c r="B132" s="11" t="s">
         <v>26</v>
@@ -11839,7 +11911,7 @@
     </row>
     <row r="133" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A133" s="11">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="B133" s="11" t="s">
         <v>26</v>
@@ -11915,7 +11987,7 @@
     </row>
     <row r="134" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A134" s="11">
-        <v>95</v>
+        <v>132</v>
       </c>
       <c r="B134" s="11" t="s">
         <v>26</v>
@@ -11989,7 +12061,7 @@
     </row>
     <row r="135" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A135" s="11">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="B135" s="11" t="s">
         <v>26</v>
@@ -12063,7 +12135,7 @@
     </row>
     <row r="136" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A136" s="11">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>26</v>
@@ -12137,7 +12209,7 @@
     </row>
     <row r="137" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A137" s="11">
-        <v>98</v>
+        <v>135</v>
       </c>
       <c r="B137" s="11" t="s">
         <v>26</v>
@@ -12211,7 +12283,7 @@
     </row>
     <row r="138" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A138" s="11">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="B138" s="11" t="s">
         <v>26</v>
@@ -12285,7 +12357,7 @@
     </row>
     <row r="139" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A139" s="11">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="B139" s="11" t="s">
         <v>26</v>
@@ -12359,7 +12431,7 @@
     </row>
     <row r="140" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A140" s="11">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="B140" s="11" t="s">
         <v>26</v>
@@ -12433,7 +12505,7 @@
     </row>
     <row r="141" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A141" s="11">
-        <v>102</v>
+        <v>139</v>
       </c>
       <c r="B141" s="11" t="s">
         <v>26</v>
@@ -12507,7 +12579,7 @@
     </row>
     <row r="142" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A142" s="11">
-        <v>103</v>
+        <v>140</v>
       </c>
       <c r="B142" s="11" t="s">
         <v>26</v>
@@ -12581,7 +12653,7 @@
     </row>
     <row r="143" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A143" s="11">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="B143" s="11"/>
       <c r="C143" s="12" t="s">
@@ -12653,7 +12725,7 @@
     </row>
     <row r="144" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A144" s="11">
-        <v>105</v>
+        <v>142</v>
       </c>
       <c r="B144" s="11" t="s">
         <v>26</v>
@@ -12727,7 +12799,7 @@
     </row>
     <row r="145" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A145" s="11">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="B145" s="11" t="s">
         <v>26</v>
@@ -12797,9 +12869,9 @@
       </c>
       <c r="Z145" s="18"/>
     </row>
-    <row r="146" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="11">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>26</v>
@@ -12869,9 +12941,9 @@
       </c>
       <c r="Z146" s="18"/>
     </row>
-    <row r="147" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="11">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="B147" s="11" t="s">
         <v>26</v>
@@ -12943,7 +13015,7 @@
     </row>
     <row r="148" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A148" s="11">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="B148" s="11" t="s">
         <v>26</v>
@@ -13017,7 +13089,7 @@
     </row>
     <row r="149" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A149" s="11">
-        <v>110</v>
+        <v>147</v>
       </c>
       <c r="B149" s="11" t="s">
         <v>26</v>
@@ -13089,7 +13161,7 @@
     </row>
     <row r="150" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A150" s="11">
-        <v>111</v>
+        <v>148</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>26</v>
@@ -13159,9 +13231,9 @@
       </c>
       <c r="Z150" s="18"/>
     </row>
-    <row r="151" spans="1:26" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:26" ht="41.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="11">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="B151" s="11" t="s">
         <v>26</v>
@@ -13225,9 +13297,9 @@
       </c>
       <c r="Z151" s="18"/>
     </row>
-    <row r="152" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="11">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="B152" s="11"/>
       <c r="C152" s="12" t="s">
@@ -13295,9 +13367,9 @@
       </c>
       <c r="Z152" s="18"/>
     </row>
-    <row r="153" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="11">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="B153" s="11" t="s">
         <v>26</v>
@@ -13367,9 +13439,9 @@
       </c>
       <c r="Z153" s="18"/>
     </row>
-    <row r="154" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="11">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="B154" s="11" t="s">
         <v>26</v>
@@ -13439,9 +13511,9 @@
       </c>
       <c r="Z154" s="18"/>
     </row>
-    <row r="155" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" s="11">
-        <v>116</v>
+        <v>153</v>
       </c>
       <c r="B155" s="11" t="s">
         <v>26</v>
@@ -13511,9 +13583,9 @@
       </c>
       <c r="Z155" s="18"/>
     </row>
-    <row r="156" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" s="11">
-        <v>117</v>
+        <v>154</v>
       </c>
       <c r="B156" s="11" t="s">
         <v>26</v>
@@ -13585,9 +13657,9 @@
       </c>
       <c r="Z156" s="18"/>
     </row>
-    <row r="157" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" s="11">
-        <v>118</v>
+        <v>155</v>
       </c>
       <c r="B157" s="11" t="s">
         <v>372</v>
@@ -13659,9 +13731,9 @@
       </c>
       <c r="Z157" s="18"/>
     </row>
-    <row r="158" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" s="11">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="B158" s="11" t="s">
         <v>372</v>
@@ -13733,9 +13805,9 @@
       </c>
       <c r="Z158" s="18"/>
     </row>
-    <row r="159" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" s="11">
-        <v>120</v>
+        <v>157</v>
       </c>
       <c r="B159" s="11" t="s">
         <v>372</v>
@@ -13807,9 +13879,9 @@
       </c>
       <c r="Z159" s="18"/>
     </row>
-    <row r="160" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" s="11">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="B160" s="11" t="s">
         <v>372</v>
@@ -13881,9 +13953,9 @@
       </c>
       <c r="Z160" s="18"/>
     </row>
-    <row r="161" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" s="11">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="B161" s="11" t="s">
         <v>372</v>
@@ -13955,9 +14027,9 @@
       </c>
       <c r="Z161" s="18"/>
     </row>
-    <row r="162" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" s="11">
-        <v>123</v>
+        <v>160</v>
       </c>
       <c r="B162" s="11" t="s">
         <v>372</v>
@@ -14029,9 +14101,9 @@
       </c>
       <c r="Z162" s="18"/>
     </row>
-    <row r="163" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" s="11">
-        <v>124</v>
+        <v>161</v>
       </c>
       <c r="B163" s="11" t="s">
         <v>372</v>
@@ -14103,9 +14175,9 @@
       </c>
       <c r="Z163" s="18"/>
     </row>
-    <row r="164" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" s="11">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="B164" s="11" t="s">
         <v>372</v>
@@ -14177,9 +14249,9 @@
       </c>
       <c r="Z164" s="18"/>
     </row>
-    <row r="165" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" s="11">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="B165" s="11" t="s">
         <v>164</v>
@@ -14251,9 +14323,9 @@
       </c>
       <c r="Z165" s="18"/>
     </row>
-    <row r="166" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" s="11">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="B166" s="11" t="s">
         <v>26</v>
@@ -14321,9 +14393,9 @@
       </c>
       <c r="Z166" s="18"/>
     </row>
-    <row r="167" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="11">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="B167" s="11" t="s">
         <v>26</v>
@@ -14393,9 +14465,9 @@
       </c>
       <c r="Z167" s="18"/>
     </row>
-    <row r="168" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="11">
-        <v>129</v>
+        <v>166</v>
       </c>
       <c r="B168" s="11" t="s">
         <v>26</v>
@@ -14465,9 +14537,9 @@
       </c>
       <c r="Z168" s="18"/>
     </row>
-    <row r="169" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="11">
-        <v>130</v>
+        <v>167</v>
       </c>
       <c r="B169" s="11" t="s">
         <v>164</v>
@@ -14535,9 +14607,9 @@
       </c>
       <c r="Z169" s="18"/>
     </row>
-    <row r="170" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="11">
-        <v>131</v>
+        <v>168</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>164</v>
@@ -14607,9 +14679,9 @@
       </c>
       <c r="Z170" s="18"/>
     </row>
-    <row r="171" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="11">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="B171" s="11" t="s">
         <v>26</v>
@@ -14671,9 +14743,9 @@
       </c>
       <c r="Z171" s="18"/>
     </row>
-    <row r="172" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="11">
-        <v>133</v>
+        <v>170</v>
       </c>
       <c r="B172" s="11" t="s">
         <v>26</v>
@@ -14739,9 +14811,9 @@
       </c>
       <c r="Z172" s="18"/>
     </row>
-    <row r="173" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="11">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="B173" s="11" t="s">
         <v>164</v>
@@ -14807,9 +14879,9 @@
       </c>
       <c r="Z173" s="18"/>
     </row>
-    <row r="174" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="11">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="B174" s="11" t="s">
         <v>26</v>
@@ -14873,9 +14945,9 @@
       </c>
       <c r="Z174" s="18"/>
     </row>
-    <row r="175" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="11">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="B175" s="11" t="s">
         <v>164</v>
@@ -14939,9 +15011,9 @@
       </c>
       <c r="Z175" s="18"/>
     </row>
-    <row r="176" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="11">
-        <v>137</v>
+        <v>174</v>
       </c>
       <c r="B176" s="11" t="s">
         <v>164</v>
@@ -15007,9 +15079,9 @@
       </c>
       <c r="Z176" s="18"/>
     </row>
-    <row r="177" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="11">
-        <v>138</v>
+        <v>175</v>
       </c>
       <c r="B177" s="11"/>
       <c r="C177" s="12"/>
@@ -15063,9 +15135,9 @@
       </c>
       <c r="Z177" s="18"/>
     </row>
-    <row r="178" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="11">
-        <v>139</v>
+        <v>176</v>
       </c>
       <c r="B178" s="11" t="s">
         <v>26</v>
@@ -15133,9 +15205,9 @@
       </c>
       <c r="Z178" s="18"/>
     </row>
-    <row r="179" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="11">
-        <v>140</v>
+        <v>177</v>
       </c>
       <c r="B179" s="11" t="s">
         <v>26</v>
@@ -15203,9 +15275,9 @@
       </c>
       <c r="Z179" s="18"/>
     </row>
-    <row r="180" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="11">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="B180" s="11" t="s">
         <v>26</v>
@@ -15273,9 +15345,9 @@
       </c>
       <c r="Z180" s="18"/>
     </row>
-    <row r="181" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="11">
-        <v>142</v>
+        <v>179</v>
       </c>
       <c r="B181" s="11" t="s">
         <v>26</v>
@@ -15343,9 +15415,9 @@
       </c>
       <c r="Z181" s="18"/>
     </row>
-    <row r="182" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" s="11">
-        <v>143</v>
+        <v>180</v>
       </c>
       <c r="B182" s="11" t="s">
         <v>164</v>
@@ -15413,9 +15485,9 @@
       </c>
       <c r="Z182" s="18"/>
     </row>
-    <row r="183" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" s="11">
-        <v>144</v>
+        <v>181</v>
       </c>
       <c r="B183" s="11" t="s">
         <v>164</v>
@@ -15483,9 +15555,9 @@
       </c>
       <c r="Z183" s="18"/>
     </row>
-    <row r="184" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" s="11">
-        <v>145</v>
+        <v>182</v>
       </c>
       <c r="B184" s="11" t="s">
         <v>26</v>
@@ -15549,9 +15621,9 @@
       </c>
       <c r="Z184" s="18"/>
     </row>
-    <row r="185" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" s="11">
-        <v>146</v>
+        <v>183</v>
       </c>
       <c r="B185" s="11" t="s">
         <v>26</v>
@@ -15619,9 +15691,9 @@
       </c>
       <c r="Z185" s="18"/>
     </row>
-    <row r="186" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" s="11">
-        <v>147</v>
+        <v>184</v>
       </c>
       <c r="B186" s="11" t="s">
         <v>26</v>
@@ -15691,9 +15763,9 @@
       </c>
       <c r="Z186" s="18"/>
     </row>
-    <row r="187" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" s="11">
-        <v>148</v>
+        <v>185</v>
       </c>
       <c r="B187" s="11" t="s">
         <v>26</v>
@@ -15767,9 +15839,9 @@
         <v>487</v>
       </c>
     </row>
-    <row r="188" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" s="11">
-        <v>149</v>
+        <v>186</v>
       </c>
       <c r="B188" s="11" t="s">
         <v>26</v>
@@ -15843,9 +15915,9 @@
         <v>507</v>
       </c>
     </row>
-    <row r="189" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" s="11">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="B189" s="11" t="s">
         <v>26</v>
@@ -15919,9 +15991,9 @@
         <v>507</v>
       </c>
     </row>
-    <row r="190" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" s="11">
-        <v>151</v>
+        <v>188</v>
       </c>
       <c r="B190" s="11" t="s">
         <v>26</v>
@@ -15993,9 +16065,9 @@
       </c>
       <c r="Z190" s="18"/>
     </row>
-    <row r="191" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" s="11">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="B191" s="11" t="s">
         <v>26</v>
@@ -16069,9 +16141,9 @@
         <v>508</v>
       </c>
     </row>
-    <row r="192" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" s="11">
-        <v>153</v>
+        <v>190</v>
       </c>
       <c r="B192" s="11" t="s">
         <v>26</v>
@@ -16143,9 +16215,9 @@
       </c>
       <c r="Z192" s="18"/>
     </row>
-    <row r="193" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" s="11">
-        <v>154</v>
+        <v>191</v>
       </c>
       <c r="B193" s="11" t="s">
         <v>26</v>
@@ -16217,9 +16289,9 @@
       </c>
       <c r="Z193" s="18"/>
     </row>
-    <row r="194" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" s="11">
-        <v>155</v>
+        <v>192</v>
       </c>
       <c r="B194" s="11" t="s">
         <v>26</v>
@@ -16291,9 +16363,9 @@
       </c>
       <c r="Z194" s="18"/>
     </row>
-    <row r="195" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" s="11">
-        <v>156</v>
+        <v>193</v>
       </c>
       <c r="B195" s="11" t="s">
         <v>26</v>
@@ -16365,9 +16437,9 @@
       </c>
       <c r="Z195" s="18"/>
     </row>
-    <row r="196" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" s="11">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="B196" s="11" t="s">
         <v>26</v>
@@ -16439,9 +16511,9 @@
       </c>
       <c r="Z196" s="18"/>
     </row>
-    <row r="197" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" s="11">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="B197" s="11" t="s">
         <v>26</v>
@@ -16513,9 +16585,9 @@
       </c>
       <c r="Z197" s="18"/>
     </row>
-    <row r="198" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" s="11">
-        <v>159</v>
+        <v>196</v>
       </c>
       <c r="B198" s="11" t="s">
         <v>26</v>
@@ -16587,9 +16659,9 @@
       </c>
       <c r="Z198" s="18"/>
     </row>
-    <row r="199" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" s="11">
-        <v>160</v>
+        <v>197</v>
       </c>
       <c r="B199" s="11" t="s">
         <v>26</v>
@@ -16657,9 +16729,9 @@
       </c>
       <c r="Z199" s="18"/>
     </row>
-    <row r="200" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" s="11">
-        <v>161</v>
+        <v>198</v>
       </c>
       <c r="B200" s="11" t="s">
         <v>26</v>
@@ -16727,9 +16799,9 @@
       </c>
       <c r="Z200" s="18"/>
     </row>
-    <row r="201" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" s="11">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="B201" s="11" t="s">
         <v>26</v>
@@ -16791,9 +16863,9 @@
       </c>
       <c r="Z201" s="18"/>
     </row>
-    <row r="202" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" s="11">
-        <v>163</v>
+        <v>200</v>
       </c>
       <c r="B202" s="11" t="s">
         <v>26</v>
@@ -16863,9 +16935,9 @@
       </c>
       <c r="Z202" s="18"/>
     </row>
-    <row r="203" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" s="11">
-        <v>164</v>
+        <v>201</v>
       </c>
       <c r="B203" s="11" t="s">
         <v>26</v>
@@ -16929,9 +17001,9 @@
       </c>
       <c r="Z203" s="18"/>
     </row>
-    <row r="204" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" s="11">
-        <v>165</v>
+        <v>202</v>
       </c>
       <c r="B204" s="11" t="s">
         <v>26</v>
@@ -16993,9 +17065,9 @@
       </c>
       <c r="Z204" s="18"/>
     </row>
-    <row r="205" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" s="11">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="B205" s="11" t="s">
         <v>26</v>
@@ -17063,9 +17135,9 @@
       </c>
       <c r="Z205" s="18"/>
     </row>
-    <row r="206" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" s="11">
-        <v>167</v>
+        <v>204</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>26</v>
@@ -17133,9 +17205,9 @@
       </c>
       <c r="Z206" s="18"/>
     </row>
-    <row r="207" spans="1:26" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:26" ht="96.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" s="11">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="B207" s="11" t="s">
         <v>26</v>
@@ -17203,9 +17275,9 @@
       </c>
       <c r="Z207" s="18"/>
     </row>
-    <row r="208" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" s="11">
-        <v>169</v>
+        <v>206</v>
       </c>
       <c r="B208" s="11" t="s">
         <v>26</v>
@@ -17273,9 +17345,9 @@
       </c>
       <c r="Z208" s="18"/>
     </row>
-    <row r="209" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" s="11">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="B209" s="11" t="s">
         <v>26</v>
@@ -17343,9 +17415,9 @@
       </c>
       <c r="Z209" s="18"/>
     </row>
-    <row r="210" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" s="11">
-        <v>171</v>
+        <v>208</v>
       </c>
       <c r="B210" s="11" t="s">
         <v>26</v>
@@ -17413,9 +17485,9 @@
       </c>
       <c r="Z210" s="18"/>
     </row>
-    <row r="211" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" s="11">
-        <v>172</v>
+        <v>209</v>
       </c>
       <c r="B211" s="11" t="s">
         <v>26</v>
@@ -17483,9 +17555,9 @@
       </c>
       <c r="Z211" s="18"/>
     </row>
-    <row r="212" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" s="11">
-        <v>173</v>
+        <v>210</v>
       </c>
       <c r="B212" s="11" t="s">
         <v>26</v>
@@ -17553,9 +17625,9 @@
       </c>
       <c r="Z212" s="18"/>
     </row>
-    <row r="213" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" s="11">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="B213" s="11" t="s">
         <v>26</v>
@@ -17619,9 +17691,9 @@
       </c>
       <c r="Z213" s="18"/>
     </row>
-    <row r="214" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" s="11">
-        <v>175</v>
+        <v>212</v>
       </c>
       <c r="B214" s="11" t="s">
         <v>26</v>
@@ -17693,9 +17765,9 @@
       </c>
       <c r="Z214" s="18"/>
     </row>
-    <row r="215" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" s="11">
-        <v>176</v>
+        <v>213</v>
       </c>
       <c r="B215" s="11" t="s">
         <v>26</v>
@@ -17761,7 +17833,7 @@
     </row>
     <row r="216" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A216" s="11">
-        <v>177</v>
+        <v>214</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>26</v>
@@ -17833,7 +17905,7 @@
     </row>
     <row r="217" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A217" s="11">
-        <v>178</v>
+        <v>215</v>
       </c>
       <c r="B217" s="11" t="s">
         <v>164</v>
@@ -17905,7 +17977,7 @@
     </row>
     <row r="218" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A218" s="11">
-        <v>179</v>
+        <v>216</v>
       </c>
       <c r="B218" s="11" t="s">
         <v>26</v>
@@ -17977,7 +18049,7 @@
     </row>
     <row r="219" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A219" s="11">
-        <v>180</v>
+        <v>217</v>
       </c>
       <c r="B219" s="11" t="s">
         <v>164</v>
@@ -18047,9 +18119,9 @@
       </c>
       <c r="Z219" s="18"/>
     </row>
-    <row r="220" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" s="11">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="B220" s="11" t="s">
         <v>164</v>
@@ -18119,9 +18191,9 @@
       </c>
       <c r="Z220" s="18"/>
     </row>
-    <row r="221" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" s="11">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="B221" s="11" t="s">
         <v>164</v>
@@ -18191,9 +18263,9 @@
       </c>
       <c r="Z221" s="18"/>
     </row>
-    <row r="222" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" s="11">
-        <v>183</v>
+        <v>220</v>
       </c>
       <c r="B222" s="11" t="s">
         <v>26</v>
@@ -18257,9 +18329,9 @@
       </c>
       <c r="Z222" s="18"/>
     </row>
-    <row r="223" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" s="11">
-        <v>184</v>
+        <v>221</v>
       </c>
       <c r="B223" s="11" t="s">
         <v>26</v>
@@ -18327,9 +18399,9 @@
       </c>
       <c r="Z223" s="18"/>
     </row>
-    <row r="224" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" s="11">
-        <v>185</v>
+        <v>222</v>
       </c>
       <c r="B224" s="11" t="s">
         <v>26</v>
@@ -18397,9 +18469,9 @@
       </c>
       <c r="Z224" s="18"/>
     </row>
-    <row r="225" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" s="11">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="B225" s="11" t="s">
         <v>26</v>
@@ -18461,9 +18533,9 @@
       </c>
       <c r="Z225" s="18"/>
     </row>
-    <row r="226" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" s="11">
-        <v>187</v>
+        <v>224</v>
       </c>
       <c r="B226" s="11" t="s">
         <v>164</v>
@@ -18527,9 +18599,9 @@
       </c>
       <c r="Z226" s="18"/>
     </row>
-    <row r="227" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" s="11">
-        <v>188</v>
+        <v>225</v>
       </c>
       <c r="B227" s="11" t="s">
         <v>164</v>
@@ -18597,9 +18669,9 @@
       </c>
       <c r="Z227" s="18"/>
     </row>
-    <row r="228" spans="1:26" ht="96.6" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:26" ht="96.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" s="11">
-        <v>189</v>
+        <v>226</v>
       </c>
       <c r="B228" s="11" t="s">
         <v>164</v>
@@ -18667,9 +18739,9 @@
       </c>
       <c r="Z228" s="18"/>
     </row>
-    <row r="229" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" s="11">
-        <v>190</v>
+        <v>227</v>
       </c>
       <c r="B229" s="11" t="s">
         <v>164</v>
@@ -18737,9 +18809,9 @@
       </c>
       <c r="Z229" s="18"/>
     </row>
-    <row r="230" spans="1:26" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:26" ht="27.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" s="11">
-        <v>191</v>
+        <v>228</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>164</v>
@@ -18807,9 +18879,9 @@
       </c>
       <c r="Z230" s="18"/>
     </row>
-    <row r="231" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" s="11">
-        <v>192</v>
+        <v>229</v>
       </c>
       <c r="B231" s="11" t="s">
         <v>164</v>
@@ -18873,9 +18945,9 @@
       </c>
       <c r="Z231" s="18"/>
     </row>
-    <row r="232" spans="1:26" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:26" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" s="11">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="B232" s="11" t="s">
         <v>164</v>
@@ -18943,8 +19015,16 @@
         <v>93</v>
       </c>
     </row>
+    <row r="233" spans="1:26" hidden="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <autoFilter ref="A2:Z233" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:Z233" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="21">
+      <filters>
+        <dateGroupItem year="2026" month="10" dateTimeGrouping="month"/>
+        <dateGroupItem year="2026" month="11" dateTimeGrouping="month"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>

--- a/KAFD00330_Delivery_Master.xlsx
+++ b/KAFD00330_Delivery_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbcmsa-my.sharepoint.com/personal/mohammed_b_sbcm-sa_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="13_ncr:1_{45B3A156-BCB9-450F-B237-8684A2907D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C7535BFF-BC06-424B-8E65-B28B3AC254C8}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{45B3A156-BCB9-450F-B237-8684A2907D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACA5FD4D-4489-4D20-B2EB-54BAFED0165F}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5259" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5262" uniqueCount="786">
   <si>
     <t>KAFD00330 — RO Plant: Material Delivery Master (edit here; sync to the report)</t>
   </si>
@@ -2477,6 +2477,12 @@
   </si>
   <si>
     <t>KAFD-636-SBC-STY-MAR-00002</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-MEC-MIR-00058</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-FFI-MIR-00001</t>
   </si>
 </sst>
 </file>
@@ -7706,7 +7712,7 @@
         <v>49</v>
       </c>
       <c r="Y62" s="12" t="s">
-        <v>353</v>
+        <v>50</v>
       </c>
       <c r="Z62" s="13"/>
       <c r="AA62" s="13" t="s">
@@ -8640,9 +8646,11 @@
         <v>49</v>
       </c>
       <c r="Y74" s="12" t="s">
-        <v>153</v>
-      </c>
-      <c r="Z74" s="13"/>
+        <v>50</v>
+      </c>
+      <c r="Z74" s="13" t="s">
+        <v>785</v>
+      </c>
       <c r="AA74" s="13" t="s">
         <v>656</v>
       </c>
@@ -9731,12 +9739,14 @@
         <v>40</v>
       </c>
       <c r="X88" s="12" t="s">
-        <v>353</v>
+        <v>49</v>
       </c>
       <c r="Y88" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="Z88" s="13"/>
+        <v>50</v>
+      </c>
+      <c r="Z88" s="13" t="s">
+        <v>784</v>
+      </c>
       <c r="AA88" s="13" t="s">
         <v>660</v>
       </c>
@@ -10405,10 +10415,10 @@
         <v>40</v>
       </c>
       <c r="X97" s="12" t="s">
-        <v>353</v>
+        <v>49</v>
       </c>
       <c r="Y97" s="12" t="s">
-        <v>353</v>
+        <v>50</v>
       </c>
       <c r="Z97" s="13"/>
       <c r="AA97" s="13" t="s">
@@ -11477,12 +11487,14 @@
         <v>40</v>
       </c>
       <c r="X111" s="12" t="s">
-        <v>353</v>
+        <v>49</v>
       </c>
       <c r="Y111" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="Z111" s="13"/>
+        <v>50</v>
+      </c>
+      <c r="Z111" s="13" t="s">
+        <v>784</v>
+      </c>
       <c r="AA111" s="13" t="s">
         <v>694</v>
       </c>
@@ -15422,7 +15434,7 @@
         <v>49</v>
       </c>
       <c r="Y161" s="12" t="s">
-        <v>353</v>
+        <v>50</v>
       </c>
       <c r="Z161" s="13"/>
       <c r="AA161" s="13" t="s">
@@ -15805,7 +15817,7 @@
         <v>46318</v>
       </c>
       <c r="V166" s="15">
-        <v>46296</v>
+        <v>46327</v>
       </c>
       <c r="W166" s="12" t="s">
         <v>40</v>
@@ -22535,7 +22547,7 @@
   <pageSetup paperSize="8" scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FF774A08-7C85-4182-A9AC-BF468B4C914C}">
           <x14:formula1>
             <xm:f>Sheet1!$A$2:$A$3</xm:f>

--- a/KAFD00330_Delivery_Master.xlsx
+++ b/KAFD00330_Delivery_Master.xlsx
@@ -8,16 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sbcmsa-my.sharepoint.com/personal/mohammed_b_sbcm-sa_com/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{45B3A156-BCB9-450F-B237-8684A2907D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ACA5FD4D-4489-4D20-B2EB-54BAFED0165F}"/>
+  <xr:revisionPtr revIDLastSave="257" documentId="13_ncr:1_{45B3A156-BCB9-450F-B237-8684A2907D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC38F7E3-9912-4342-A518-3C5A0FC63229}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Delivery" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Delivery!$A$2:$AB$251</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Delivery!$A$2:$AB$254</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Delivery!$A$1:$AB$254</definedName>
   </definedNames>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5262" uniqueCount="786">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5280" uniqueCount="802">
   <si>
     <t>KAFD00330 — RO Plant: Material Delivery Master (edit here; sync to the report)</t>
   </si>
@@ -2484,6 +2485,57 @@
   <si>
     <t>KAFD-636-SBC-FFI-MIR-00001</t>
   </si>
+  <si>
+    <t xml:space="preserve"> ,.</t>
+  </si>
+  <si>
+    <t>KAFD-636-SBC-ELE-MIR-00001
+KAFD-636-SBC-ELE-MIR-00012
+KAFD-636-SBC-ELE-MIR-00014
+KAFD-636-SBC-ELE-MIR-00030</t>
+  </si>
+  <si>
+    <t>Pump No.</t>
+  </si>
+  <si>
+    <t>FAT Status</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>SP-01</t>
+  </si>
+  <si>
+    <t>SP- 4.11.1</t>
+  </si>
+  <si>
+    <t>SP-4.11.2</t>
+  </si>
+  <si>
+    <t>SP-2.15</t>
+  </si>
+  <si>
+    <t>SP-2.09</t>
+  </si>
+  <si>
+    <t>SP-1.11</t>
+  </si>
+  <si>
+    <t>SP-5.06</t>
+  </si>
+  <si>
+    <t>SP-3.1</t>
+  </si>
+  <si>
+    <t>SP-5.03</t>
+  </si>
+  <si>
+    <t>Vertical Turbine</t>
+  </si>
+  <si>
+    <t>SR</t>
+  </si>
 </sst>
 </file>
 
@@ -2492,7 +2544,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2519,6 +2571,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2539,7 +2604,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -2562,11 +2627,185 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2631,6 +2870,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2975,8 +3234,8 @@
     <col min="8" max="8" width="22.88671875" style="4" customWidth="1"/>
     <col min="9" max="9" width="21.33203125" style="3" customWidth="1"/>
     <col min="10" max="10" width="14.77734375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="31.44140625" style="4" customWidth="1"/>
-    <col min="12" max="12" width="16.88671875" style="4" customWidth="1"/>
+    <col min="11" max="11" width="31.44140625" style="4" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="16.88671875" style="4" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="34.109375" style="4" customWidth="1"/>
     <col min="14" max="14" width="20.88671875" style="3" customWidth="1"/>
     <col min="15" max="15" width="20.77734375" style="3" customWidth="1"/>
@@ -3239,7 +3498,9 @@
       </c>
       <c r="S4" s="11"/>
       <c r="T4" s="11"/>
-      <c r="U4" s="14"/>
+      <c r="U4" s="14">
+        <v>46367</v>
+      </c>
       <c r="V4" s="15"/>
       <c r="W4" s="12" t="s">
         <v>353</v>
@@ -3307,7 +3568,9 @@
       </c>
       <c r="S5" s="11"/>
       <c r="T5" s="11"/>
-      <c r="U5" s="14"/>
+      <c r="U5" s="14">
+        <v>46367</v>
+      </c>
       <c r="V5" s="15"/>
       <c r="W5" s="12" t="s">
         <v>353</v>
@@ -3523,7 +3786,7 @@
         <v>36</v>
       </c>
       <c r="P8" s="11" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="Q8" s="11" t="s">
         <v>38</v>
@@ -3547,12 +3810,14 @@
         <v>40</v>
       </c>
       <c r="X8" s="12" t="s">
-        <v>353</v>
+        <v>49</v>
       </c>
       <c r="Y8" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="Z8" s="13"/>
+        <v>153</v>
+      </c>
+      <c r="Z8" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="AA8" s="13" t="s">
         <v>652</v>
       </c>
@@ -3560,7 +3825,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:28" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A9" s="11">
         <v>7</v>
       </c>
@@ -3601,7 +3866,7 @@
         <v>36</v>
       </c>
       <c r="P9" s="11" t="s">
-        <v>37</v>
+        <v>128</v>
       </c>
       <c r="Q9" s="11" t="s">
         <v>38</v>
@@ -3625,12 +3890,14 @@
         <v>40</v>
       </c>
       <c r="X9" s="12" t="s">
-        <v>353</v>
+        <v>49</v>
       </c>
       <c r="Y9" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="Z9" s="13"/>
+        <v>50</v>
+      </c>
+      <c r="Z9" s="13" t="s">
+        <v>787</v>
+      </c>
       <c r="AA9" s="13" t="s">
         <v>650</v>
       </c>
@@ -3704,17 +3971,15 @@
         <v>46321</v>
       </c>
       <c r="W10" s="12" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="X10" s="12" t="s">
-        <v>49</v>
+        <v>353</v>
       </c>
       <c r="Y10" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z10" s="13" t="s">
-        <v>51</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="Z10" s="13"/>
       <c r="AA10" s="13" t="s">
         <v>738</v>
       </c>
@@ -3788,17 +4053,15 @@
         <v>46321</v>
       </c>
       <c r="W11" s="12" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="X11" s="12" t="s">
-        <v>49</v>
+        <v>353</v>
       </c>
       <c r="Y11" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="Z11" s="13" t="s">
-        <v>51</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="Z11" s="13"/>
       <c r="AA11" s="13" t="s">
         <v>736</v>
       </c>
@@ -4375,7 +4638,7 @@
         <v>70</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>35</v>
+        <v>786</v>
       </c>
       <c r="O19" s="11" t="s">
         <v>45</v>
@@ -17328,7 +17591,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="186" spans="1:28" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A186" s="11">
         <v>184</v>
       </c>
@@ -17398,10 +17661,10 @@
       </c>
       <c r="Z186" s="13"/>
       <c r="AA186" s="13" t="s">
-        <v>626</v>
+        <v>421</v>
       </c>
       <c r="AB186" s="13" t="s">
-        <v>627</v>
+        <v>421</v>
       </c>
     </row>
     <row r="187" spans="1:28" x14ac:dyDescent="0.3">
@@ -21188,7 +21451,7 @@
         <v>509</v>
       </c>
       <c r="E237" s="11" t="s">
-        <v>86</v>
+        <v>611</v>
       </c>
       <c r="F237" s="12" t="s">
         <v>92</v>
@@ -21266,7 +21529,7 @@
         <v>509</v>
       </c>
       <c r="E238" s="11" t="s">
-        <v>86</v>
+        <v>611</v>
       </c>
       <c r="F238" s="12" t="s">
         <v>92</v>
@@ -22539,15 +22802,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AB251" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:AB254" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:Z1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="8" scale="28" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="8" scale="30" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FF774A08-7C85-4182-A9AC-BF468B4C914C}">
           <x14:formula1>
             <xm:f>Sheet1!$A$2:$A$3</xm:f>
@@ -22579,6 +22842,133 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F312647B-375E-41A0-9DB8-ECBFEBAC759F}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="22" t="s">
+        <v>801</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>788</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="25">
+        <v>1</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>792</v>
+      </c>
+      <c r="C2" s="27" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="28">
+        <v>2</v>
+      </c>
+      <c r="B3" s="29" t="s">
+        <v>793</v>
+      </c>
+      <c r="C3" s="30" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="28">
+        <v>3</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>794</v>
+      </c>
+      <c r="C4" s="30"/>
+    </row>
+    <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="28">
+        <v>4</v>
+      </c>
+      <c r="B5" s="29" t="s">
+        <v>795</v>
+      </c>
+      <c r="C5" s="30" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="28">
+        <v>5</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>796</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="28">
+        <v>6</v>
+      </c>
+      <c r="B7" s="29" t="s">
+        <v>797</v>
+      </c>
+      <c r="C7" s="30"/>
+    </row>
+    <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A8" s="28">
+        <v>7</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>798</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="28">
+        <v>8</v>
+      </c>
+      <c r="B9" s="29" t="s">
+        <v>799</v>
+      </c>
+      <c r="C9" s="30"/>
+    </row>
+    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.35">
+      <c r="A10" s="28">
+        <v>9</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>791</v>
+      </c>
+      <c r="C10" s="30"/>
+    </row>
+    <row r="11" spans="1:3" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="31">
+        <v>10</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>800</v>
+      </c>
+      <c r="C11" s="33"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E14A222-39F3-423C-A627-D642A8E94DE8}">
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
